--- a/weeks/2026-09-10/巡查表.xlsx
+++ b/weeks/2026-09-10/巡查表.xlsx
@@ -665,9 +665,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O3">
+      <c r="O3" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E9%87%91%E7%94%B0%E8%B7%AF2003_5%E5%8F%B7_%E9%87%91%E6%80%A1%E5%8D%8E%E5%BA%AD.html","查看证据(7项/9张)")</f>
-        <v/>
+        <v>查看证据(7项/9张)</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -784,9 +784,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-4)</t>
         </is>
       </c>
-      <c r="O4">
+      <c r="O4" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E7%A6%8F%E6%B0%91%E8%B7%AF22_3%E5%8F%B7%E7%9A%87%E5%85%B4%E5%A4%A7%E5%8E%A6_%E7%9A%87%E5%85%B4%E5%A4%A7%E5%8E%A6.html","查看证据(4项/9张)")</f>
-        <v/>
+        <v>查看证据(4项/9张)</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -911,9 +911,9 @@
 2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O5">
+      <c r="O5" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%9A%87%E5%B2%97%E5%85%AC%E5%9B%AD%E4%BA%8C%E8%A1%972%E5%8F%B7_%E7%9A%87%E5%BA%AD%E5%BD%A9%E5%9B%AD.html","查看证据(7项/11张)")</f>
-        <v/>
+        <v>查看证据(7项/11张)</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1042,9 +1042,9 @@
 4.5: 回收箱及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O6">
+      <c r="O6" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91_%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91.html","查看证据(11项/23张)")</f>
-        <v/>
+        <v>查看证据(11项/23张)</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1164,9 +1164,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O7">
+      <c r="O7" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%87%A4%E5%87%B0%E8%A1%97%E9%81%93%E5%A1%98%E5%AE%81%E8%8B%91_%E5%A1%98%E5%AE%81%E8%8B%91.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,9 +1282,9 @@
 4.2: 箱体外观应使用“深i回收”标识，并公示备案编号、监管电话、回收电话等信息，回收电话真实有效，提供预约回收服务。（1分） (-1)</t>
         </is>
       </c>
-      <c r="O8">
+      <c r="O8" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA_%E8%88%AA%E5%9F%8E%E8%A1%97%E9%81%93%E9%BB%84%E7%94%B0%E7%A4%BE%E5%8C%BA%E5%88%A9%E8%BE%BE%E6%97%B6%E8%B7%AF_%E9%BB%84%E7%94%B0%E5%B0%8F%E5%8C%BA.html","查看证据(3项/4张)")</f>
-        <v/>
+        <v>查看证据(3项/4张)</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1399,9 +1399,9 @@
 1.4: 各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题。（15分） (-3)</t>
         </is>
       </c>
-      <c r="O9">
+      <c r="O9" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E8%88%AA%E5%9F%8E%E8%A1%97%E9%81%93%E5%88%A9%E9%94%A6%E7%A4%BE%E5%8C%BA%E5%A4%A9%E7%A6%8F%E5%8D%8E%E5%BA%9CA4_101_%E5%B7%A7%E6%89%8B%E5%8E%A8%E5%A8%98.html","查看证据(2项/5张)")</f>
-        <v/>
+        <v>查看证据(2项/5张)</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1522,9 +1522,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O10">
+      <c r="O10" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA107%E5%9B%BD%E9%81%93%E4%B8%8E%E5%87%AF%E6%88%90%E4%B8%80%E8%B7%AF%E4%BA%A4%E5%8F%89%E5%8F%A3%E5%A4%A9%E7%A6%8F%E5%8D%8E%E5%BA%9C_%E5%A4%A9%E7%A6%8F%E5%8D%8E%E5%BA%9C.html","查看证据(3项/7张)")</f>
-        <v/>
+        <v>查看证据(3项/7张)</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1645,9 +1645,9 @@
 3.1: 公共区域张贴或摆放垃圾分类宣传海报或指引等。 (-3)</t>
         </is>
       </c>
-      <c r="O11">
+      <c r="O11" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E9%95%87%E6%B2%99%E6%B5%A6%E4%BA%8C%E6%9D%91%E5%B9%BF%E8%BF%9B%E8%B7%AF24%E5%8F%B7_%E4%BA%9A%E5%8D%8E%E5%B7%A5%E4%B8%9A%E5%9B%AD.html","查看证据(3项/5张)")</f>
-        <v/>
+        <v>查看证据(3项/5张)</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1768,9 +1768,9 @@
 3.1: 用餐区张贴或摆放光盘行动、节约粮食等宣传海报或温馨提示。（5分） (-5)</t>
         </is>
       </c>
-      <c r="O12">
+      <c r="O12" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E8%89%BA%E5%B1%95%E4%B8%80%E8%B7%AF%E8%89%BA%E5%B1%95%E5%B0%8F%E9%95%871%E5%8F%B7%E6%A5%BCT1_001_004_%E9%BA%A6%E5%BD%93%E5%8A%B3_%E6%BB%A1%E7%BA%B7%E5%A4%A9%E5%9C%B0_.html","查看证据(3项/9张)")</f>
-        <v/>
+        <v>查看证据(3项/9张)</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1891,9 +1891,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O13">
+      <c r="O13" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E5%85%B4%E5%AE%87%E8%B7%AF%E4%B8%8E%E7%91%9E%E5%BA%B7%E8%B7%AF%E4%BA%A4%E5%8F%89%E5%8F%A3%E4%B8%9C%E5%8D%97%E9%87%91%E8%BE%BE%E8%8A%B1%E5%9B%AD_%E9%87%91%E8%BE%BE%E8%8A%B1%E5%9B%AD.html","查看证据(3项/5张)")</f>
-        <v/>
+        <v>查看证据(3项/5张)</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -2018,9 +2018,9 @@
 1.7: 各类收集容器的分类标志完整、正确、清晰。 （9分） (-6)</t>
         </is>
       </c>
-      <c r="O14">
+      <c r="O14" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%B2%99%E6%B5%A6%E7%A4%BE%E5%8C%BA%E8%89%BA%E5%B1%95%E5%9B%9B%E8%B7%AF8%E5%8F%B7102%E5%8F%B7_%E6%BB%A1%E4%BA%AC%E5%8D%8E%E5%85%AC%E5%AF%93%E9%85%92%E5%BA%97.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -2142,9 +2142,9 @@
 3.3: 公共打印区张贴“节约用纸”“双面打印”等标语。 (-3)</t>
         </is>
       </c>
-      <c r="O15">
+      <c r="O15" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA_%E8%89%BA%E5%B1%95%E5%9B%9B%E8%B7%AF%E4%B8%8E%E6%9D%BE%E7%A6%8F%E5%A4%A7%E9%81%93%E8%BE%85%E8%B7%AF%E4%BA%A4%E5%8F%89%E5%8F%A3%E4%B8%9C%E5%8D%9780%E7%B1%B3_%E6%BB%A1%E4%BA%AC%E5%8D%8E%E7%9B%88%E7%A1%95.html","查看证据(4项/8张)")</f>
-        <v/>
+        <v>查看证据(4项/8张)</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -2262,9 +2262,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O16">
+      <c r="O16" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E5%88%A9%E8%BE%BE%E8%B7%AF3%E8%BE%BE%E5%88%A9%E8%8A%B1%E5%9B%AD_%E8%BE%BE%E5%88%A9%E8%8A%B1%E5%9B%AD.html","查看证据(5项/12张)")</f>
-        <v/>
+        <v>查看证据(5项/12张)</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -2384,9 +2384,9 @@
 1.16: 禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分） (-4)</t>
         </is>
       </c>
-      <c r="O17">
+      <c r="O17" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E6%B5%A6%E7%A4%BE%E5%8C%BA%E6%B0%B8%E5%85%B4%E8%8A%B1%E5%9B%AD_%E6%B0%B8%E5%85%B4%E8%8A%B1%E5%9B%AD.html","查看证据(2项/4张)")</f>
-        <v/>
+        <v>查看证据(2项/4张)</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -2513,9 +2513,9 @@
 4.1: 小区内设置废旧织物回收箱的企业数量原则上不超过3家。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O18">
+      <c r="O18" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E5%AE%B6%E8%B1%AA%E5%B1%85_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA%E5%BA%97_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA_%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA.html","查看证据(9项/12张)")</f>
-        <v/>
+        <v>查看证据(9项/12张)</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2641,9 +2641,9 @@
 6.1: 公共区域宣传栏张贴垃圾分类投放指引或宣传海报。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O19">
+      <c r="O19" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%B2%99%E6%B1%9F%E8%B7%AF116%E5%8F%B7%E6%B2%99%E6%B5%A6%E4%BA%8C%E6%9D%91%E5%BE%A1%E6%99%AF%E5%9F%8E_%E5%BE%A1%E6%99%AF%E5%9F%8E.html","查看证据(8项/15张)")</f>
-        <v/>
+        <v>查看证据(8项/15张)</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2759,9 +2759,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O20">
+      <c r="O20" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%9D%BE%E5%9B%AD%E5%8C%97%E8%A1%9738%E5%8F%B7_%E6%96%B9%E8%99%B9%E5%A4%A7%E9%99%A2.html","查看证据(3项/3张)")</f>
-        <v/>
+        <v>查看证据(3项/3张)</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2881,9 +2881,9 @@
 1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)</t>
         </is>
       </c>
-      <c r="O21">
+      <c r="O21" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E6%9D%BE%E5%9B%AD%E5%8C%97%E8%A1%9760%E5%8F%B7_%E5%85%AC%E5%AE%89%E5%B1%80%E6%8E%A5%E5%BE%85%E7%AB%99%E5%AE%BF%E8%88%8D.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2999,9 +2999,9 @@
 3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O22">
+      <c r="O22" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF3097_%E6%B4%AA%E6%B6%9B%E5%A4%A7%E5%8E%A6.html","查看证据(3项/3张)")</f>
-        <v/>
+        <v>查看证据(3项/3张)</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -3116,9 +3116,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O23">
+      <c r="O23" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF3073%E5%8F%B7_%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF3073%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -3232,9 +3232,9 @@
           <t>4.1: 不得主动向消费者提供客房一次性日用品。（10分） (-10)</t>
         </is>
       </c>
-      <c r="O24">
+      <c r="O24" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF%E4%B8%AD%E8%88%AA%E5%87%AF%E7%89%B9%E5%85%AC%E5%AF%93%E5%9B%9B%E6%A5%BC_%E9%BA%A6%E5%90%89%E9%85%92%E5%BA%97.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -3355,9 +3355,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O25">
+      <c r="O25" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF3005%E5%8F%B7_%E4%B8%AD%E5%8D%97%E5%B0%8F%E5%8C%BA.html","查看证据(3项/4张)")</f>
-        <v/>
+        <v>查看证据(3项/4张)</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -3474,9 +3474,9 @@
 5.5: 回收箱及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O26">
+      <c r="O26" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BA%A2%E6%A1%82%E8%B7%AF2020_%E9%87%91%E4%BC%97%E7%BB%8F%E5%85%B8%E5%AE%B6%E5%9B%AD.html","查看证据(4项/7张)")</f>
-        <v/>
+        <v>查看证据(4项/7张)</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3591,9 +3591,9 @@
 2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O27">
+      <c r="O27" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E8%A7%82%E8%B7%AF45%E5%8F%B7%E5%A4%A9%E7%8E%91%E5%85%AC%E9%A6%86_%E5%A4%A9%E7%8E%91%E5%85%AC%E9%A6%86.html","查看证据(2项/4张)")</f>
-        <v/>
+        <v>查看证据(2项/4张)</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -3715,9 +3715,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O28">
+      <c r="O28" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E7%A5%A5%E5%88%A9%E8%B7%AF54%E5%8F%B7%E5%AE%9D%E6%B9%96%E6%96%B0%E6%9D%91_%E6%96%B0%E7%A2%91%E6%9D%91.html","查看证据(4项/8张)")</f>
-        <v/>
+        <v>查看证据(4项/8张)</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -3836,9 +3836,9 @@
           <t>2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O29">
+      <c r="O29" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA_%E5%A4%A7%E5%94%90%E6%97%B6%E4%BB%A3.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -3953,9 +3953,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O30">
+      <c r="O30" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E9%BE%99%E5%B2%97%E5%8C%BA%E4%B8%87%E7%A7%91%E5%A4%A9%E8%AA%89%E4%B8%80_%E4%BA%8C%E6%9C%9F_%E4%B8%87%E7%A7%91%E5%A4%A9%E8%AA%89%E4%B8%80_%E4%BA%8C%E6%9C%9F.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -4069,9 +4069,9 @@
           <t>1.3: 至少设置一处有害垃圾收集容器。 (-5)</t>
         </is>
       </c>
-      <c r="O31">
+      <c r="O31" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E4%B8%87%E7%A7%91%E5%A4%A7%E5%8E%A6_%E4%B8%87%E7%A7%91%E5%A4%A7%E5%8E%A6.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -4185,9 +4185,9 @@
           <t>1.3: 各类收集容器的分类标志完整、正确、清晰。 （18分） (-3)</t>
         </is>
       </c>
-      <c r="O32">
+      <c r="O32" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E5%9F%8E%E8%A1%97%E9%81%93%E5%90%89%E7%A5%A5%E7%A4%BE%E5%8C%BA%E9%BE%99%E7%BF%94%E5%A4%A7%E9%81%938014%E5%8F%B7_%E9%BA%A6%E5%BD%93%E5%8A%B3.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -4307,9 +4307,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O33">
+      <c r="O33" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%BD%99%E5%B2%AD%E4%B8%9C%E8%B7%AF11%E5%8F%B7_%E4%BD%99%E5%B2%AD%E5%B1%B1%E5%BA%84.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -4424,9 +4424,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O34">
+      <c r="O34" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%90%89%E7%A5%A5%E8%B7%AF95%E5%8F%B7_%E5%90%89%E7%A5%A5%E6%9D%A5%E8%8A%B1%E5%9B%AD.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -4541,9 +4541,9 @@
 1.6: 设置洗手设施。（2分） (-1)</t>
         </is>
       </c>
-      <c r="O35">
+      <c r="O35" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E6%96%B0%E6%A1%A5%E8%A5%BF%E4%B8%80%E5%B7%B715%E5%8F%B7_%E5%B2%97%E8%B4%9D%E6%9D%91.html","查看证据(2项/4张)")</f>
-        <v/>
+        <v>查看证据(2项/4张)</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -4659,9 +4659,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O36">
+      <c r="O36" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E7%BF%94%E5%A4%A7%E9%81%936132%E5%8F%B7_%E4%B8%9C%E9%83%BD%E8%8A%B1%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据(3项/3张)")</f>
-        <v/>
+        <v>查看证据(3项/3张)</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -4777,9 +4777,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O37">
+      <c r="O37" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E6%80%A1%E7%BF%A0%E8%B7%AF202%E5%8F%B7_%E4%BF%9D%E5%88%A9%E4%B8%8A%E5%9F%8E.html","查看证据(3项/5张)")</f>
-        <v/>
+        <v>查看证据(3项/5张)</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -4896,9 +4896,9 @@
 2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O38">
+      <c r="O38" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E5%A1%98%E5%B0%BE%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%80%E5%8C%BA%E5%B7%A5%E4%B8%9A%E5%A4%A7%E9%81%936_1_%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%80%E5%8C%BA.html","查看证据(4项/12张)")</f>
-        <v/>
+        <v>查看证据(4项/12张)</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -5012,9 +5012,9 @@
           <t>2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O39">
+      <c r="O39" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B8%83%E6%B2%99%E8%B7%AF156%E5%8F%B7_%E7%A5%A5%E4%BA%91%E8%8B%91.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -5128,9 +5128,9 @@
           <t>1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-2)</t>
         </is>
       </c>
-      <c r="O40">
+      <c r="O40" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E6%B2%99%E8%B7%AF172%E5%8F%B7_%E9%A2%82%E9%9B%85%E8%8B%91.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -5247,9 +5247,9 @@
 2.3: 各类垃圾及时清运。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O41">
+      <c r="O41" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%A4%A7%E9%81%93_%E5%B8%83%E5%90%89%E6%AE%B5_2578%E5%8F%B7_%E6%A1%82%E8%8A%B3%E5%9B%AD.html","查看证据(4项/5张)")</f>
-        <v/>
+        <v>查看证据(4项/5张)</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -5365,9 +5365,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O42">
+      <c r="O42" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%A4%A7%E9%81%93_%E5%B8%83%E5%90%89%E6%AE%B5_2582%E5%8F%B7_%E4%B8%AD%E5%85%86%E8%8A%B1%E5%9B%AD.html","查看证据(3项/7张)")</f>
-        <v/>
+        <v>查看证据(3项/7张)</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -5482,9 +5482,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O43">
+      <c r="O43" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%BA%B7%E6%A1%A5%E8%8A%B1%E5%9B%AD%E4%BA%8C%E6%9C%9F_%E4%B8%AD%E5%9F%8E%E5%BA%B7%E6%A1%A5%E8%8A%B1%E5%9B%AD%E8%A5%BF%E5%8C%97100%E7%B1%B3_%E5%BA%B7%E6%A1%A5%E8%8A%B1%E5%9B%AD.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -5605,9 +5605,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O44">
+      <c r="O44" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF2%E5%8F%B7_%E9%95%BF%E5%9F%8E%E4%B8%80%E8%8A%B1%E5%9B%AD.html","查看证据(3项/8张)")</f>
-        <v/>
+        <v>查看证据(3项/8张)</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -5728,9 +5728,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O45">
+      <c r="O45" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF11%E5%8F%B7_%E9%95%BF%E5%AE%89%E8%8A%B1%E5%9B%AD.html","查看证据(3项/4张)")</f>
-        <v/>
+        <v>查看证据(3项/4张)</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -5850,9 +5850,9 @@
 4.4: 设备及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O46">
+      <c r="O46" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%9B%AD%E5%B2%AD%E8%A1%97%E9%81%93%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF8%E5%8F%B7_%E9%95%BF%E5%9F%8E%E4%BA%8C%E8%8A%B1%E5%9B%AD.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -5972,9 +5972,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O47">
+      <c r="O47" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF10%E5%8F%B7_%E9%95%BF%E6%B3%B0%E8%8A%B1%E5%9B%AD.html","查看证据(2项/4张)")</f>
-        <v/>
+        <v>查看证据(2项/4张)</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -6096,9 +6096,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O48">
+      <c r="O48" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E4%BA%94%E8%B7%AF3%E5%8F%B7_%E6%A0%B8%E7%94%B5%E8%8A%B1%E5%9B%AD.html","查看证据(4项/4张)")</f>
-        <v/>
+        <v>查看证据(4项/4张)</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -6214,9 +6214,9 @@
 3.1: 用餐区张贴或摆放光盘行动、节约粮食等宣传海报或温馨提示。（5分） (-5)</t>
         </is>
       </c>
-      <c r="O49">
+      <c r="O49" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E4%BA%94%E8%B7%AF8%E5%8F%B7_%E8%80%81%E7%A2%97%E4%BC%9A_%E7%99%BE%E8%8A%B1%E5%BA%97_.html","查看证据(3项/5张)")</f>
-        <v/>
+        <v>查看证据(3项/5张)</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -6330,9 +6330,9 @@
           <t>3.1: 公共区域张贴或摆放垃圾分类宣传海报或指引等。 （4分） (-4)</t>
         </is>
       </c>
-      <c r="O50">
+      <c r="O50" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF_%E7%99%BD%E6%B2%99%E5%B2%AD%E7%A4%BE%E5%8C%BA%E5%85%AC%E5%9B%AD.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -6452,9 +6452,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O51">
+      <c r="O51" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%A2%85%E9%BE%99%E5%A4%A7%E9%81%932153%E5%8F%B7%E7%A5%A5%E5%92%8C%E5%BE%A1%E5%9B%AD_%E7%A5%A5%E5%92%8C%E5%BE%A1%E5%9B%AD.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -6574,9 +6574,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O52">
+      <c r="O52" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E9%87%91%E8%8B%B9%E6%9E%9C%E8%8A%B1%E5%9B%AD_%E9%87%91%E8%8B%B9%E6%9E%9C%E8%8A%B1%E5%9B%AD.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -6699,9 +6699,9 @@
 3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O53">
+      <c r="O53" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E5%B9%B8%E7%A6%8F%E5%9F%8E%E4%BA%8C%E6%9C%9F_%E5%B9%B8%E7%A6%8F%E5%9F%8E%E6%B6%A6%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据(5项/7张)")</f>
-        <v/>
+        <v>查看证据(5项/7张)</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -6823,9 +6823,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O54">
+      <c r="O54" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E7%99%BE%E8%8A%B1%E4%BA%8C%E8%B7%AF%E5%85%AD%E5%B7%B7_%E7%99%BE%E8%8A%B1%E5%B0%8F%E5%8C%BA.html","查看证据(4项/7张)")</f>
-        <v/>
+        <v>查看证据(4项/7张)</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -6952,9 +6952,9 @@
 4.2: 箱体外观应使用“深i回收”标识，并公示备案编号、监管电话、回收电话等信息，回收电话真实有效，提供预约回收服务。（1分） (-1)</t>
         </is>
       </c>
-      <c r="O55">
+      <c r="O55" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E4%B8%87%E5%AF%8C%E6%A5%BC%E6%A1%91%E8%BE%BE%E5%AE%9D%E7%94%B5%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E6%9D%8E%E5%B1%8B%E6%9D%91.html","查看证据(9项/14张)")</f>
-        <v/>
+        <v>查看证据(9项/14张)</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -7078,9 +7078,9 @@
 5.1: 公共区域宣传栏张贴垃圾分类投放指引或宣传海报。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O56">
+      <c r="O56" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E5%B8%83%E5%90%89%E4%B8%80%E6%9D%91_%E4%BD%95%E5%B1%8B%E6%9D%91.html","查看证据(6项/6张)")</f>
-        <v/>
+        <v>查看证据(6项/6张)</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -7206,9 +7206,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O57">
+      <c r="O57" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E6%B2%99%E9%BE%99%E8%B7%AF32%E4%B9%8B1_3%E5%8F%B7_%E8%80%81%E5%9C%A9%E6%9D%91.html","查看证据(8项/8张)")</f>
-        <v/>
+        <v>查看证据(8项/8张)</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -7322,9 +7322,9 @@
           <t>3.1: 公共区域张贴或摆放垃圾分类宣传海报或指引等。 （5分） (-5)</t>
         </is>
       </c>
-      <c r="O58">
+      <c r="O58" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%AE%9D%E4%B8%BD%E8%B7%AF90%E5%8F%B7_%E7%B2%A4%E5%AE%9D%E7%A4%BE%E5%BA%B7.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -7439,9 +7439,9 @@
 4.1: 不得主动向消费者提供客房一次性日用品。（10分） (-10)</t>
         </is>
       </c>
-      <c r="O59">
+      <c r="O59" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E7%A4%BE%E5%8C%BA%E6%B3%93%E6%B6%A6%E9%85%92%E5%BA%97_%E6%B7%B1%E5%9C%B3%E5%B8%83%E5%90%89%E4%B8%9C%E7%AB%99%E5%BA%97_%E6%B3%93%E6%B6%A6%E9%85%92%E5%BA%97.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -7562,9 +7562,9 @@
 3.1: 用餐区张贴或摆放光盘行动、节约粮食等宣传海报或温馨提示。（5分） (-5)</t>
         </is>
       </c>
-      <c r="O60">
+      <c r="O60" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E4%B8%BD%E5%B1%B1%E8%B7%AF15%E5%8F%B7%E7%A1%85%E8%B0%B7%E4%BA%BA%E6%89%8D%E5%85%AC%E5%AF%93_%E9%BA%A6%E5%BD%93%E5%8A%B3%E5%BA%97.html","查看证据(3项/8张)")</f>
-        <v/>
+        <v>查看证据(3项/8张)</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -7678,9 +7678,9 @@
           <t>3.1: 公共区域张贴或摆放垃圾分类宣传海报或指引等。（4分） (-4)</t>
         </is>
       </c>
-      <c r="O61">
+      <c r="O61" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E5%B8%83%E5%90%89%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99_%E5%B8%83%E5%90%89%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -7799,9 +7799,9 @@
           <t>4.1: 不得免费向消费者提供塑料购物袋。 (-8)</t>
         </is>
       </c>
-      <c r="O62">
+      <c r="O62" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A4%A7%E6%B2%99%E6%B2%B3%E7%94%9F%E6%80%81%E9%95%BF%E5%BB%8A%E7%BB%BF%E9%81%93%E5%8C%97%E4%BA%AC%E5%A4%A7%E5%AD%A6%E6%B7%B1%E5%9C%B3%E7%A0%94%E7%A9%B6%E7%94%9F%E9%99%A2%E6%A0%A1%E5%8C%BA_%E7%94%B0%E5%AF%AE%E5%B8%82%E5%9C%BA.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -7920,9 +7920,9 @@
           <t>1.7: 各类收集容器的分类标志完整、正确、清晰。 （9分） (-6)</t>
         </is>
       </c>
-      <c r="O63">
+      <c r="O63" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E4%B8%BD%E5%B1%B1%E8%B7%AF36%E5%8F%B7%E7%A1%85%E8%B0%B7%E4%BA%BA%E6%89%8D%E5%85%AC%E5%AF%93_%E7%BB%B4%E4%B9%9F%E7%BA%B3%E4%B8%89%E5%A5%BD%E9%85%92%E5%BA%97_%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%B8%BF%E5%8D%93%E9%85%92%E5%BA%97%E7%AE%A1%E7%90%86%E6%9C%89%E9%99%90%E5%85%AC%E5%8F%B8%E6%A1%83%E6%BA%90%E5%88%86%E5%85%AC%E5%8F%B8_.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -8044,9 +8044,9 @@
 3.1: 公共区域张贴或摆放垃圾分类宣传海报或指引等。（4分） (-4)</t>
         </is>
       </c>
-      <c r="O64">
+      <c r="O64" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99_%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99.html","查看证据(4项/4张)")</f>
-        <v/>
+        <v>查看证据(4项/4张)</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -8167,9 +8167,9 @@
 2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O65">
+      <c r="O65" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E8%B7%AF20%E5%8F%B7_%E7%A2%A7%E6%B9%96%E8%8A%B1%E5%9B%AD.html","查看证据(3项/5张)")</f>
-        <v/>
+        <v>查看证据(3项/5张)</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -8288,9 +8288,9 @@
           <t>1.9: 各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O66">
+      <c r="O66" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E7%A1%85%E8%B0%B7%E4%BA%BA%E6%89%8D%E5%85%AC%E5%AF%93_%E8%81%9A%E5%AE%81%E5%B1%B1%E5%BA%84.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -8411,9 +8411,9 @@
 2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O67">
+      <c r="O67" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E7%AC%8B%E5%B2%97%E6%B4%AA%E6%B9%96%E8%8A%B1%E5%9B%AD_%E6%B4%AA%E6%B9%96%E8%8A%B1%E5%9B%AD.html","查看证据(3项/6张)")</f>
-        <v/>
+        <v>查看证据(3项/6张)</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -8527,9 +8527,9 @@
           <t>1.3: 各类收集容器的分类标志完整、正确、清晰。 （18分） (-3)</t>
         </is>
       </c>
-      <c r="O68">
+      <c r="O68" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%96%B0%E4%B8%9C%E6%B1%9F%E6%A1%A5%E5%98%B4%E6%B2%B3%E9%B2%9C%E5%9D%8A_%E6%96%B0%E4%B8%9C%E6%B1%9F%E6%A1%A5%E5%98%B4%E6%B2%B3%E9%B2%9C%E5%9D%8A.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -8646,9 +8646,9 @@
 3.1: 各类垃圾及时清运。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O69">
+      <c r="O69" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%9723%E5%8F%B7_%E7%BF%A0%E7%9B%88%E5%98%89%E5%9B%AD.html","查看证据(4项/6张)")</f>
-        <v/>
+        <v>查看证据(4项/6张)</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -8766,9 +8766,9 @@
 5.2: 箱体外观应使用“深i回收”标识，并公示备案编号、监管电话、回收电话等信息，回收电话真实有效，提供预约回收服务。（1分） (-1)</t>
         </is>
       </c>
-      <c r="O70">
+      <c r="O70" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%97%E4%B8%80%E5%8F%B7%E5%A4%A7%E9%99%A2_%E6%B0%B4%E6%B3%A5%E5%8E%82%E5%B0%8F%E5%8C%BA.html","查看证据(5项/6张)")</f>
-        <v/>
+        <v>查看证据(5项/6张)</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -8889,9 +8889,9 @@
 3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O71">
+      <c r="O71" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%A1%98%E6%9C%97%E6%9D%91_%E5%A1%98%E6%9C%97%E6%9D%91.html","查看证据(3项/4张)")</f>
-        <v/>
+        <v>查看证据(3项/4张)</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -9014,9 +9014,9 @@
 2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O72">
+      <c r="O72" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%9721%E5%8F%B7_%E5%90%88%E6%AD%A3%E9%94%A6%E6%B9%96%E9%80%B8%E5%9B%AD.html","查看证据(5项/8张)")</f>
-        <v/>
+        <v>查看证据(5项/8张)</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
@@ -9135,9 +9135,9 @@
           <t>2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O73">
+      <c r="O73" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%A1%98%E6%9C%97%E6%B0%B4%E6%9C%A8%E4%B8%B9%E5%8D%8E%E5%9B%AD_%E6%B0%B4%E6%9C%A8%E4%B8%B9%E5%8D%8E%E5%9B%AD.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -9258,9 +9258,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O74">
+      <c r="O74" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%BA%8C%E8%A1%9759%E5%8F%B7_%E5%B7%A5%E5%95%86%E5%AE%BF%E8%88%8D.html","查看证据(3项/4张)")</f>
-        <v/>
+        <v>查看证据(3项/4张)</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -9381,9 +9381,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O75">
+      <c r="O75" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%AE%9D%E8%83%BD%E5%9F%8E%E8%A5%BF%E5%8C%BA_%E5%AE%9D%E8%83%BD%E5%9F%8E%E8%A5%BF%E5%8C%BA.html","查看证据(3项/5张)")</f>
-        <v/>
+        <v>查看证据(3项/5张)</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
@@ -9507,9 +9507,9 @@
 5.5: 回收箱及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O76">
+      <c r="O76" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF%E4%B9%A6%E9%99%A2%E8%A1%9711%E5%8F%B7_%E9%87%91%E6%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据(6项/7张)")</f>
-        <v/>
+        <v>查看证据(6项/7张)</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
@@ -9632,9 +9632,9 @@
 5.2: 箱体外观应使用“深i回收”标识，并公示备案编号、监管电话、回收电话等信息，回收电话真实有效，提供预约回收服务。（1分） (-1)</t>
         </is>
       </c>
-      <c r="O77">
+      <c r="O77" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%B9%A6%E9%99%A2%E8%A1%978%E5%8F%B7_%E4%B9%A6%E9%99%A2%E8%A1%978%E5%8F%B7.html","查看证据(5项/6张)")</f>
-        <v/>
+        <v>查看证据(5项/6张)</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
@@ -9754,9 +9754,9 @@
 1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)</t>
         </is>
       </c>
-      <c r="O78">
+      <c r="O78" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%B9%A6%E9%99%A2%E8%A1%977%E5%8F%B7_%E4%B9%A6%E9%99%A2%E8%A1%977%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
@@ -9878,9 +9878,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O79">
+      <c r="O79" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B9%A6%E9%99%A2%E8%A1%97_%E4%B9%A6%E9%99%A2%E8%A1%97_5%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据(4项/4张)")</f>
-        <v/>
+        <v>查看证据(4项/4张)</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
@@ -10004,9 +10004,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O80">
+      <c r="O80" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3101%E5%8F%B7_%E5%9F%B9%E6%A3%AE%E5%A4%A7%E5%8E%A6.html","查看证据(6项/7张)")</f>
-        <v/>
+        <v>查看证据(6项/7张)</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
@@ -10130,9 +10130,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O81">
+      <c r="O81" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3119%E5%8F%B7_%E6%B4%AA%E6%B9%96%E5%A4%A7%E5%8E%A6.html","查看证据(6项/7张)")</f>
-        <v/>
+        <v>查看证据(6项/7张)</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
@@ -10254,9 +10254,9 @@
 3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O82">
+      <c r="O82" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3131%E5%8F%B7_%E6%B0%B4%E4%BA%A7%E5%A4%A7%E5%8E%A6.html","查看证据(4项/5张)")</f>
-        <v/>
+        <v>查看证据(4项/5张)</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
@@ -10370,9 +10370,9 @@
           <t>1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-4)</t>
         </is>
       </c>
-      <c r="O83">
+      <c r="O83" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%9B%90%E7%94%B0%E5%8C%BA%E6%A2%85%E6%B2%99%E8%A1%97%E9%81%93%E4%B8%9C%E6%B5%B7%E5%B2%B8%E7%A4%BE%E5%8C%BA%E4%B8%87%E7%A7%91%E4%B8%9C%E6%B5%B7%E5%B2%B8_%E4%B8%87%E7%A7%91%E4%B8%9C%E6%B5%B7%E5%B2%B8.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -10486,9 +10486,9 @@
           <t>1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O84">
+      <c r="O84" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E4%BA%91%E9%A1%B6%E5%A4%A9%E6%B5%B7_%E4%BA%91%E9%A1%B6%E5%A4%A9%E6%B5%B7.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -10602,9 +10602,9 @@
           <t>1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O85">
+      <c r="O85" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E6%A2%85%E6%B2%99%E8%A1%97%E9%81%93%E6%B5%B7%E8%AF%AD%E4%B8%9C%E5%9B%AD_%E6%B5%B7%E8%AF%AD%E4%B8%9C%E5%9B%AD.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
@@ -10723,9 +10723,9 @@
           <t>1.15: 投放点均安装具备AI识别功能的视频监控设备，监控视野保持在合理角度。（4分） (-2)</t>
         </is>
       </c>
-      <c r="O86">
+      <c r="O86" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E8%B5%9B%E9%BE%99%E8%B1%AA%E8%BD%A9%E5%B0%8F%E5%8C%BA_%E8%B5%9B%E9%BE%99%E8%B1%AA%E8%BD%A9BC%E5%BA%A7.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
@@ -10848,9 +10848,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O87">
+      <c r="O87" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E6%B8%85%E6%B9%96%E7%A4%BE%E5%8C%BA%E6%B8%85%E6%B9%96%E6%96%B0%E6%9D%91_%E6%B8%85%E6%B9%96%E6%96%B0%E6%9D%91.html","查看证据(5项/19张)")</f>
-        <v/>
+        <v>查看证据(5项/19张)</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -10969,9 +10969,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O88">
+      <c r="O88" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E7%BE%8E%E4%B8%BD365%E8%8A%B1%E5%9B%AD_%E7%BE%8E%E4%B8%BD365%E8%8A%B1%E5%9B%AD.html","查看证据(6项/11张)")</f>
-        <v/>
+        <v>查看证据(6项/11张)</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
@@ -11085,9 +11085,9 @@
           <t>1.2: 至少设置一处有害垃圾收集容器。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O89">
+      <c r="O89" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E5%A1%98%E5%B0%BE%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%B0%BE%E5%8D%81%E4%BA%8C%E5%8C%BA%E5%8C%975%E5%B7%B71%E5%8F%B7_%E5%A1%98%E5%B0%BE%E5%8D%81%E4%BA%8C%E5%8C%BA.html","查看证据(1项/5张)")</f>
-        <v/>
+        <v>查看证据(1项/5张)</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
@@ -11204,9 +11204,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O90">
+      <c r="O90" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E5%AF%8C%E8%81%94%E4%B8%80%E5%8C%BA_%E5%AF%8C%E8%81%94%E4%B8%80%E5%8C%BA.html","查看证据(4项/7张)")</f>
-        <v/>
+        <v>查看证据(4项/7张)</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
@@ -11322,9 +11322,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-6)</t>
         </is>
       </c>
-      <c r="O91">
+      <c r="O91" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%BC%8F%E8%8B%B1%E5%A6%87%E7%A7%91_%E5%A1%98%E5%B0%BE%E4%B9%9D%E5%8C%BA.html","查看证据(3项/11张)")</f>
-        <v/>
+        <v>查看证据(3项/11张)</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
@@ -11439,9 +11439,9 @@
 1.5: 至少设置一处有害垃圾收集容器。 (-5)</t>
         </is>
       </c>
-      <c r="O92">
+      <c r="O92" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%A4%A7%E6%A2%85%E6%B2%99%E5%85%AC%E4%BA%A4%E6%80%BB%E7%AB%99_%E5%A4%A7%E6%A2%85%E6%B2%99%E5%85%AC%E4%BA%A4%E6%80%BB%E7%AB%99_M191_.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -11556,9 +11556,9 @@
 3.1: 公共区域张贴或摆放垃圾分类宣传海报或指引等。（4分） (-4)</t>
         </is>
       </c>
-      <c r="O93">
+      <c r="O93" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E4%B8%9C%E6%B5%B7%E5%B2%B8%E7%A4%BE%E5%8C%BA_%E4%B8%9C%E6%B5%B7%E5%B2%B8%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -11672,9 +11672,9 @@
           <t>1.3: 各类收集容器的分类标志完整、正确、清晰。 （18分） (-3)</t>
         </is>
       </c>
-      <c r="O94">
+      <c r="O94" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E6%A2%85%E6%B2%99%E8%A1%97%E9%81%93%E4%BC%98%E5%93%81%E8%89%BA%E5%A2%85%E9%9B%85%E5%B1%85_%E6%BC%AB%E9%AA%91%E9%A4%90%E5%90%A7%E7%A7%81%E6%88%BF%E8%8F%9C.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -11791,9 +11791,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-6)</t>
         </is>
       </c>
-      <c r="O95">
+      <c r="O95" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%BC%8F%E8%8B%B1%E5%A6%87%E7%A7%91_%E5%A1%98%E5%B0%BE%E5%85%AB%E5%8C%BA.html","查看证据(4项/12张)")</f>
-        <v/>
+        <v>查看证据(4项/12张)</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
@@ -11918,9 +11918,9 @@
 3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O96">
+      <c r="O96" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%8E%E5%B7%A5%E4%B8%9A%E5%85%AB%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84%E4%B8%9C%E5%8D%97200%E7%B1%B3%E8%B7%AF%E4%B8%9C_%E6%9B%A6%E6%B9%BE%E5%A4%A9%E9%A6%A5.html","查看证据(7项/19张)")</f>
-        <v/>
+        <v>查看证据(7项/19张)</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
@@ -12039,9 +12039,9 @@
           <t>1.7: 各类收集容器的分类标志完整、正确、清晰。 （9分） (-9)</t>
         </is>
       </c>
-      <c r="O97">
+      <c r="O97" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B2%B8%E6%B9%BE%E4%B8%89%E8%A1%975%E5%8F%B7_%E6%B7%B1%E5%9C%B3%E5%90%8E%E6%B5%B7%E6%9C%A8%E6%A3%89%E8%8A%B1%E9%85%92%E5%BA%97.html","查看证据(1项/5张)")</f>
-        <v/>
+        <v>查看证据(1项/5张)</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
@@ -12156,9 +12156,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-6)</t>
         </is>
       </c>
-      <c r="O98">
+      <c r="O98" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E5%A1%98%E5%B0%BE%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%89%E5%8C%BA_%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%89%E5%8C%BA.html","查看证据(2项/9张)")</f>
-        <v/>
+        <v>查看证据(2项/9张)</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -12276,9 +12276,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-6)</t>
         </is>
       </c>
-      <c r="O99">
+      <c r="O99" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E5%BC%93%E6%9D%91_%E5%BC%93%E6%9D%91.html","查看证据(5项/21张)")</f>
-        <v/>
+        <v>查看证据(5项/21张)</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -12401,9 +12401,9 @@
 3.1: 公共区域张贴或摆放垃圾分类宣传海报或指引等。 (-4)</t>
         </is>
       </c>
-      <c r="O100">
+      <c r="O100" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%B8%9C%E7%BF%A0%E9%9B%85%E5%B1%85%E6%96%B0%E9%A2%86%E6%B1%87%E8%B4%AD%E7%89%A9%E5%B9%BF%E5%9C%BA_%E5%A1%98%E5%B0%BE%E5%BA%97_%E6%96%B0%E9%A2%86%E6%B1%87%E8%B4%AD%E7%89%A9%E4%B8%AD%E5%BF%83.html","查看证据(5项/8张)")</f>
-        <v/>
+        <v>查看证据(5项/8张)</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -12527,9 +12527,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O101">
+      <c r="O101" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E8%9B%87%E5%8F%A3%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%AD%E5%BF%83%E8%B7%AF%E6%AE%B5%E5%90%89%E7%A5%A5%E9%BE%99%E8%8A%B1%E5%9B%AD_%E5%90%89%E7%A5%A5%E9%BE%99%E8%8A%B1%E5%9B%AD.html","查看证据(6项/16张)")</f>
-        <v/>
+        <v>查看证据(6项/16张)</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -12653,9 +12653,9 @@
 3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O102">
+      <c r="O102" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E8%9B%87%E5%8F%A3%E8%A1%97%E9%81%93%E9%A6%99%E6%82%A6%E9%87%8C_%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E%E8%8A%B1%E5%9B%AD_%E4%BA%8C%E6%9C%9F_.html","查看证据(6项/17张)")</f>
-        <v/>
+        <v>查看证据(6项/17张)</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
@@ -12771,9 +12771,9 @@
 3.1: 公共区域张贴或摆放垃圾分类宣传海报或指引等。 (-4)</t>
         </is>
       </c>
-      <c r="O103">
+      <c r="O103" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E4%B8%AD%E5%BF%83%E8%B7%AF%E9%A6%99%E6%82%A6%E9%87%8C_%E9%A6%99%E6%82%A6%E9%87%8C.html","查看证据(3项/9张)")</f>
-        <v/>
+        <v>查看证据(3项/9张)</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
@@ -12896,9 +12896,9 @@
 5.5: 回收箱及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O104">
+      <c r="O104" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%8D%97%E5%B1%B1%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E_%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E%E8%8A%B1%E5%9B%AD_%E4%B8%80%E6%9C%9F_.html","查看证据(5项/11张)")</f>
-        <v/>
+        <v>查看证据(5项/11张)</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -13021,9 +13021,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O105">
+      <c r="O105" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BB%BF%E6%B5%B7%E6%B9%BE_%E7%BB%BF%E6%B5%B7%E6%B9%BE.html","查看证据(5项/9张)")</f>
-        <v/>
+        <v>查看证据(5项/9张)</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -13167,9 +13167,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G2">
+      <c r="G2" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E9%87%91%E7%94%B0%E8%B7%AF2003_5%E5%8F%B7_%E9%87%91%E6%80%A1%E5%8D%8E%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="3">
@@ -13203,9 +13203,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G3">
+      <c r="G3" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E9%87%91%E7%94%B0%E8%B7%AF2003_5%E5%8F%B7_%E9%87%91%E6%80%A1%E5%8D%8E%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="4">
@@ -13239,9 +13239,9 @@
           <t>（2）投放口被封闭或遮挡(-2)（1处问题）； （4）厨余误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G4">
+      <c r="G4" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E9%87%91%E7%94%B0%E8%B7%AF2003_5%E5%8F%B7_%E9%87%91%E6%80%A1%E5%8D%8E%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="5">
@@ -13275,9 +13275,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G5">
+      <c r="G5" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E9%87%91%E7%94%B0%E8%B7%AF2003_5%E5%8F%B7_%E9%87%91%E6%80%A1%E5%8D%8E%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="6">
@@ -13311,9 +13311,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G6">
+      <c r="G6" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E9%87%91%E7%94%B0%E8%B7%AF2003_5%E5%8F%B7_%E9%87%91%E6%80%A1%E5%8D%8E%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="7">
@@ -13347,9 +13347,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G7">
+      <c r="G7" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E9%87%91%E7%94%B0%E8%B7%AF2003_5%E5%8F%B7_%E9%87%91%E6%80%A1%E5%8D%8E%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="8">
@@ -13383,9 +13383,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G8">
+      <c r="G8" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E9%87%91%E7%94%B0%E8%B7%AF2003_5%E5%8F%B7_%E9%87%91%E6%80%A1%E5%8D%8E%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="9">
@@ -13419,9 +13419,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G9">
+      <c r="G9" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E7%A6%8F%E6%B0%91%E8%B7%AF22_3%E5%8F%B7%E7%9A%87%E5%85%B4%E5%A4%A7%E5%8E%A6_%E7%9A%87%E5%85%B4%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="10">
@@ -13455,9 +13455,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G10">
+      <c r="G10" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E7%A6%8F%E6%B0%91%E8%B7%AF22_3%E5%8F%B7%E7%9A%87%E5%85%B4%E5%A4%A7%E5%8E%A6_%E7%9A%87%E5%85%B4%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="11">
@@ -13491,9 +13491,9 @@
           <t>（2）投放口被封闭或遮挡(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G11">
+      <c r="G11" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E7%A6%8F%E6%B0%91%E8%B7%AF22_3%E5%8F%B7%E7%9A%87%E5%85%B4%E5%A4%A7%E5%8E%A6_%E7%9A%87%E5%85%B4%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="12">
@@ -13527,9 +13527,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G12">
+      <c r="G12" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E7%A6%8F%E6%B0%91%E8%B7%AF22_3%E5%8F%B7%E7%9A%87%E5%85%B4%E5%A4%A7%E5%8E%A6_%E7%9A%87%E5%85%B4%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="13">
@@ -13563,9 +13563,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G13">
+      <c r="G13" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%9A%87%E5%B2%97%E5%85%AC%E5%9B%AD%E4%BA%8C%E8%A1%972%E5%8F%B7_%E7%9A%87%E5%BA%AD%E5%BD%A9%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="14">
@@ -13599,9 +13599,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G14">
+      <c r="G14" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%9A%87%E5%B2%97%E5%85%AC%E5%9B%AD%E4%BA%8C%E8%A1%972%E5%8F%B7_%E7%9A%87%E5%BA%AD%E5%BD%A9%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="15">
@@ -13635,9 +13635,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）； （3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G15">
+      <c r="G15" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%9A%87%E5%B2%97%E5%85%AC%E5%9B%AD%E4%BA%8C%E8%A1%972%E5%8F%B7_%E7%9A%87%E5%BA%AD%E5%BD%A9%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="16">
@@ -13671,9 +13671,9 @@
           <t>（3）内桶未开盖(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G16">
+      <c r="G16" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%9A%87%E5%B2%97%E5%85%AC%E5%9B%AD%E4%BA%8C%E8%A1%972%E5%8F%B7_%E7%9A%87%E5%BA%AD%E5%BD%A9%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="17">
@@ -13707,9 +13707,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G17">
+      <c r="G17" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%9A%87%E5%B2%97%E5%85%AC%E5%9B%AD%E4%BA%8C%E8%A1%972%E5%8F%B7_%E7%9A%87%E5%BA%AD%E5%BD%A9%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="18">
@@ -13743,9 +13743,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G18">
+      <c r="G18" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%9A%87%E5%B2%97%E5%85%AC%E5%9B%AD%E4%BA%8C%E8%A1%972%E5%8F%B7_%E7%9A%87%E5%BA%AD%E5%BD%A9%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="19">
@@ -13779,9 +13779,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G19">
+      <c r="G19" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%9A%87%E5%B2%97%E5%85%AC%E5%9B%AD%E4%BA%8C%E8%A1%972%E5%8F%B7_%E7%9A%87%E5%BA%AD%E5%BD%A9%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="20">
@@ -13815,9 +13815,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G20">
+      <c r="G20" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91_%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="21">
@@ -13851,9 +13851,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G21">
+      <c r="G21" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91_%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="22">
@@ -13887,9 +13887,9 @@
           <t>（2）车辆挡住投放点过道、投放口前堆放大件杂物，阻碍居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G22">
+      <c r="G22" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91_%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="23">
@@ -13923,9 +13923,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G23">
+      <c r="G23" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91_%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="24">
@@ -13959,9 +13959,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G24">
+      <c r="G24" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91_%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="25">
@@ -13995,9 +13995,9 @@
           <t>（2）未在黄线划定区域内(-2)（2处问题）； （3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G25">
+      <c r="G25" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91_%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="26">
@@ -14031,9 +14031,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）； （5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G26">
+      <c r="G26" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91_%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="27">
@@ -14067,9 +14067,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G27">
+      <c r="G27" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91_%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="28">
@@ -14103,9 +14103,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G28">
+      <c r="G28" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91_%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="29">
@@ -14139,9 +14139,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）； （4）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G29">
+      <c r="G29" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91_%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="30">
@@ -14175,9 +14175,9 @@
           <t>（3）其他问题(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G30">
+      <c r="G30" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91_%E5%BC%A0%E5%B1%8B%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="31">
@@ -14211,9 +14211,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G31">
+      <c r="G31" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%87%A4%E5%87%B0%E8%A1%97%E9%81%93%E5%A1%98%E5%AE%81%E8%8B%91_%E5%A1%98%E5%AE%81%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="32">
@@ -14247,9 +14247,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G32">
+      <c r="G32" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%87%A4%E5%87%B0%E8%A1%97%E9%81%93%E5%A1%98%E5%AE%81%E8%8B%91_%E5%A1%98%E5%AE%81%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="33">
@@ -14283,9 +14283,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G33">
+      <c r="G33" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA_%E8%88%AA%E5%9F%8E%E8%A1%97%E9%81%93%E9%BB%84%E7%94%B0%E7%A4%BE%E5%8C%BA%E5%88%A9%E8%BE%BE%E6%97%B6%E8%B7%AF_%E9%BB%84%E7%94%B0%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="34">
@@ -14319,9 +14319,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G34">
+      <c r="G34" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA_%E8%88%AA%E5%9F%8E%E8%A1%97%E9%81%93%E9%BB%84%E7%94%B0%E7%A4%BE%E5%8C%BA%E5%88%A9%E8%BE%BE%E6%97%B6%E8%B7%AF_%E9%BB%84%E7%94%B0%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="35">
@@ -14355,9 +14355,9 @@
           <t>（2）未使用(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G35">
+      <c r="G35" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA_%E8%88%AA%E5%9F%8E%E8%A1%97%E9%81%93%E9%BB%84%E7%94%B0%E7%A4%BE%E5%8C%BA%E5%88%A9%E8%BE%BE%E6%97%B6%E8%B7%AF_%E9%BB%84%E7%94%B0%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="36">
@@ -14391,9 +14391,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（2处问题）</t>
         </is>
       </c>
-      <c r="G36">
+      <c r="G36" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E8%88%AA%E5%9F%8E%E8%A1%97%E9%81%93%E5%88%A9%E9%94%A6%E7%A4%BE%E5%8C%BA%E5%A4%A9%E7%A6%8F%E5%8D%8E%E5%BA%9CA4_101_%E5%B7%A7%E6%89%8B%E5%8E%A8%E5%A8%98.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="37">
@@ -14427,9 +14427,9 @@
           <t>（2）分类设施损坏或摆放不整齐，内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G37">
+      <c r="G37" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E8%88%AA%E5%9F%8E%E8%A1%97%E9%81%93%E5%88%A9%E9%94%A6%E7%A4%BE%E5%8C%BA%E5%A4%A9%E7%A6%8F%E5%8D%8E%E5%BA%9CA4_101_%E5%B7%A7%E6%89%8B%E5%8E%A8%E5%A8%98.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="38">
@@ -14463,9 +14463,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G38">
+      <c r="G38" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA107%E5%9B%BD%E9%81%93%E4%B8%8E%E5%87%AF%E6%88%90%E4%B8%80%E8%B7%AF%E4%BA%A4%E5%8F%89%E5%8F%A3%E5%A4%A9%E7%A6%8F%E5%8D%8E%E5%BA%9C_%E5%A4%A9%E7%A6%8F%E5%8D%8E%E5%BA%9C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="39">
@@ -14499,9 +14499,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G39">
+      <c r="G39" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA107%E5%9B%BD%E9%81%93%E4%B8%8E%E5%87%AF%E6%88%90%E4%B8%80%E8%B7%AF%E4%BA%A4%E5%8F%89%E5%8F%A3%E5%A4%A9%E7%A6%8F%E5%8D%8E%E5%BA%9C_%E5%A4%A9%E7%A6%8F%E5%8D%8E%E5%BA%9C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="40">
@@ -14535,9 +14535,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G40">
+      <c r="G40" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA107%E5%9B%BD%E9%81%93%E4%B8%8E%E5%87%AF%E6%88%90%E4%B8%80%E8%B7%AF%E4%BA%A4%E5%8F%89%E5%8F%A3%E5%A4%A9%E7%A6%8F%E5%8D%8E%E5%BA%9C_%E5%A4%A9%E7%A6%8F%E5%8D%8E%E5%BA%9C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="41">
@@ -14571,9 +14571,9 @@
           <t>（2）未成组摆放两分类收集容器(-3)</t>
         </is>
       </c>
-      <c r="G41">
+      <c r="G41" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E9%95%87%E6%B2%99%E6%B5%A6%E4%BA%8C%E6%9D%91%E5%B9%BF%E8%BF%9B%E8%B7%AF24%E5%8F%B7_%E4%BA%9A%E5%8D%8E%E5%B7%A5%E4%B8%9A%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="42">
@@ -14607,9 +14607,9 @@
           <t>（2）收集容器缺失(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G42">
+      <c r="G42" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E9%95%87%E6%B2%99%E6%B5%A6%E4%BA%8C%E6%9D%91%E5%B9%BF%E8%BF%9B%E8%B7%AF24%E5%8F%B7_%E4%BA%9A%E5%8D%8E%E5%B7%A5%E4%B8%9A%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="43">
@@ -14643,9 +14643,9 @@
           <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G43">
+      <c r="G43" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E9%95%87%E6%B2%99%E6%B5%A6%E4%BA%8C%E6%9D%91%E5%B9%BF%E8%BF%9B%E8%B7%AF24%E5%8F%B7_%E4%BA%9A%E5%8D%8E%E5%B7%A5%E4%B8%9A%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="44">
@@ -14679,9 +14679,9 @@
           <t>（2）收集容器缺失(-6)（1处问题）</t>
         </is>
       </c>
-      <c r="G44">
+      <c r="G44" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E8%89%BA%E5%B1%95%E4%B8%80%E8%B7%AF%E8%89%BA%E5%B1%95%E5%B0%8F%E9%95%871%E5%8F%B7%E6%A5%BCT1_001_004_%E9%BA%A6%E5%BD%93%E5%8A%B3_%E6%BB%A1%E7%BA%B7%E5%A4%A9%E5%9C%B0_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="45">
@@ -14715,9 +14715,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（3处问题）</t>
         </is>
       </c>
-      <c r="G45">
+      <c r="G45" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E8%89%BA%E5%B1%95%E4%B8%80%E8%B7%AF%E8%89%BA%E5%B1%95%E5%B0%8F%E9%95%871%E5%8F%B7%E6%A5%BCT1_001_004_%E9%BA%A6%E5%BD%93%E5%8A%B3_%E6%BB%A1%E7%BA%B7%E5%A4%A9%E5%9C%B0_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="46">
@@ -14751,9 +14751,9 @@
           <t>（2）未设置光盘行动、节约粮食等宣传海报或温馨提示等(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G46">
+      <c r="G46" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E8%89%BA%E5%B1%95%E4%B8%80%E8%B7%AF%E8%89%BA%E5%B1%95%E5%B0%8F%E9%95%871%E5%8F%B7%E6%A5%BCT1_001_004_%E9%BA%A6%E5%BD%93%E5%8A%B3_%E6%BB%A1%E7%BA%B7%E5%A4%A9%E5%9C%B0_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="47">
@@ -14787,9 +14787,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G47">
+      <c r="G47" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E5%85%B4%E5%AE%87%E8%B7%AF%E4%B8%8E%E7%91%9E%E5%BA%B7%E8%B7%AF%E4%BA%A4%E5%8F%89%E5%8F%A3%E4%B8%9C%E5%8D%97%E9%87%91%E8%BE%BE%E8%8A%B1%E5%9B%AD_%E9%87%91%E8%BE%BE%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="48">
@@ -14823,9 +14823,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G48">
+      <c r="G48" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E5%85%B4%E5%AE%87%E8%B7%AF%E4%B8%8E%E7%91%9E%E5%BA%B7%E8%B7%AF%E4%BA%A4%E5%8F%89%E5%8F%A3%E4%B8%9C%E5%8D%97%E9%87%91%E8%BE%BE%E8%8A%B1%E5%9B%AD_%E9%87%91%E8%BE%BE%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="49">
@@ -14859,9 +14859,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G49">
+      <c r="G49" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E5%85%B4%E5%AE%87%E8%B7%AF%E4%B8%8E%E7%91%9E%E5%BA%B7%E8%B7%AF%E4%BA%A4%E5%8F%89%E5%8F%A3%E4%B8%9C%E5%8D%97%E9%87%91%E8%BE%BE%E8%8A%B1%E5%9B%AD_%E9%87%91%E8%BE%BE%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="50">
@@ -14895,9 +14895,9 @@
           <t>（2）收集容器缺失(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G50">
+      <c r="G50" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%B2%99%E6%B5%A6%E7%A4%BE%E5%8C%BA%E8%89%BA%E5%B1%95%E5%9B%9B%E8%B7%AF8%E5%8F%B7102%E5%8F%B7_%E6%BB%A1%E4%BA%AC%E5%8D%8E%E5%85%AC%E5%AF%93%E9%85%92%E5%BA%97.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="51">
@@ -14931,9 +14931,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（2处问题）</t>
         </is>
       </c>
-      <c r="G51">
+      <c r="G51" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%B2%99%E6%B5%A6%E7%A4%BE%E5%8C%BA%E8%89%BA%E5%B1%95%E5%9B%9B%E8%B7%AF8%E5%8F%B7102%E5%8F%B7_%E6%BB%A1%E4%BA%AC%E5%8D%8E%E5%85%AC%E5%AF%93%E9%85%92%E5%BA%97.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="52">
@@ -14967,9 +14967,9 @@
           <t>（2）未成组摆放两分类收集容器；(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G52">
+      <c r="G52" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA_%E8%89%BA%E5%B1%95%E5%9B%9B%E8%B7%AF%E4%B8%8E%E6%9D%BE%E7%A6%8F%E5%A4%A7%E9%81%93%E8%BE%85%E8%B7%AF%E4%BA%A4%E5%8F%89%E5%8F%A3%E4%B8%9C%E5%8D%9780%E7%B1%B3_%E6%BB%A1%E4%BA%AC%E5%8D%8E%E7%9B%88%E7%A1%95.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="53">
@@ -15003,9 +15003,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（3处问题）</t>
         </is>
       </c>
-      <c r="G53">
+      <c r="G53" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA_%E8%89%BA%E5%B1%95%E5%9B%9B%E8%B7%AF%E4%B8%8E%E6%9D%BE%E7%A6%8F%E5%A4%A7%E9%81%93%E8%BE%85%E8%B7%AF%E4%BA%A4%E5%8F%89%E5%8F%A3%E4%B8%9C%E5%8D%9780%E7%B1%B3_%E6%BB%A1%E4%BA%AC%E5%8D%8E%E7%9B%88%E7%A1%95.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="54">
@@ -15039,9 +15039,9 @@
           <t>（2）其他问题说明（备注描述）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G54">
+      <c r="G54" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA_%E8%89%BA%E5%B1%95%E5%9B%9B%E8%B7%AF%E4%B8%8E%E6%9D%BE%E7%A6%8F%E5%A4%A7%E9%81%93%E8%BE%85%E8%B7%AF%E4%BA%A4%E5%8F%89%E5%8F%A3%E4%B8%9C%E5%8D%9780%E7%B1%B3_%E6%BB%A1%E4%BA%AC%E5%8D%8E%E7%9B%88%E7%A1%95.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="55">
@@ -15075,9 +15075,9 @@
           <t>（2）未张贴节约用纸、双面打印宣传标语(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G55">
+      <c r="G55" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA_%E8%89%BA%E5%B1%95%E5%9B%9B%E8%B7%AF%E4%B8%8E%E6%9D%BE%E7%A6%8F%E5%A4%A7%E9%81%93%E8%BE%85%E8%B7%AF%E4%BA%A4%E5%8F%89%E5%8F%A3%E4%B8%9C%E5%8D%9780%E7%B1%B3_%E6%BB%A1%E4%BA%AC%E5%8D%8E%E7%9B%88%E7%A1%95.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="56">
@@ -15111,9 +15111,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（2处问题）</t>
         </is>
       </c>
-      <c r="G56">
+      <c r="G56" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E5%88%A9%E8%BE%BE%E8%B7%AF3%E8%BE%BE%E5%88%A9%E8%8A%B1%E5%9B%AD_%E8%BE%BE%E5%88%A9%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="57">
@@ -15147,9 +15147,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G57">
+      <c r="G57" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E5%88%A9%E8%BE%BE%E8%B7%AF3%E8%BE%BE%E5%88%A9%E8%8A%B1%E5%9B%AD_%E8%BE%BE%E5%88%A9%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="58">
@@ -15183,9 +15183,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G58">
+      <c r="G58" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E5%88%A9%E8%BE%BE%E8%B7%AF3%E8%BE%BE%E5%88%A9%E8%8A%B1%E5%9B%AD_%E8%BE%BE%E5%88%A9%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="59">
@@ -15219,9 +15219,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G59">
+      <c r="G59" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E5%88%A9%E8%BE%BE%E8%B7%AF3%E8%BE%BE%E5%88%A9%E8%8A%B1%E5%9B%AD_%E8%BE%BE%E5%88%A9%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="60">
@@ -15255,9 +15255,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G60">
+      <c r="G60" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E5%88%A9%E8%BE%BE%E8%B7%AF3%E8%BE%BE%E5%88%A9%E8%8A%B1%E5%9B%AD_%E8%BE%BE%E5%88%A9%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="61">
@@ -15291,9 +15291,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G61">
+      <c r="G61" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E6%B5%A6%E7%A4%BE%E5%8C%BA%E6%B0%B8%E5%85%B4%E8%8A%B1%E5%9B%AD_%E6%B0%B8%E5%85%B4%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="62">
@@ -15327,9 +15327,9 @@
           <t>（3）内桶未开盖(-2)（1处问题）； （4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G62">
+      <c r="G62" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E6%B5%A6%E7%A4%BE%E5%8C%BA%E6%B0%B8%E5%85%B4%E8%8A%B1%E5%9B%AD_%E6%B0%B8%E5%85%B4%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="63">
@@ -15363,9 +15363,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G63">
+      <c r="G63" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E5%AE%B6%E8%B1%AA%E5%B1%85_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA%E5%BA%97_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA_%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="64">
@@ -15399,9 +15399,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G64">
+      <c r="G64" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E5%AE%B6%E8%B1%AA%E5%B1%85_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA%E5%BA%97_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA_%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="65">
@@ -15435,9 +15435,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G65">
+      <c r="G65" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E5%AE%B6%E8%B1%AA%E5%B1%85_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA%E5%BA%97_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA_%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="66">
@@ -15471,9 +15471,9 @@
           <t>（4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G66">
+      <c r="G66" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E5%AE%B6%E8%B1%AA%E5%B1%85_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA%E5%BA%97_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA_%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="67">
@@ -15507,9 +15507,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G67">
+      <c r="G67" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E5%AE%B6%E8%B1%AA%E5%B1%85_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA%E5%BA%97_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA_%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="68">
@@ -15543,9 +15543,9 @@
           <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G68">
+      <c r="G68" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E5%AE%B6%E8%B1%AA%E5%B1%85_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA%E5%BA%97_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA_%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="69">
@@ -15579,9 +15579,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G69">
+      <c r="G69" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E5%AE%B6%E8%B1%AA%E5%B1%85_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA%E5%BA%97_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA_%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="70">
@@ -15615,9 +15615,9 @@
           <t>（7）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G70">
+      <c r="G70" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E5%AE%B6%E8%B1%AA%E5%B1%85_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA%E5%BA%97_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA_%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="71">
@@ -15651,9 +15651,9 @@
           <t>（2）存在超过3家(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G71">
+      <c r="G71" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E5%AE%B6%E8%B1%AA%E5%B1%85_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA%E5%BA%97_%E6%B2%99%E4%BA%8C%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA_%E6%B2%B3%E6%BB%A8%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="72">
@@ -15687,9 +15687,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G72">
+      <c r="G72" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%B2%99%E6%B1%9F%E8%B7%AF116%E5%8F%B7%E6%B2%99%E6%B5%A6%E4%BA%8C%E6%9D%91%E5%BE%A1%E6%99%AF%E5%9F%8E_%E5%BE%A1%E6%99%AF%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="73">
@@ -15723,9 +15723,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G73">
+      <c r="G73" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%B2%99%E6%B1%9F%E8%B7%AF116%E5%8F%B7%E6%B2%99%E6%B5%A6%E4%BA%8C%E6%9D%91%E5%BE%A1%E6%99%AF%E5%9F%8E_%E5%BE%A1%E6%99%AF%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="74">
@@ -15759,9 +15759,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G74">
+      <c r="G74" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%B2%99%E6%B1%9F%E8%B7%AF116%E5%8F%B7%E6%B2%99%E6%B5%A6%E4%BA%8C%E6%9D%91%E5%BE%A1%E6%99%AF%E5%9F%8E_%E5%BE%A1%E6%99%AF%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="75">
@@ -15795,9 +15795,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G75">
+      <c r="G75" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%B2%99%E6%B1%9F%E8%B7%AF116%E5%8F%B7%E6%B2%99%E6%B5%A6%E4%BA%8C%E6%9D%91%E5%BE%A1%E6%99%AF%E5%9F%8E_%E5%BE%A1%E6%99%AF%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="76">
@@ -15831,9 +15831,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）； （5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G76">
+      <c r="G76" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%B2%99%E6%B1%9F%E8%B7%AF116%E5%8F%B7%E6%B2%99%E6%B5%A6%E4%BA%8C%E6%9D%91%E5%BE%A1%E6%99%AF%E5%9F%8E_%E5%BE%A1%E6%99%AF%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="77">
@@ -15867,9 +15867,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G77">
+      <c r="G77" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%B2%99%E6%B1%9F%E8%B7%AF116%E5%8F%B7%E6%B2%99%E6%B5%A6%E4%BA%8C%E6%9D%91%E5%BE%A1%E6%99%AF%E5%9F%8E_%E5%BE%A1%E6%99%AF%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="78">
@@ -15903,9 +15903,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）； （4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）； （7）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G78">
+      <c r="G78" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%B2%99%E6%B1%9F%E8%B7%AF116%E5%8F%B7%E6%B2%99%E6%B5%A6%E4%BA%8C%E6%9D%91%E5%BE%A1%E6%99%AF%E5%9F%8E_%E5%BE%A1%E6%99%AF%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="79">
@@ -15939,9 +15939,9 @@
           <t>（2）未规范张贴垃圾分类宣传海报（海报缺失、内容错误/未更新等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G79">
+      <c r="G79" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%B2%99%E6%B1%9F%E8%B7%AF116%E5%8F%B7%E6%B2%99%E6%B5%A6%E4%BA%8C%E6%9D%91%E5%BE%A1%E6%99%AF%E5%9F%8E_%E5%BE%A1%E6%99%AF%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="80">
@@ -15975,9 +15975,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G80">
+      <c r="G80" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%9D%BE%E5%9B%AD%E5%8C%97%E8%A1%9738%E5%8F%B7_%E6%96%B9%E8%99%B9%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="81">
@@ -16011,9 +16011,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G81">
+      <c r="G81" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%9D%BE%E5%9B%AD%E5%8C%97%E8%A1%9738%E5%8F%B7_%E6%96%B9%E8%99%B9%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="82">
@@ -16047,9 +16047,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G82">
+      <c r="G82" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%9D%BE%E5%9B%AD%E5%8C%97%E8%A1%9738%E5%8F%B7_%E6%96%B9%E8%99%B9%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="83">
@@ -16083,9 +16083,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G83">
+      <c r="G83" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E6%9D%BE%E5%9B%AD%E5%8C%97%E8%A1%9760%E5%8F%B7_%E5%85%AC%E5%AE%89%E5%B1%80%E6%8E%A5%E5%BE%85%E7%AB%99%E5%AE%BF%E8%88%8D.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="84">
@@ -16119,9 +16119,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G84">
+      <c r="G84" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E6%9D%BE%E5%9B%AD%E5%8C%97%E8%A1%9760%E5%8F%B7_%E5%85%AC%E5%AE%89%E5%B1%80%E6%8E%A5%E5%BE%85%E7%AB%99%E5%AE%BF%E8%88%8D.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="85">
@@ -16155,9 +16155,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G85">
+      <c r="G85" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF3097_%E6%B4%AA%E6%B6%9B%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="86">
@@ -16191,9 +16191,9 @@
           <t>（4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G86">
+      <c r="G86" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF3097_%E6%B4%AA%E6%B6%9B%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="87">
@@ -16227,9 +16227,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G87">
+      <c r="G87" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF3097_%E6%B4%AA%E6%B6%9B%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="88">
@@ -16263,9 +16263,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G88">
+      <c r="G88" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF3073%E5%8F%B7_%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF3073%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="89">
@@ -16299,9 +16299,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G89">
+      <c r="G89" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF3073%E5%8F%B7_%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF3073%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="90">
@@ -16335,9 +16335,9 @@
           <t>（2）主动向消费者提供客房一次性日用品(-10)（1处问题）</t>
         </is>
       </c>
-      <c r="G90">
+      <c r="G90" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF%E4%B8%AD%E8%88%AA%E5%87%AF%E7%89%B9%E5%85%AC%E5%AF%93%E5%9B%9B%E6%A5%BC_%E9%BA%A6%E5%90%89%E9%85%92%E5%BA%97.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="91">
@@ -16371,9 +16371,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G91">
+      <c r="G91" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF3005%E5%8F%B7_%E4%B8%AD%E5%8D%97%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="92">
@@ -16407,9 +16407,9 @@
           <t>（2）投放口被封闭或遮挡(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G92">
+      <c r="G92" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF3005%E5%8F%B7_%E4%B8%AD%E5%8D%97%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="93">
@@ -16443,9 +16443,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G93">
+      <c r="G93" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%AE%9D%E5%AE%89%E5%8D%97%E8%B7%AF3005%E5%8F%B7_%E4%B8%AD%E5%8D%97%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="94">
@@ -16479,9 +16479,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G94">
+      <c r="G94" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BA%A2%E6%A1%82%E8%B7%AF2020_%E9%87%91%E4%BC%97%E7%BB%8F%E5%85%B8%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="95">
@@ -16515,9 +16515,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G95">
+      <c r="G95" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BA%A2%E6%A1%82%E8%B7%AF2020_%E9%87%91%E4%BC%97%E7%BB%8F%E5%85%B8%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="96">
@@ -16551,9 +16551,9 @@
           <t>（2）存在超过3家(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G96">
+      <c r="G96" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BA%A2%E6%A1%82%E8%B7%AF2020_%E9%87%91%E4%BC%97%E7%BB%8F%E5%85%B8%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="97">
@@ -16587,9 +16587,9 @@
           <t>周边环境脏乱(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G97">
+      <c r="G97" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BA%A2%E6%A1%82%E8%B7%AF2020_%E9%87%91%E4%BC%97%E7%BB%8F%E5%85%B8%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="98">
@@ -16623,9 +16623,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G98">
+      <c r="G98" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E8%A7%82%E8%B7%AF45%E5%8F%B7%E5%A4%A9%E7%8E%91%E5%85%AC%E9%A6%86_%E5%A4%A9%E7%8E%91%E5%85%AC%E9%A6%86.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="99">
@@ -16659,9 +16659,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G99">
+      <c r="G99" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E8%A7%82%E8%B7%AF45%E5%8F%B7%E5%A4%A9%E7%8E%91%E5%85%AC%E9%A6%86_%E5%A4%A9%E7%8E%91%E5%85%AC%E9%A6%86.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="100">
@@ -16695,9 +16695,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（4处问题）</t>
         </is>
       </c>
-      <c r="G100">
+      <c r="G100" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E7%A5%A5%E5%88%A9%E8%B7%AF54%E5%8F%B7%E5%AE%9D%E6%B9%96%E6%96%B0%E6%9D%91_%E6%96%B0%E7%A2%91%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="101">
@@ -16731,9 +16731,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G101">
+      <c r="G101" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E7%A5%A5%E5%88%A9%E8%B7%AF54%E5%8F%B7%E5%AE%9D%E6%B9%96%E6%96%B0%E6%9D%91_%E6%96%B0%E7%A2%91%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="102">
@@ -16767,9 +16767,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G102">
+      <c r="G102" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E7%A5%A5%E5%88%A9%E8%B7%AF54%E5%8F%B7%E5%AE%9D%E6%B9%96%E6%96%B0%E6%9D%91_%E6%96%B0%E7%A2%91%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="103">
@@ -16803,9 +16803,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G103">
+      <c r="G103" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E7%A5%A5%E5%88%A9%E8%B7%AF54%E5%8F%B7%E5%AE%9D%E6%B9%96%E6%96%B0%E6%9D%91_%E6%96%B0%E7%A2%91%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="104">
@@ -16839,9 +16839,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G104">
+      <c r="G104" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA_%E5%A4%A7%E5%94%90%E6%97%B6%E4%BB%A3.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="105">
@@ -16875,9 +16875,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G105">
+      <c r="G105" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E9%BE%99%E5%B2%97%E5%8C%BA%E4%B8%87%E7%A7%91%E5%A4%A9%E8%AA%89%E4%B8%80_%E4%BA%8C%E6%9C%9F_%E4%B8%87%E7%A7%91%E5%A4%A9%E8%AA%89%E4%B8%80_%E4%BA%8C%E6%9C%9F.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="106">
@@ -16911,9 +16911,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G106">
+      <c r="G106" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E9%BE%99%E5%B2%97%E5%8C%BA%E4%B8%87%E7%A7%91%E5%A4%A9%E8%AA%89%E4%B8%80_%E4%BA%8C%E6%9C%9F_%E4%B8%87%E7%A7%91%E5%A4%A9%E8%AA%89%E4%B8%80_%E4%BA%8C%E6%9C%9F.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="107">
@@ -16947,9 +16947,9 @@
           <t>（2）收集容器缺失；(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G107">
+      <c r="G107" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E4%B8%87%E7%A7%91%E5%A4%A7%E5%8E%A6_%E4%B8%87%E7%A7%91%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="108">
@@ -16983,9 +16983,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G108">
+      <c r="G108" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E5%9F%8E%E8%A1%97%E9%81%93%E5%90%89%E7%A5%A5%E7%A4%BE%E5%8C%BA%E9%BE%99%E7%BF%94%E5%A4%A7%E9%81%938014%E5%8F%B7_%E9%BA%A6%E5%BD%93%E5%8A%B3.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="109">
@@ -17019,9 +17019,9 @@
           <t>（2）责任公示牌缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G109">
+      <c r="G109" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%BD%99%E5%B2%AD%E4%B8%9C%E8%B7%AF11%E5%8F%B7_%E4%BD%99%E5%B2%AD%E5%B1%B1%E5%BA%84.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="110">
@@ -17055,9 +17055,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G110">
+      <c r="G110" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%BD%99%E5%B2%AD%E4%B8%9C%E8%B7%AF11%E5%8F%B7_%E4%BD%99%E5%B2%AD%E5%B1%B1%E5%BA%84.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="111">
@@ -17091,9 +17091,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G111">
+      <c r="G111" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%90%89%E7%A5%A5%E8%B7%AF95%E5%8F%B7_%E5%90%89%E7%A5%A5%E6%9D%A5%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="112">
@@ -17127,9 +17127,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G112">
+      <c r="G112" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%90%89%E7%A5%A5%E8%B7%AF95%E5%8F%B7_%E5%90%89%E7%A5%A5%E6%9D%A5%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="113">
@@ -17163,9 +17163,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G113">
+      <c r="G113" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E6%96%B0%E6%A1%A5%E8%A5%BF%E4%B8%80%E5%B7%B715%E5%8F%B7_%E5%B2%97%E8%B4%9D%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="114">
@@ -17199,9 +17199,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G114">
+      <c r="G114" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E6%96%B0%E6%A1%A5%E8%A5%BF%E4%B8%80%E5%B7%B715%E5%8F%B7_%E5%B2%97%E8%B4%9D%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="115">
@@ -17235,9 +17235,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G115">
+      <c r="G115" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E7%BF%94%E5%A4%A7%E9%81%936132%E5%8F%B7_%E4%B8%9C%E9%83%BD%E8%8A%B1%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="116">
@@ -17271,9 +17271,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G116">
+      <c r="G116" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E7%BF%94%E5%A4%A7%E9%81%936132%E5%8F%B7_%E4%B8%9C%E9%83%BD%E8%8A%B1%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="117">
@@ -17307,9 +17307,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G117">
+      <c r="G117" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E7%BF%94%E5%A4%A7%E9%81%936132%E5%8F%B7_%E4%B8%9C%E9%83%BD%E8%8A%B1%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="118">
@@ -17343,9 +17343,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G118">
+      <c r="G118" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E6%80%A1%E7%BF%A0%E8%B7%AF202%E5%8F%B7_%E4%BF%9D%E5%88%A9%E4%B8%8A%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="119">
@@ -17379,9 +17379,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G119">
+      <c r="G119" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E6%80%A1%E7%BF%A0%E8%B7%AF202%E5%8F%B7_%E4%BF%9D%E5%88%A9%E4%B8%8A%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="120">
@@ -17415,9 +17415,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G120">
+      <c r="G120" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E6%80%A1%E7%BF%A0%E8%B7%AF202%E5%8F%B7_%E4%BF%9D%E5%88%A9%E4%B8%8A%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="121">
@@ -17451,9 +17451,9 @@
           <t>（2）分类收集容器缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G121">
+      <c r="G121" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E5%A1%98%E5%B0%BE%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%80%E5%8C%BA%E5%B7%A5%E4%B8%9A%E5%A4%A7%E9%81%936_1_%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%80%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="122">
@@ -17487,9 +17487,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（4处问题）</t>
         </is>
       </c>
-      <c r="G122">
+      <c r="G122" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E5%A1%98%E5%B0%BE%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%80%E5%8C%BA%E5%B7%A5%E4%B8%9A%E5%A4%A7%E9%81%936_1_%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%80%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="123">
@@ -17523,9 +17523,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G123">
+      <c r="G123" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E5%A1%98%E5%B0%BE%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%80%E5%8C%BA%E5%B7%A5%E4%B8%9A%E5%A4%A7%E9%81%936_1_%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%80%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="124">
@@ -17559,9 +17559,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G124">
+      <c r="G124" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E5%A1%98%E5%B0%BE%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%80%E5%8C%BA%E5%B7%A5%E4%B8%9A%E5%A4%A7%E9%81%936_1_%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%80%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="125">
@@ -17595,9 +17595,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G125">
+      <c r="G125" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B8%83%E6%B2%99%E8%B7%AF156%E5%8F%B7_%E7%A5%A5%E4%BA%91%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="126">
@@ -17631,9 +17631,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G126">
+      <c r="G126" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E6%B2%99%E8%B7%AF172%E5%8F%B7_%E9%A2%82%E9%9B%85%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="127">
@@ -17667,9 +17667,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G127">
+      <c r="G127" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%A4%A7%E9%81%93_%E5%B8%83%E5%90%89%E6%AE%B5_2578%E5%8F%B7_%E6%A1%82%E8%8A%B3%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="128">
@@ -17703,9 +17703,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G128">
+      <c r="G128" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%A4%A7%E9%81%93_%E5%B8%83%E5%90%89%E6%AE%B5_2578%E5%8F%B7_%E6%A1%82%E8%8A%B3%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="129">
@@ -17739,9 +17739,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G129">
+      <c r="G129" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%A4%A7%E9%81%93_%E5%B8%83%E5%90%89%E6%AE%B5_2578%E5%8F%B7_%E6%A1%82%E8%8A%B3%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="130">
@@ -17775,9 +17775,9 @@
           <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G130">
+      <c r="G130" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%A4%A7%E9%81%93_%E5%B8%83%E5%90%89%E6%AE%B5_2578%E5%8F%B7_%E6%A1%82%E8%8A%B3%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="131">
@@ -17811,9 +17811,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（5处问题）</t>
         </is>
       </c>
-      <c r="G131">
+      <c r="G131" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%A4%A7%E9%81%93_%E5%B8%83%E5%90%89%E6%AE%B5_2582%E5%8F%B7_%E4%B8%AD%E5%85%86%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="132">
@@ -17847,9 +17847,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G132">
+      <c r="G132" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%A4%A7%E9%81%93_%E5%B8%83%E5%90%89%E6%AE%B5_2582%E5%8F%B7_%E4%B8%AD%E5%85%86%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="133">
@@ -17883,9 +17883,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G133">
+      <c r="G133" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%A4%A7%E9%81%93_%E5%B8%83%E5%90%89%E6%AE%B5_2582%E5%8F%B7_%E4%B8%AD%E5%85%86%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="134">
@@ -17919,9 +17919,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G134">
+      <c r="G134" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%BA%B7%E6%A1%A5%E8%8A%B1%E5%9B%AD%E4%BA%8C%E6%9C%9F_%E4%B8%AD%E5%9F%8E%E5%BA%B7%E6%A1%A5%E8%8A%B1%E5%9B%AD%E8%A5%BF%E5%8C%97100%E7%B1%B3_%E5%BA%B7%E6%A1%A5%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="135">
@@ -17955,9 +17955,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G135">
+      <c r="G135" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%BA%B7%E6%A1%A5%E8%8A%B1%E5%9B%AD%E4%BA%8C%E6%9C%9F_%E4%B8%AD%E5%9F%8E%E5%BA%B7%E6%A1%A5%E8%8A%B1%E5%9B%AD%E8%A5%BF%E5%8C%97100%E7%B1%B3_%E5%BA%B7%E6%A1%A5%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="136">
@@ -17991,9 +17991,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G136">
+      <c r="G136" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF2%E5%8F%B7_%E9%95%BF%E5%9F%8E%E4%B8%80%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="137">
@@ -18027,9 +18027,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G137">
+      <c r="G137" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF2%E5%8F%B7_%E9%95%BF%E5%9F%8E%E4%B8%80%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="138">
@@ -18063,9 +18063,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G138">
+      <c r="G138" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF2%E5%8F%B7_%E9%95%BF%E5%9F%8E%E4%B8%80%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="139">
@@ -18099,9 +18099,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G139">
+      <c r="G139" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF11%E5%8F%B7_%E9%95%BF%E5%AE%89%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="140">
@@ -18135,9 +18135,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G140">
+      <c r="G140" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF11%E5%8F%B7_%E9%95%BF%E5%AE%89%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="141">
@@ -18171,9 +18171,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G141">
+      <c r="G141" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF11%E5%8F%B7_%E9%95%BF%E5%AE%89%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="142">
@@ -18207,9 +18207,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G142">
+      <c r="G142" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%9B%AD%E5%B2%AD%E8%A1%97%E9%81%93%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF8%E5%8F%B7_%E9%95%BF%E5%9F%8E%E4%BA%8C%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="143">
@@ -18243,9 +18243,9 @@
           <t>（1）存在问题(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G143">
+      <c r="G143" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%9B%AD%E5%B2%AD%E8%A1%97%E9%81%93%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF8%E5%8F%B7_%E9%95%BF%E5%9F%8E%E4%BA%8C%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="144">
@@ -18279,9 +18279,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G144">
+      <c r="G144" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF10%E5%8F%B7_%E9%95%BF%E6%B3%B0%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="145">
@@ -18315,9 +18315,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G145">
+      <c r="G145" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF10%E5%8F%B7_%E9%95%BF%E6%B3%B0%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="146">
@@ -18351,9 +18351,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（4处问题）</t>
         </is>
       </c>
-      <c r="G146">
+      <c r="G146" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E4%BA%94%E8%B7%AF3%E5%8F%B7_%E6%A0%B8%E7%94%B5%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="147">
@@ -18387,9 +18387,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（4处问题）</t>
         </is>
       </c>
-      <c r="G147">
+      <c r="G147" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E4%BA%94%E8%B7%AF3%E5%8F%B7_%E6%A0%B8%E7%94%B5%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="148">
@@ -18423,9 +18423,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G148">
+      <c r="G148" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E4%BA%94%E8%B7%AF3%E5%8F%B7_%E6%A0%B8%E7%94%B5%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="149">
@@ -18459,9 +18459,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G149">
+      <c r="G149" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E4%BA%94%E8%B7%AF3%E5%8F%B7_%E6%A0%B8%E7%94%B5%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="150">
@@ -18495,9 +18495,9 @@
           <t>（2）收集容器缺失(-6)（1处问题）</t>
         </is>
       </c>
-      <c r="G150">
+      <c r="G150" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E4%BA%94%E8%B7%AF8%E5%8F%B7_%E8%80%81%E7%A2%97%E4%BC%9A_%E7%99%BE%E8%8A%B1%E5%BA%97_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="151">
@@ -18531,9 +18531,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G151">
+      <c r="G151" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E4%BA%94%E8%B7%AF8%E5%8F%B7_%E8%80%81%E7%A2%97%E4%BC%9A_%E7%99%BE%E8%8A%B1%E5%BA%97_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="152">
@@ -18567,9 +18567,9 @@
           <t>（2）未设置光盘行动、节约粮食等宣传海报或温馨提示等(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G152">
+      <c r="G152" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E4%BA%94%E8%B7%AF8%E5%8F%B7_%E8%80%81%E7%A2%97%E4%BC%9A_%E7%99%BE%E8%8A%B1%E5%BA%97_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="153">
@@ -18603,9 +18603,9 @@
           <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-4)（1处问题）</t>
         </is>
       </c>
-      <c r="G153">
+      <c r="G153" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%99%BE%E8%8A%B1%E5%9B%9B%E8%B7%AF_%E7%99%BD%E6%B2%99%E5%B2%AD%E7%A4%BE%E5%8C%BA%E5%85%AC%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="154">
@@ -18639,9 +18639,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G154">
+      <c r="G154" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%A2%85%E9%BE%99%E5%A4%A7%E9%81%932153%E5%8F%B7%E7%A5%A5%E5%92%8C%E5%BE%A1%E5%9B%AD_%E7%A5%A5%E5%92%8C%E5%BE%A1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="155">
@@ -18675,9 +18675,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G155">
+      <c r="G155" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%A2%85%E9%BE%99%E5%A4%A7%E9%81%932153%E5%8F%B7%E7%A5%A5%E5%92%8C%E5%BE%A1%E5%9B%AD_%E7%A5%A5%E5%92%8C%E5%BE%A1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="156">
@@ -18711,9 +18711,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G156">
+      <c r="G156" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E9%87%91%E8%8B%B9%E6%9E%9C%E8%8A%B1%E5%9B%AD_%E9%87%91%E8%8B%B9%E6%9E%9C%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="157">
@@ -18747,9 +18747,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G157">
+      <c r="G157" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E9%87%91%E8%8B%B9%E6%9E%9C%E8%8A%B1%E5%9B%AD_%E9%87%91%E8%8B%B9%E6%9E%9C%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="158">
@@ -18783,9 +18783,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G158">
+      <c r="G158" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E5%B9%B8%E7%A6%8F%E5%9F%8E%E4%BA%8C%E6%9C%9F_%E5%B9%B8%E7%A6%8F%E5%9F%8E%E6%B6%A6%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="159">
@@ -18819,9 +18819,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G159">
+      <c r="G159" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E5%B9%B8%E7%A6%8F%E5%9F%8E%E4%BA%8C%E6%9C%9F_%E5%B9%B8%E7%A6%8F%E5%9F%8E%E6%B6%A6%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="160">
@@ -18855,9 +18855,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G160">
+      <c r="G160" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E5%B9%B8%E7%A6%8F%E5%9F%8E%E4%BA%8C%E6%9C%9F_%E5%B9%B8%E7%A6%8F%E5%9F%8E%E6%B6%A6%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="161">
@@ -18891,9 +18891,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G161">
+      <c r="G161" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E5%B9%B8%E7%A6%8F%E5%9F%8E%E4%BA%8C%E6%9C%9F_%E5%B9%B8%E7%A6%8F%E5%9F%8E%E6%B6%A6%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="162">
@@ -18927,9 +18927,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G162">
+      <c r="G162" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E5%B9%B8%E7%A6%8F%E5%9F%8E%E4%BA%8C%E6%9C%9F_%E5%B9%B8%E7%A6%8F%E5%9F%8E%E6%B6%A6%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="163">
@@ -18963,9 +18963,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G163">
+      <c r="G163" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E7%99%BE%E8%8A%B1%E4%BA%8C%E8%B7%AF%E5%85%AD%E5%B7%B7_%E7%99%BE%E8%8A%B1%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="164">
@@ -18999,9 +18999,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（2处问题）</t>
         </is>
       </c>
-      <c r="G164">
+      <c r="G164" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E7%99%BE%E8%8A%B1%E4%BA%8C%E8%B7%AF%E5%85%AD%E5%B7%B7_%E7%99%BE%E8%8A%B1%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="165">
@@ -19035,9 +19035,9 @@
           <t>（2）责任公示牌缺失(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G165">
+      <c r="G165" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E7%99%BE%E8%8A%B1%E4%BA%8C%E8%B7%AF%E5%85%AD%E5%B7%B7_%E7%99%BE%E8%8A%B1%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="166">
@@ -19071,9 +19071,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G166">
+      <c r="G166" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E7%99%BE%E8%8A%B1%E4%BA%8C%E8%B7%AF%E5%85%AD%E5%B7%B7_%E7%99%BE%E8%8A%B1%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="167">
@@ -19107,9 +19107,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G167">
+      <c r="G167" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E4%B8%87%E5%AF%8C%E6%A5%BC%E6%A1%91%E8%BE%BE%E5%AE%9D%E7%94%B5%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E6%9D%8E%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="168">
@@ -19143,9 +19143,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G168">
+      <c r="G168" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E4%B8%87%E5%AF%8C%E6%A5%BC%E6%A1%91%E8%BE%BE%E5%AE%9D%E7%94%B5%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E6%9D%8E%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="169">
@@ -19179,9 +19179,9 @@
           <t>（2）责任公示牌缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G169">
+      <c r="G169" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E4%B8%87%E5%AF%8C%E6%A5%BC%E6%A1%91%E8%BE%BE%E5%AE%9D%E7%94%B5%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E6%9D%8E%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="170">
@@ -19215,9 +19215,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G170">
+      <c r="G170" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E4%B8%87%E5%AF%8C%E6%A5%BC%E6%A1%91%E8%BE%BE%E5%AE%9D%E7%94%B5%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E6%9D%8E%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="171">
@@ -19251,9 +19251,9 @@
           <t>（2）柜门未保持关闭(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G171">
+      <c r="G171" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E4%B8%87%E5%AF%8C%E6%A5%BC%E6%A1%91%E8%BE%BE%E5%AE%9D%E7%94%B5%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E6%9D%8E%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="172">
@@ -19287,9 +19287,9 @@
           <t>（3）内桶未开盖(-2)（1处问题）； （4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G172">
+      <c r="G172" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E4%B8%87%E5%AF%8C%E6%A5%BC%E6%A1%91%E8%BE%BE%E5%AE%9D%E7%94%B5%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E6%9D%8E%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="173">
@@ -19323,9 +19323,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G173">
+      <c r="G173" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E4%B8%87%E5%AF%8C%E6%A5%BC%E6%A1%91%E8%BE%BE%E5%AE%9D%E7%94%B5%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E6%9D%8E%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="174">
@@ -19359,9 +19359,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G174">
+      <c r="G174" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E4%B8%87%E5%AF%8C%E6%A5%BC%E6%A1%91%E8%BE%BE%E5%AE%9D%E7%94%B5%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E6%9D%8E%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="175">
@@ -19395,9 +19395,9 @@
           <t>（2）未使用(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G175">
+      <c r="G175" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E4%B8%87%E5%AF%8C%E6%A5%BC%E6%A1%91%E8%BE%BE%E5%AE%9D%E7%94%B5%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E6%9D%8E%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="176">
@@ -19431,9 +19431,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G176">
+      <c r="G176" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E5%B8%83%E5%90%89%E4%B8%80%E6%9D%91_%E4%BD%95%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="177">
@@ -19467,9 +19467,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G177">
+      <c r="G177" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E5%B8%83%E5%90%89%E4%B8%80%E6%9D%91_%E4%BD%95%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="178">
@@ -19503,9 +19503,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G178">
+      <c r="G178" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E5%B8%83%E5%90%89%E4%B8%80%E6%9D%91_%E4%BD%95%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="179">
@@ -19539,9 +19539,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G179">
+      <c r="G179" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E5%B8%83%E5%90%89%E4%B8%80%E6%9D%91_%E4%BD%95%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="180">
@@ -19575,9 +19575,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G180">
+      <c r="G180" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E5%B8%83%E5%90%89%E4%B8%80%E6%9D%91_%E4%BD%95%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="181">
@@ -19611,9 +19611,9 @@
           <t>（2）未规范张贴垃圾分类宣传海报（海报缺失、内容错误/未更新等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G181">
+      <c r="G181" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E5%B8%83%E5%90%89%E4%B8%80%E6%9D%91_%E4%BD%95%E5%B1%8B%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="182">
@@ -19647,9 +19647,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G182">
+      <c r="G182" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E6%B2%99%E9%BE%99%E8%B7%AF32%E4%B9%8B1_3%E5%8F%B7_%E8%80%81%E5%9C%A9%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="183">
@@ -19683,9 +19683,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G183">
+      <c r="G183" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E6%B2%99%E9%BE%99%E8%B7%AF32%E4%B9%8B1_3%E5%8F%B7_%E8%80%81%E5%9C%A9%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="184">
@@ -19719,9 +19719,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G184">
+      <c r="G184" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E6%B2%99%E9%BE%99%E8%B7%AF32%E4%B9%8B1_3%E5%8F%B7_%E8%80%81%E5%9C%A9%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="185">
@@ -19755,9 +19755,9 @@
           <t>（2）责任公示牌缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G185">
+      <c r="G185" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E6%B2%99%E9%BE%99%E8%B7%AF32%E4%B9%8B1_3%E5%8F%B7_%E8%80%81%E5%9C%A9%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="186">
@@ -19791,9 +19791,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G186">
+      <c r="G186" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E6%B2%99%E9%BE%99%E8%B7%AF32%E4%B9%8B1_3%E5%8F%B7_%E8%80%81%E5%9C%A9%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="187">
@@ -19827,9 +19827,9 @@
           <t>（3）内桶未开盖(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G187">
+      <c r="G187" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E6%B2%99%E9%BE%99%E8%B7%AF32%E4%B9%8B1_3%E5%8F%B7_%E8%80%81%E5%9C%A9%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="188">
@@ -19863,9 +19863,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G188">
+      <c r="G188" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E6%B2%99%E9%BE%99%E8%B7%AF32%E4%B9%8B1_3%E5%8F%B7_%E8%80%81%E5%9C%A9%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="189">
@@ -19899,9 +19899,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G189">
+      <c r="G189" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E6%B2%99%E9%BE%99%E8%B7%AF32%E4%B9%8B1_3%E5%8F%B7_%E8%80%81%E5%9C%A9%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="190">
@@ -19935,9 +19935,9 @@
           <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G190">
+      <c r="G190" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%AE%9D%E4%B8%BD%E8%B7%AF90%E5%8F%B7_%E7%B2%A4%E5%AE%9D%E7%A4%BE%E5%BA%B7.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="191">
@@ -19971,9 +19971,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（2处问题）</t>
         </is>
       </c>
-      <c r="G191">
+      <c r="G191" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E7%A4%BE%E5%8C%BA%E6%B3%93%E6%B6%A6%E9%85%92%E5%BA%97_%E6%B7%B1%E5%9C%B3%E5%B8%83%E5%90%89%E4%B8%9C%E7%AB%99%E5%BA%97_%E6%B3%93%E6%B6%A6%E9%85%92%E5%BA%97.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="192">
@@ -20007,9 +20007,9 @@
           <t>（2）主动向消费者提供客房一次性日用品(-10)（1处问题）</t>
         </is>
       </c>
-      <c r="G192">
+      <c r="G192" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E7%A4%BE%E5%8C%BA%E6%B3%93%E6%B6%A6%E9%85%92%E5%BA%97_%E6%B7%B1%E5%9C%B3%E5%B8%83%E5%90%89%E4%B8%9C%E7%AB%99%E5%BA%97_%E6%B3%93%E6%B6%A6%E9%85%92%E5%BA%97.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="193">
@@ -20043,9 +20043,9 @@
           <t>（2）收集容器缺失(-6)（1处问题）</t>
         </is>
       </c>
-      <c r="G193">
+      <c r="G193" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E4%B8%BD%E5%B1%B1%E8%B7%AF15%E5%8F%B7%E7%A1%85%E8%B0%B7%E4%BA%BA%E6%89%8D%E5%85%AC%E5%AF%93_%E9%BA%A6%E5%BD%93%E5%8A%B3%E5%BA%97.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="194">
@@ -20079,9 +20079,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（3处问题）</t>
         </is>
       </c>
-      <c r="G194">
+      <c r="G194" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E4%B8%BD%E5%B1%B1%E8%B7%AF15%E5%8F%B7%E7%A1%85%E8%B0%B7%E4%BA%BA%E6%89%8D%E5%85%AC%E5%AF%93_%E9%BA%A6%E5%BD%93%E5%8A%B3%E5%BA%97.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="195">
@@ -20115,9 +20115,9 @@
           <t>（2）未设置光盘行动、节约粮食等宣传海报或温馨提示等(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G195">
+      <c r="G195" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E4%B8%BD%E5%B1%B1%E8%B7%AF15%E5%8F%B7%E7%A1%85%E8%B0%B7%E4%BA%BA%E6%89%8D%E5%85%AC%E5%AF%93_%E9%BA%A6%E5%BD%93%E5%8A%B3%E5%BA%97.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="196">
@@ -20151,9 +20151,9 @@
           <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-4)（1处问题）</t>
         </is>
       </c>
-      <c r="G196">
+      <c r="G196" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B8%83%E5%90%89%E8%A1%97%E9%81%93%E5%B8%83%E5%90%89%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99_%E5%B8%83%E5%90%89%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="197">
@@ -20187,9 +20187,9 @@
           <t>（3）其他问题说明（备注描述） (-8)（1处问题）</t>
         </is>
       </c>
-      <c r="G197">
+      <c r="G197" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A4%A7%E6%B2%99%E6%B2%B3%E7%94%9F%E6%80%81%E9%95%BF%E5%BB%8A%E7%BB%BF%E9%81%93%E5%8C%97%E4%BA%AC%E5%A4%A7%E5%AD%A6%E6%B7%B1%E5%9C%B3%E7%A0%94%E7%A9%B6%E7%94%9F%E9%99%A2%E6%A0%A1%E5%8C%BA_%E7%94%B0%E5%AF%AE%E5%B8%82%E5%9C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="198">
@@ -20223,9 +20223,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（2处问题）</t>
         </is>
       </c>
-      <c r="G198">
+      <c r="G198" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E4%B8%BD%E5%B1%B1%E8%B7%AF36%E5%8F%B7%E7%A1%85%E8%B0%B7%E4%BA%BA%E6%89%8D%E5%85%AC%E5%AF%93_%E7%BB%B4%E4%B9%9F%E7%BA%B3%E4%B8%89%E5%A5%BD%E9%85%92%E5%BA%97_%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%B8%BF%E5%8D%93%E9%85%92%E5%BA%97%E7%AE%A1%E7%90%86%E6%9C%89%E9%99%90%E5%85%AC%E5%8F%B8%E6%A1%83%E6%BA%90%E5%88%86%E5%85%AC%E5%8F%B8_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="199">
@@ -20259,9 +20259,9 @@
           <t>（2）未成组摆放两分类收集容器(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G199">
+      <c r="G199" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99_%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="200">
@@ -20295,9 +20295,9 @@
           <t>（2）收集容器缺失(5)（1处问题）</t>
         </is>
       </c>
-      <c r="G200">
+      <c r="G200" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99_%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="201">
@@ -20331,9 +20331,9 @@
           <t>（3）环境卫生不整洁（投放点有散落垃圾、杂物堆放，地面有明显污水污渍等）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G201">
+      <c r="G201" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99_%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="202">
@@ -20367,9 +20367,9 @@
           <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-4)（1处问题）</t>
         </is>
       </c>
-      <c r="G202">
+      <c r="G202" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99_%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="203">
@@ -20403,9 +20403,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G203">
+      <c r="G203" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E8%B7%AF20%E5%8F%B7_%E7%A2%A7%E6%B9%96%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="204">
@@ -20439,9 +20439,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G204">
+      <c r="G204" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E8%B7%AF20%E5%8F%B7_%E7%A2%A7%E6%B9%96%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="205">
@@ -20475,9 +20475,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G205">
+      <c r="G205" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E8%B7%AF20%E5%8F%B7_%E7%A2%A7%E6%B9%96%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="206">
@@ -20511,9 +20511,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G206">
+      <c r="G206" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E7%A1%85%E8%B0%B7%E4%BA%BA%E6%89%8D%E5%85%AC%E5%AF%93_%E8%81%9A%E5%AE%81%E5%B1%B1%E5%BA%84.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="207">
@@ -20547,9 +20547,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G207">
+      <c r="G207" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E7%AC%8B%E5%B2%97%E6%B4%AA%E6%B9%96%E8%8A%B1%E5%9B%AD_%E6%B4%AA%E6%B9%96%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="208">
@@ -20583,9 +20583,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G208">
+      <c r="G208" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E7%AC%8B%E5%B2%97%E6%B4%AA%E6%B9%96%E8%8A%B1%E5%9B%AD_%E6%B4%AA%E6%B9%96%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="209">
@@ -20619,9 +20619,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G209">
+      <c r="G209" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E7%AC%8B%E5%B2%97%E6%B4%AA%E6%B9%96%E8%8A%B1%E5%9B%AD_%E6%B4%AA%E6%B9%96%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="210">
@@ -20655,9 +20655,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G210">
+      <c r="G210" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%96%B0%E4%B8%9C%E6%B1%9F%E6%A1%A5%E5%98%B4%E6%B2%B3%E9%B2%9C%E5%9D%8A_%E6%96%B0%E4%B8%9C%E6%B1%9F%E6%A1%A5%E5%98%B4%E6%B2%B3%E9%B2%9C%E5%9D%8A.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="211">
@@ -20691,9 +20691,9 @@
           <t>（2）洗手设施缺失(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G211">
+      <c r="G211" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%9723%E5%8F%B7_%E7%BF%A0%E7%9B%88%E5%98%89%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="212">
@@ -20727,9 +20727,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G212">
+      <c r="G212" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%9723%E5%8F%B7_%E7%BF%A0%E7%9B%88%E5%98%89%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="213">
@@ -20763,9 +20763,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G213">
+      <c r="G213" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%9723%E5%8F%B7_%E7%BF%A0%E7%9B%88%E5%98%89%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="214">
@@ -20799,9 +20799,9 @@
           <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G214">
+      <c r="G214" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%9723%E5%8F%B7_%E7%BF%A0%E7%9B%88%E5%98%89%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="215">
@@ -20835,9 +20835,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G215">
+      <c r="G215" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%97%E4%B8%80%E5%8F%B7%E5%A4%A7%E9%99%A2_%E6%B0%B4%E6%B3%A5%E5%8E%82%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="216">
@@ -20871,9 +20871,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G216">
+      <c r="G216" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%97%E4%B8%80%E5%8F%B7%E5%A4%A7%E9%99%A2_%E6%B0%B4%E6%B3%A5%E5%8E%82%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="217">
@@ -20907,9 +20907,9 @@
           <t>（4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G217">
+      <c r="G217" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%97%E4%B8%80%E5%8F%B7%E5%A4%A7%E9%99%A2_%E6%B0%B4%E6%B3%A5%E5%8E%82%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="218">
@@ -20943,9 +20943,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G218">
+      <c r="G218" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%97%E4%B8%80%E5%8F%B7%E5%A4%A7%E9%99%A2_%E6%B0%B4%E6%B3%A5%E5%8E%82%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="219">
@@ -20979,9 +20979,9 @@
           <t>（2）未使用(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G219">
+      <c r="G219" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%97%E4%B8%80%E5%8F%B7%E5%A4%A7%E9%99%A2_%E6%B0%B4%E6%B3%A5%E5%8E%82%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="220">
@@ -21015,9 +21015,9 @@
           <t>（2）洗手设施缺失(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G220">
+      <c r="G220" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%A1%98%E6%9C%97%E6%9D%91_%E5%A1%98%E6%9C%97%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="221">
@@ -21051,9 +21051,9 @@
           <t>（2）围挡设置不规范（未设置围挡，围挡封闭不全，或使用移动式栅栏、水马等围合）(-2)（1处问题）； （3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）； （5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G221">
+      <c r="G221" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%A1%98%E6%9C%97%E6%9D%91_%E5%A1%98%E6%9C%97%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="222">
@@ -21087,9 +21087,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G222">
+      <c r="G222" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%A1%98%E6%9C%97%E6%9D%91_%E5%A1%98%E6%9C%97%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="223">
@@ -21123,9 +21123,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G223">
+      <c r="G223" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%9721%E5%8F%B7_%E5%90%88%E6%AD%A3%E9%94%A6%E6%B9%96%E9%80%B8%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="224">
@@ -21159,9 +21159,9 @@
           <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G224">
+      <c r="G224" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%9721%E5%8F%B7_%E5%90%88%E6%AD%A3%E9%94%A6%E6%B9%96%E9%80%B8%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="225">
@@ -21195,9 +21195,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G225">
+      <c r="G225" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%9721%E5%8F%B7_%E5%90%88%E6%AD%A3%E9%94%A6%E6%B9%96%E9%80%B8%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="226">
@@ -21231,9 +21231,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G226">
+      <c r="G226" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%9721%E5%8F%B7_%E5%90%88%E6%AD%A3%E9%94%A6%E6%B9%96%E9%80%B8%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="227">
@@ -21267,9 +21267,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G227">
+      <c r="G227" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%B8%80%E8%A1%9721%E5%8F%B7_%E5%90%88%E6%AD%A3%E9%94%A6%E6%B9%96%E9%80%B8%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="228">
@@ -21303,9 +21303,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）； （5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G228">
+      <c r="G228" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%A1%98%E6%9C%97%E6%B0%B4%E6%9C%A8%E4%B8%B9%E5%8D%8E%E5%9B%AD_%E6%B0%B4%E6%9C%A8%E4%B8%B9%E5%8D%8E%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="229">
@@ -21339,9 +21339,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G229">
+      <c r="G229" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%BA%8C%E8%A1%9759%E5%8F%B7_%E5%B7%A5%E5%95%86%E5%AE%BF%E8%88%8D.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="230">
@@ -21375,9 +21375,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G230">
+      <c r="G230" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%BA%8C%E8%A1%9759%E5%8F%B7_%E5%B7%A5%E5%95%86%E5%AE%BF%E8%88%8D.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="231">
@@ -21411,9 +21411,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G231">
+      <c r="G231" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B4%AA%E6%B9%96%E4%BA%8C%E8%A1%9759%E5%8F%B7_%E5%B7%A5%E5%95%86%E5%AE%BF%E8%88%8D.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="232">
@@ -21447,9 +21447,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G232">
+      <c r="G232" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%AE%9D%E8%83%BD%E5%9F%8E%E8%A5%BF%E5%8C%BA_%E5%AE%9D%E8%83%BD%E5%9F%8E%E8%A5%BF%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="233">
@@ -21483,9 +21483,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G233">
+      <c r="G233" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%AE%9D%E8%83%BD%E5%9F%8E%E8%A5%BF%E5%8C%BA_%E5%AE%9D%E8%83%BD%E5%9F%8E%E8%A5%BF%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="234">
@@ -21519,9 +21519,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）； （5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G234">
+      <c r="G234" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%A1%83%E6%BA%90%E8%A1%97%E9%81%93%E5%A1%98%E6%9C%97%E7%A4%BE%E5%8C%BA%E5%AE%9D%E8%83%BD%E5%9F%8E%E8%A5%BF%E5%8C%BA_%E5%AE%9D%E8%83%BD%E5%9F%8E%E8%A5%BF%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="235">
@@ -21555,9 +21555,9 @@
           <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G235">
+      <c r="G235" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF%E4%B9%A6%E9%99%A2%E8%A1%9711%E5%8F%B7_%E9%87%91%E6%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="236">
@@ -21591,9 +21591,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G236">
+      <c r="G236" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF%E4%B9%A6%E9%99%A2%E8%A1%9711%E5%8F%B7_%E9%87%91%E6%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="237">
@@ -21627,9 +21627,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G237">
+      <c r="G237" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF%E4%B9%A6%E9%99%A2%E8%A1%9711%E5%8F%B7_%E9%87%91%E6%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="238">
@@ -21663,9 +21663,9 @@
           <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-4)（1处问题）</t>
         </is>
       </c>
-      <c r="G238">
+      <c r="G238" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF%E4%B9%A6%E9%99%A2%E8%A1%9711%E5%8F%B7_%E9%87%91%E6%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="239">
@@ -21699,9 +21699,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G239">
+      <c r="G239" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF%E4%B9%A6%E9%99%A2%E8%A1%9711%E5%8F%B7_%E9%87%91%E6%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="240">
@@ -21735,9 +21735,9 @@
           <t>周边环境脏乱(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G240">
+      <c r="G240" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF%E4%B9%A6%E9%99%A2%E8%A1%9711%E5%8F%B7_%E9%87%91%E6%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="241">
@@ -21771,9 +21771,9 @@
           <t>（2）分类收集容器缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G241">
+      <c r="G241" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%B9%A6%E9%99%A2%E8%A1%978%E5%8F%B7_%E4%B9%A6%E9%99%A2%E8%A1%978%E5%8F%B7.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="242">
@@ -21807,9 +21807,9 @@
           <t>（2）洗手设施缺失(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G242">
+      <c r="G242" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%B9%A6%E9%99%A2%E8%A1%978%E5%8F%B7_%E4%B9%A6%E9%99%A2%E8%A1%978%E5%8F%B7.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="243">
@@ -21843,9 +21843,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G243">
+      <c r="G243" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%B9%A6%E9%99%A2%E8%A1%978%E5%8F%B7_%E4%B9%A6%E9%99%A2%E8%A1%978%E5%8F%B7.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="244">
@@ -21879,9 +21879,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G244">
+      <c r="G244" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%B9%A6%E9%99%A2%E8%A1%978%E5%8F%B7_%E4%B9%A6%E9%99%A2%E8%A1%978%E5%8F%B7.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="245">
@@ -21915,9 +21915,9 @@
           <t>（2）未使用(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G245">
+      <c r="G245" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%B9%A6%E9%99%A2%E8%A1%978%E5%8F%B7_%E4%B9%A6%E9%99%A2%E8%A1%978%E5%8F%B7.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="246">
@@ -21951,9 +21951,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G246">
+      <c r="G246" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%B9%A6%E9%99%A2%E8%A1%977%E5%8F%B7_%E4%B9%A6%E9%99%A2%E8%A1%977%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="247">
@@ -21987,9 +21987,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G247">
+      <c r="G247" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%B9%A6%E9%99%A2%E8%A1%977%E5%8F%B7_%E4%B9%A6%E9%99%A2%E8%A1%977%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="248">
@@ -22023,9 +22023,9 @@
           <t>（2）车辆挡住投放点过道、投放口前堆放大件杂物，阻碍居民投放(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G248">
+      <c r="G248" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B9%A6%E9%99%A2%E8%A1%97_%E4%B9%A6%E9%99%A2%E8%A1%97_5%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="249">
@@ -22059,9 +22059,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G249">
+      <c r="G249" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B9%A6%E9%99%A2%E8%A1%97_%E4%B9%A6%E9%99%A2%E8%A1%97_5%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="250">
@@ -22095,9 +22095,9 @@
           <t>（4）其他问题（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G250">
+      <c r="G250" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B9%A6%E9%99%A2%E8%A1%97_%E4%B9%A6%E9%99%A2%E8%A1%97_5%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="251">
@@ -22131,9 +22131,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G251">
+      <c r="G251" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B9%A6%E9%99%A2%E8%A1%97_%E4%B9%A6%E9%99%A2%E8%A1%97_5%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="252">
@@ -22167,9 +22167,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G252">
+      <c r="G252" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3101%E5%8F%B7_%E5%9F%B9%E6%A3%AE%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="253">
@@ -22203,9 +22203,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G253">
+      <c r="G253" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3101%E5%8F%B7_%E5%9F%B9%E6%A3%AE%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="254">
@@ -22239,9 +22239,9 @@
           <t>（4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G254">
+      <c r="G254" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3101%E5%8F%B7_%E5%9F%B9%E6%A3%AE%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="255">
@@ -22275,9 +22275,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G255">
+      <c r="G255" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3101%E5%8F%B7_%E5%9F%B9%E6%A3%AE%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="256">
@@ -22311,9 +22311,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G256">
+      <c r="G256" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3101%E5%8F%B7_%E5%9F%B9%E6%A3%AE%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="257">
@@ -22347,9 +22347,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G257">
+      <c r="G257" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3101%E5%8F%B7_%E5%9F%B9%E6%A3%AE%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="258">
@@ -22383,9 +22383,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G258">
+      <c r="G258" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3119%E5%8F%B7_%E6%B4%AA%E6%B9%96%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="259">
@@ -22419,9 +22419,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G259">
+      <c r="G259" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3119%E5%8F%B7_%E6%B4%AA%E6%B9%96%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="260">
@@ -22455,9 +22455,9 @@
           <t>（3）内桶未开盖(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G260">
+      <c r="G260" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3119%E5%8F%B7_%E6%B4%AA%E6%B9%96%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="261">
@@ -22491,9 +22491,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G261">
+      <c r="G261" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3119%E5%8F%B7_%E6%B4%AA%E6%B9%96%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="262">
@@ -22527,9 +22527,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G262">
+      <c r="G262" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3119%E5%8F%B7_%E6%B4%AA%E6%B9%96%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="263">
@@ -22563,9 +22563,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G263">
+      <c r="G263" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E9%97%A8%E8%A1%97%E9%81%93%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3119%E5%8F%B7_%E6%B4%AA%E6%B9%96%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="264">
@@ -22599,9 +22599,9 @@
           <t>（4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G264">
+      <c r="G264" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3131%E5%8F%B7_%E6%B0%B4%E4%BA%A7%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="265">
@@ -22635,9 +22635,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G265">
+      <c r="G265" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3131%E5%8F%B7_%E6%B0%B4%E4%BA%A7%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="266">
@@ -22671,9 +22671,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G266">
+      <c r="G266" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3131%E5%8F%B7_%E6%B0%B4%E4%BA%A7%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="267">
@@ -22707,9 +22707,9 @@
           <t>（3）暂存点与专项垃圾暂存点共用的，应保留一部分位置存放专项垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G267">
+      <c r="G267" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E4%BA%BA%E6%B0%91%E5%8C%97%E8%B7%AF3131%E5%8F%B7_%E6%B0%B4%E4%BA%A7%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="268">
@@ -22743,9 +22743,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G268">
+      <c r="G268" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%9B%90%E7%94%B0%E5%8C%BA%E6%A2%85%E6%B2%99%E8%A1%97%E9%81%93%E4%B8%9C%E6%B5%B7%E5%B2%B8%E7%A4%BE%E5%8C%BA%E4%B8%87%E7%A7%91%E4%B8%9C%E6%B5%B7%E5%B2%B8_%E4%B8%87%E7%A7%91%E4%B8%9C%E6%B5%B7%E5%B2%B8.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="269">
@@ -22779,9 +22779,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G269">
+      <c r="G269" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E4%BA%91%E9%A1%B6%E5%A4%A9%E6%B5%B7_%E4%BA%91%E9%A1%B6%E5%A4%A9%E6%B5%B7.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="270">
@@ -22815,9 +22815,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G270">
+      <c r="G270" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E6%A2%85%E6%B2%99%E8%A1%97%E9%81%93%E6%B5%B7%E8%AF%AD%E4%B8%9C%E5%9B%AD_%E6%B5%B7%E8%AF%AD%E4%B8%9C%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="271">
@@ -22851,9 +22851,9 @@
           <t>（4）其他问题（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G271">
+      <c r="G271" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E8%B5%9B%E9%BE%99%E8%B1%AA%E8%BD%A9%E5%B0%8F%E5%8C%BA_%E8%B5%9B%E9%BE%99%E8%B1%AA%E8%BD%A9BC%E5%BA%A7.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="272">
@@ -22887,9 +22887,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G272">
+      <c r="G272" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E6%B8%85%E6%B9%96%E7%A4%BE%E5%8C%BA%E6%B8%85%E6%B9%96%E6%96%B0%E6%9D%91_%E6%B8%85%E6%B9%96%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="273">
@@ -22923,9 +22923,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（3处问题）</t>
         </is>
       </c>
-      <c r="G273">
+      <c r="G273" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E6%B8%85%E6%B9%96%E7%A4%BE%E5%8C%BA%E6%B8%85%E6%B9%96%E6%96%B0%E6%9D%91_%E6%B8%85%E6%B9%96%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="274">
@@ -22959,9 +22959,9 @@
           <t>（2）投放口被封闭或遮挡(-2)（3处问题）； （3）内桶未开盖(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G274">
+      <c r="G274" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E6%B8%85%E6%B9%96%E7%A4%BE%E5%8C%BA%E6%B8%85%E6%B9%96%E6%96%B0%E6%9D%91_%E6%B8%85%E6%B9%96%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="275">
@@ -22995,9 +22995,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（5处问题）</t>
         </is>
       </c>
-      <c r="G275">
+      <c r="G275" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E6%B8%85%E6%B9%96%E7%A4%BE%E5%8C%BA%E6%B8%85%E6%B9%96%E6%96%B0%E6%9D%91_%E6%B8%85%E6%B9%96%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="276">
@@ -23031,9 +23031,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G276">
+      <c r="G276" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E6%B8%85%E6%B9%96%E7%A4%BE%E5%8C%BA%E6%B8%85%E6%B9%96%E6%96%B0%E6%9D%91_%E6%B8%85%E6%B9%96%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="277">
@@ -23067,9 +23067,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）； （3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G277">
+      <c r="G277" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E7%BE%8E%E4%B8%BD365%E8%8A%B1%E5%9B%AD_%E7%BE%8E%E4%B8%BD365%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="278">
@@ -23103,9 +23103,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G278">
+      <c r="G278" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E7%BE%8E%E4%B8%BD365%E8%8A%B1%E5%9B%AD_%E7%BE%8E%E4%B8%BD365%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="279">
@@ -23139,9 +23139,9 @@
           <t>（4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G279">
+      <c r="G279" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E7%BE%8E%E4%B8%BD365%E8%8A%B1%E5%9B%AD_%E7%BE%8E%E4%B8%BD365%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="280">
@@ -23175,9 +23175,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G280">
+      <c r="G280" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E7%BE%8E%E4%B8%BD365%E8%8A%B1%E5%9B%AD_%E7%BE%8E%E4%B8%BD365%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="281">
@@ -23211,9 +23211,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G281">
+      <c r="G281" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E7%BE%8E%E4%B8%BD365%E8%8A%B1%E5%9B%AD_%E7%BE%8E%E4%B8%BD365%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="282">
@@ -23247,9 +23247,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G282">
+      <c r="G282" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E7%BE%8E%E4%B8%BD365%E8%8A%B1%E5%9B%AD_%E7%BE%8E%E4%B8%BD365%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="283">
@@ -23283,9 +23283,9 @@
           <t>（2）分类收集容器缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G283">
+      <c r="G283" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E5%A1%98%E5%B0%BE%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%B0%BE%E5%8D%81%E4%BA%8C%E5%8C%BA%E5%8C%975%E5%B7%B71%E5%8F%B7_%E5%A1%98%E5%B0%BE%E5%8D%81%E4%BA%8C%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="284">
@@ -23319,9 +23319,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（3处问题）</t>
         </is>
       </c>
-      <c r="G284">
+      <c r="G284" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E5%AF%8C%E8%81%94%E4%B8%80%E5%8C%BA_%E5%AF%8C%E8%81%94%E4%B8%80%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="285">
@@ -23355,9 +23355,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G285">
+      <c r="G285" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E5%AF%8C%E8%81%94%E4%B8%80%E5%8C%BA_%E5%AF%8C%E8%81%94%E4%B8%80%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="286">
@@ -23391,9 +23391,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G286">
+      <c r="G286" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E5%AF%8C%E8%81%94%E4%B8%80%E5%8C%BA_%E5%AF%8C%E8%81%94%E4%B8%80%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="287">
@@ -23427,9 +23427,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G287">
+      <c r="G287" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E5%AF%8C%E8%81%94%E4%B8%80%E5%8C%BA_%E5%AF%8C%E8%81%94%E4%B8%80%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="288">
@@ -23463,9 +23463,9 @@
           <t>（2）责任公示牌缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G288">
+      <c r="G288" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%BC%8F%E8%8B%B1%E5%A6%87%E7%A7%91_%E5%A1%98%E5%B0%BE%E4%B9%9D%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="289">
@@ -23499,9 +23499,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（2处问题）； （3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G289">
+      <c r="G289" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%BC%8F%E8%8B%B1%E5%A6%87%E7%A7%91_%E5%A1%98%E5%B0%BE%E4%B9%9D%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="290">
@@ -23535,9 +23535,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
         </is>
       </c>
-      <c r="G290">
+      <c r="G290" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%BC%8F%E8%8B%B1%E5%A6%87%E7%A7%91_%E5%A1%98%E5%B0%BE%E4%B9%9D%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="291">
@@ -23571,9 +23571,9 @@
           <t>（2）未成组摆放两分类收集容器(-3)</t>
         </is>
       </c>
-      <c r="G291">
+      <c r="G291" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%A4%A7%E6%A2%85%E6%B2%99%E5%85%AC%E4%BA%A4%E6%80%BB%E7%AB%99_%E5%A4%A7%E6%A2%85%E6%B2%99%E5%85%AC%E4%BA%A4%E6%80%BB%E7%AB%99_M191_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="292">
@@ -23607,9 +23607,9 @@
           <t>（2）收集容器缺失(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G292">
+      <c r="G292" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%A4%A7%E6%A2%85%E6%B2%99%E5%85%AC%E4%BA%A4%E6%80%BB%E7%AB%99_%E5%A4%A7%E6%A2%85%E6%B2%99%E5%85%AC%E4%BA%A4%E6%80%BB%E7%AB%99_M191_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="293">
@@ -23643,9 +23643,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G293">
+      <c r="G293" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E4%B8%9C%E6%B5%B7%E5%B2%B8%E7%A4%BE%E5%8C%BA_%E4%B8%9C%E6%B5%B7%E5%B2%B8%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="294">
@@ -23679,9 +23679,9 @@
           <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-4)（1处问题）</t>
         </is>
       </c>
-      <c r="G294">
+      <c r="G294" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E4%B8%9C%E6%B5%B7%E5%B2%B8%E7%A4%BE%E5%8C%BA_%E4%B8%9C%E6%B5%B7%E5%B2%B8%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="295">
@@ -23715,9 +23715,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G295">
+      <c r="G295" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E6%A2%85%E6%B2%99%E8%A1%97%E9%81%93%E4%BC%98%E5%93%81%E8%89%BA%E5%A2%85%E9%9B%85%E5%B1%85_%E6%BC%AB%E9%AA%91%E9%A4%90%E5%90%A7%E7%A7%81%E6%88%BF%E8%8F%9C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="296">
@@ -23751,9 +23751,9 @@
           <t>（2）分类收集容器缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G296">
+      <c r="G296" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%BC%8F%E8%8B%B1%E5%A6%87%E7%A7%91_%E5%A1%98%E5%B0%BE%E5%85%AB%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="297">
@@ -23787,9 +23787,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G297">
+      <c r="G297" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%BC%8F%E8%8B%B1%E5%A6%87%E7%A7%91_%E5%A1%98%E5%B0%BE%E5%85%AB%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="298">
@@ -23823,9 +23823,9 @@
           <t>（3）内桶未开盖(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G298">
+      <c r="G298" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%BC%8F%E8%8B%B1%E5%A6%87%E7%A7%91_%E5%A1%98%E5%B0%BE%E5%85%AB%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="299">
@@ -23859,9 +23859,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
         </is>
       </c>
-      <c r="G299">
+      <c r="G299" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%BC%8F%E8%8B%B1%E5%A6%87%E7%A7%91_%E5%A1%98%E5%B0%BE%E5%85%AB%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="300">
@@ -23895,9 +23895,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G300">
+      <c r="G300" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%8E%E5%B7%A5%E4%B8%9A%E5%85%AB%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84%E4%B8%9C%E5%8D%97200%E7%B1%B3%E8%B7%AF%E4%B8%9C_%E6%9B%A6%E6%B9%BE%E5%A4%A9%E9%A6%A5.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="301">
@@ -23931,9 +23931,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G301">
+      <c r="G301" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%8E%E5%B7%A5%E4%B8%9A%E5%85%AB%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84%E4%B8%9C%E5%8D%97200%E7%B1%B3%E8%B7%AF%E4%B8%9C_%E6%9B%A6%E6%B9%BE%E5%A4%A9%E9%A6%A5.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="302">
@@ -23967,9 +23967,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G302">
+      <c r="G302" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%8E%E5%B7%A5%E4%B8%9A%E5%85%AB%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84%E4%B8%9C%E5%8D%97200%E7%B1%B3%E8%B7%AF%E4%B8%9C_%E6%9B%A6%E6%B9%BE%E5%A4%A9%E9%A6%A5.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="303">
@@ -24003,9 +24003,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G303">
+      <c r="G303" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%8E%E5%B7%A5%E4%B8%9A%E5%85%AB%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84%E4%B8%9C%E5%8D%97200%E7%B1%B3%E8%B7%AF%E4%B8%9C_%E6%9B%A6%E6%B9%BE%E5%A4%A9%E9%A6%A5.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="304">
@@ -24039,9 +24039,9 @@
           <t>（2）投放口被封闭或遮挡(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G304">
+      <c r="G304" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%8E%E5%B7%A5%E4%B8%9A%E5%85%AB%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84%E4%B8%9C%E5%8D%97200%E7%B1%B3%E8%B7%AF%E4%B8%9C_%E6%9B%A6%E6%B9%BE%E5%A4%A9%E9%A6%A5.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="305">
@@ -24075,9 +24075,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）； （4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）； （5）暂存点存在用水用电安全隐患(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G305">
+      <c r="G305" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%8E%E5%B7%A5%E4%B8%9A%E5%85%AB%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84%E4%B8%9C%E5%8D%97200%E7%B1%B3%E8%B7%AF%E4%B8%9C_%E6%9B%A6%E6%B9%BE%E5%A4%A9%E9%A6%A5.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="306">
@@ -24111,9 +24111,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G306">
+      <c r="G306" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%8E%E5%B7%A5%E4%B8%9A%E5%85%AB%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84%E4%B8%9C%E5%8D%97200%E7%B1%B3%E8%B7%AF%E4%B8%9C_%E6%9B%A6%E6%B9%BE%E5%A4%A9%E9%A6%A5.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="307">
@@ -24147,9 +24147,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（3处问题）</t>
         </is>
       </c>
-      <c r="G307">
+      <c r="G307" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B2%B8%E6%B9%BE%E4%B8%89%E8%A1%975%E5%8F%B7_%E6%B7%B1%E5%9C%B3%E5%90%8E%E6%B5%B7%E6%9C%A8%E6%A3%89%E8%8A%B1%E9%85%92%E5%BA%97.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="308">
@@ -24183,9 +24183,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G308">
+      <c r="G308" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E5%A1%98%E5%B0%BE%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%89%E5%8C%BA_%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%89%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="309">
@@ -24219,9 +24219,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
         </is>
       </c>
-      <c r="G309">
+      <c r="G309" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E5%A1%98%E5%B0%BE%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%89%E5%8C%BA_%E5%A1%98%E5%B0%BE%E5%8D%81%E4%B8%89%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="310">
@@ -24255,9 +24255,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G310">
+      <c r="G310" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E5%BC%93%E6%9D%91_%E5%BC%93%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="311">
@@ -24291,9 +24291,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（5处问题）</t>
         </is>
       </c>
-      <c r="G311">
+      <c r="G311" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E5%BC%93%E6%9D%91_%E5%BC%93%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="312">
@@ -24327,9 +24327,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（5处问题）</t>
         </is>
       </c>
-      <c r="G312">
+      <c r="G312" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E5%BC%93%E6%9D%91_%E5%BC%93%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="313">
@@ -24363,9 +24363,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G313">
+      <c r="G313" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E5%BC%93%E6%9D%91_%E5%BC%93%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="314">
@@ -24399,9 +24399,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（5处问题）</t>
         </is>
       </c>
-      <c r="G314">
+      <c r="G314" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E9%BE%99%E5%8D%8E%E8%A1%97%E9%81%93%E4%B8%89%E8%81%94%E7%A4%BE%E5%8C%BA%E5%BC%93%E6%9D%91_%E5%BC%93%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="315">
@@ -24435,9 +24435,9 @@
           <t>（2）未成组摆放两分类收集容器(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G315">
+      <c r="G315" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%B8%9C%E7%BF%A0%E9%9B%85%E5%B1%85%E6%96%B0%E9%A2%86%E6%B1%87%E8%B4%AD%E7%89%A9%E5%B9%BF%E5%9C%BA_%E5%A1%98%E5%B0%BE%E5%BA%97_%E6%96%B0%E9%A2%86%E6%B1%87%E8%B4%AD%E7%89%A9%E4%B8%AD%E5%BF%83.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="316">
@@ -24471,9 +24471,9 @@
           <t>（2）收集容器缺失(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G316">
+      <c r="G316" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%B8%9C%E7%BF%A0%E9%9B%85%E5%B1%85%E6%96%B0%E9%A2%86%E6%B1%87%E8%B4%AD%E7%89%A9%E5%B9%BF%E5%9C%BA_%E5%A1%98%E5%B0%BE%E5%BA%97_%E6%96%B0%E9%A2%86%E6%B1%87%E8%B4%AD%E7%89%A9%E4%B8%AD%E5%BF%83.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="317">
@@ -24507,9 +24507,9 @@
           <t>（2）收集容器缺失</t>
         </is>
       </c>
-      <c r="G317">
+      <c r="G317" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%B8%9C%E7%BF%A0%E9%9B%85%E5%B1%85%E6%96%B0%E9%A2%86%E6%B1%87%E8%B4%AD%E7%89%A9%E5%B9%BF%E5%9C%BA_%E5%A1%98%E5%B0%BE%E5%BA%97_%E6%96%B0%E9%A2%86%E6%B1%87%E8%B4%AD%E7%89%A9%E4%B8%AD%E5%BF%83.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="318">
@@ -24543,9 +24543,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G318">
+      <c r="G318" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%B8%9C%E7%BF%A0%E9%9B%85%E5%B1%85%E6%96%B0%E9%A2%86%E6%B1%87%E8%B4%AD%E7%89%A9%E5%B9%BF%E5%9C%BA_%E5%A1%98%E5%B0%BE%E5%BA%97_%E6%96%B0%E9%A2%86%E6%B1%87%E8%B4%AD%E7%89%A9%E4%B8%AD%E5%BF%83.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="319">
@@ -24579,9 +24579,9 @@
           <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-4)（1处问题）</t>
         </is>
       </c>
-      <c r="G319">
+      <c r="G319" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%A6%8F%E6%B5%B7%E8%A1%97%E9%81%93%E4%B8%9C%E7%BF%A0%E9%9B%85%E5%B1%85%E6%96%B0%E9%A2%86%E6%B1%87%E8%B4%AD%E7%89%A9%E5%B9%BF%E5%9C%BA_%E5%A1%98%E5%B0%BE%E5%BA%97_%E6%96%B0%E9%A2%86%E6%B1%87%E8%B4%AD%E7%89%A9%E4%B8%AD%E5%BF%83.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="320">
@@ -24615,9 +24615,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G320">
+      <c r="G320" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E8%9B%87%E5%8F%A3%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%AD%E5%BF%83%E8%B7%AF%E6%AE%B5%E5%90%89%E7%A5%A5%E9%BE%99%E8%8A%B1%E5%9B%AD_%E5%90%89%E7%A5%A5%E9%BE%99%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="321">
@@ -24651,9 +24651,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G321">
+      <c r="G321" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E8%9B%87%E5%8F%A3%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%AD%E5%BF%83%E8%B7%AF%E6%AE%B5%E5%90%89%E7%A5%A5%E9%BE%99%E8%8A%B1%E5%9B%AD_%E5%90%89%E7%A5%A5%E9%BE%99%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="322">
@@ -24687,9 +24687,9 @@
           <t>（4）其他问题说明（备注描述）(-1)（2处问题）</t>
         </is>
       </c>
-      <c r="G322">
+      <c r="G322" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E8%9B%87%E5%8F%A3%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%AD%E5%BF%83%E8%B7%AF%E6%AE%B5%E5%90%89%E7%A5%A5%E9%BE%99%E8%8A%B1%E5%9B%AD_%E5%90%89%E7%A5%A5%E9%BE%99%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="323">
@@ -24723,9 +24723,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G323">
+      <c r="G323" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E8%9B%87%E5%8F%A3%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%AD%E5%BF%83%E8%B7%AF%E6%AE%B5%E5%90%89%E7%A5%A5%E9%BE%99%E8%8A%B1%E5%9B%AD_%E5%90%89%E7%A5%A5%E9%BE%99%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="324">
@@ -24759,9 +24759,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（2处问题）； （3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G324">
+      <c r="G324" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E8%9B%87%E5%8F%A3%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%AD%E5%BF%83%E8%B7%AF%E6%AE%B5%E5%90%89%E7%A5%A5%E9%BE%99%E8%8A%B1%E5%9B%AD_%E5%90%89%E7%A5%A5%E9%BE%99%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="325">
@@ -24795,9 +24795,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G325">
+      <c r="G325" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E8%9B%87%E5%8F%A3%E5%90%8E%E6%B5%B7%E6%BB%A8%E8%B7%AF%E4%B8%AD%E5%BF%83%E8%B7%AF%E6%AE%B5%E5%90%89%E7%A5%A5%E9%BE%99%E8%8A%B1%E5%9B%AD_%E5%90%89%E7%A5%A5%E9%BE%99%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="326">
@@ -24831,9 +24831,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G326">
+      <c r="G326" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E8%9B%87%E5%8F%A3%E8%A1%97%E9%81%93%E9%A6%99%E6%82%A6%E9%87%8C_%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E%E8%8A%B1%E5%9B%AD_%E4%BA%8C%E6%9C%9F_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="327">
@@ -24867,9 +24867,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）； （4）分类设施存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G327">
+      <c r="G327" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E8%9B%87%E5%8F%A3%E8%A1%97%E9%81%93%E9%A6%99%E6%82%A6%E9%87%8C_%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E%E8%8A%B1%E5%9B%AD_%E4%BA%8C%E6%9C%9F_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="328">
@@ -24903,9 +24903,9 @@
           <t>（4）其他问题说明（备注描述）(-1)（2处问题）</t>
         </is>
       </c>
-      <c r="G328">
+      <c r="G328" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E8%9B%87%E5%8F%A3%E8%A1%97%E9%81%93%E9%A6%99%E6%82%A6%E9%87%8C_%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E%E8%8A%B1%E5%9B%AD_%E4%BA%8C%E6%9C%9F_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="329">
@@ -24939,9 +24939,9 @@
           <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G329">
+      <c r="G329" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E8%9B%87%E5%8F%A3%E8%A1%97%E9%81%93%E9%A6%99%E6%82%A6%E9%87%8C_%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E%E8%8A%B1%E5%9B%AD_%E4%BA%8C%E6%9C%9F_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="330">
@@ -24975,9 +24975,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）； （3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G330">
+      <c r="G330" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E8%9B%87%E5%8F%A3%E8%A1%97%E9%81%93%E9%A6%99%E6%82%A6%E9%87%8C_%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E%E8%8A%B1%E5%9B%AD_%E4%BA%8C%E6%9C%9F_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="331">
@@ -25011,9 +25011,9 @@
           <t>（4）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G331">
+      <c r="G331" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E8%9B%87%E5%8F%A3%E8%A1%97%E9%81%93%E9%A6%99%E6%82%A6%E9%87%8C_%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E%E8%8A%B1%E5%9B%AD_%E4%BA%8C%E6%9C%9F_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="332">
@@ -25047,9 +25047,9 @@
           <t>（2）收集容器缺失(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G332">
+      <c r="G332" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E4%B8%AD%E5%BF%83%E8%B7%AF%E9%A6%99%E6%82%A6%E9%87%8C_%E9%A6%99%E6%82%A6%E9%87%8C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="333">
@@ -25083,9 +25083,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（4处问题）</t>
         </is>
       </c>
-      <c r="G333">
+      <c r="G333" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E4%B8%AD%E5%BF%83%E8%B7%AF%E9%A6%99%E6%82%A6%E9%87%8C_%E9%A6%99%E6%82%A6%E9%87%8C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="334">
@@ -25119,9 +25119,9 @@
           <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-4)（1处问题）</t>
         </is>
       </c>
-      <c r="G334">
+      <c r="G334" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E4%B8%AD%E5%BF%83%E8%B7%AF%E9%A6%99%E6%82%A6%E9%87%8C_%E9%A6%99%E6%82%A6%E9%87%8C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="335">
@@ -25155,9 +25155,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）； （3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G335">
+      <c r="G335" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%8D%97%E5%B1%B1%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E_%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E%E8%8A%B1%E5%9B%AD_%E4%B8%80%E6%9C%9F_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="336">
@@ -25191,9 +25191,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G336">
+      <c r="G336" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%8D%97%E5%B1%B1%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E_%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E%E8%8A%B1%E5%9B%AD_%E4%B8%80%E6%9C%9F_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="337">
@@ -25227,9 +25227,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G337">
+      <c r="G337" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%8D%97%E5%B1%B1%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E_%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E%E8%8A%B1%E5%9B%AD_%E4%B8%80%E6%9C%9F_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="338">
@@ -25263,9 +25263,9 @@
           <t>（2）未使用(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G338">
+      <c r="G338" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%8D%97%E5%B1%B1%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E_%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E%E8%8A%B1%E5%9B%AD_%E4%B8%80%E6%9C%9F_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="339">
@@ -25299,9 +25299,9 @@
           <t>周边环境脏乱(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G339">
+      <c r="G339" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E5%8D%97%E5%B1%B1%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E_%E6%81%92%E8%A3%95%E6%BB%A8%E5%9F%8E%E8%8A%B1%E5%9B%AD_%E4%B8%80%E6%9C%9F_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="340">
@@ -25335,9 +25335,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G340">
+      <c r="G340" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BB%BF%E6%B5%B7%E6%B9%BE_%E7%BB%BF%E6%B5%B7%E6%B9%BE.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="341">
@@ -25371,9 +25371,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G341">
+      <c r="G341" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BB%BF%E6%B5%B7%E6%B9%BE_%E7%BB%BF%E6%B5%B7%E6%B9%BE.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="342">
@@ -25407,9 +25407,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G342">
+      <c r="G342" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BB%BF%E6%B5%B7%E6%B9%BE_%E7%BB%BF%E6%B5%B7%E6%B9%BE.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="343">
@@ -25443,9 +25443,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G343">
+      <c r="G343" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BB%BF%E6%B5%B7%E6%B9%BE_%E7%BB%BF%E6%B5%B7%E6%B9%BE.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="344">
@@ -25479,9 +25479,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G344">
+      <c r="G344" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-10/venue/v-%E7%BB%BF%E6%B5%B7%E6%B9%BE_%E7%BB%BF%E6%B5%B7%E6%B9%BE.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
   </sheetData>

--- a/weeks/2026-09-10/巡查表.xlsx
+++ b/weeks/2026-09-10/巡查表.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Z105"/>
+  <dimension ref="A2:Z114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13181,6 +13181,559 @@
       <c r="Z105" t="inlineStr">
         <is>
           <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>马坑</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>龙岗区</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>南澳街道</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>广东省深圳市龙岗区南澳街道南澳派出所辖区工作点大鹏新区</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>1.6: 设置洗手设施。（2分） (-1)
+1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（6分） (-3)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
+2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
+2.3: 各类垃圾及时清运。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O106" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(6项/6张)</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>88</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:01:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>南澳湾花园</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>龙岗区</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>南澳街道</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>广东省深圳市龙岗区南澳街道南澳湾花园</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
+2.3: 各类垃圾及时清运。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O107" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(2项/2张)</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>96</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:02:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>老街</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>龙岗区</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>南澳街道</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>广东省深圳市龙岗区南澳街道南澳湾花园大鹏新区</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
+2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
+2.3: 各类垃圾及时清运。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O108" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(3项/4张)</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>94</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:02:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>风球山小区</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>龙岗区</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>南澳街道</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>广东省深圳市龙岗区南澳街道风球山小区</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
+2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
+2.3: 各类垃圾及时清运。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O109" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(3项/3张)</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>94</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>上企沙</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>龙岗区</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>南澳街道</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>广东省深圳市龙岗区南澳街道上企沙大鹏新区</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
+        </is>
+      </c>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(1项/1张)</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>98</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:02:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>山海名苑</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>龙岗区</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>南澳街道</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>广东省深圳市龙岗区南澳街道山海名苑</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-4)</t>
+        </is>
+      </c>
+      <c r="O111" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(1项/2张)</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>96</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:02:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>下企沙</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>龙岗区</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>南澳街道</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>广东省深圳市龙岗区南澳街道企沙下路大鹏新区</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
+        </is>
+      </c>
+      <c r="O112" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(1项/2张)</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>98</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>2026-09-16 14:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>金地朗悦西区</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>坪山区</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>马峦街道</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>坪山区马峦街道金地朗悦西区3栋集中分类投放点</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-4)
+1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O113" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(3项/5张)</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>92</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:11:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>金地朗悦东区</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>坪山区</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>马峦街道</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>坪山区马峦街道金地朗悦东区1栋集中分类投放点</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>1.6: 设置洗手设施。（2分） (-1)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O114" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(2项/3张)</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>97</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:11:47</t>
         </is>
       </c>
     </row>
@@ -13289,6 +13842,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId112"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13300,7 +13862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G344"/>
+  <dimension ref="A1:G366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23704,7 +24266,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F315" s="6" t="inlineStr"/>
+      <c r="F315" s="6" t="inlineStr">
+        <is>
+          <t>（2）未成组摆放两分类收集容器(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G315" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23737,7 +24303,11 @@
           <t>-5</t>
         </is>
       </c>
-      <c r="F316" s="6" t="inlineStr"/>
+      <c r="F316" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-5)（1处问题）</t>
+        </is>
+      </c>
       <c r="G316" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23770,7 +24340,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F317" s="6" t="inlineStr"/>
+      <c r="F317" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失</t>
+        </is>
+      </c>
       <c r="G317" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23803,7 +24377,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F318" s="6" t="inlineStr"/>
+      <c r="F318" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G318" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23836,7 +24414,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F319" s="6" t="inlineStr"/>
+      <c r="F319" s="6" t="inlineStr">
+        <is>
+          <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-4)（1处问题）</t>
+        </is>
+      </c>
       <c r="G319" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24663,6 +25245,820 @@
       </c>
       <c r="F344" s="6" t="inlineStr"/>
       <c r="G344" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>马坑</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D345" s="6" t="inlineStr">
+        <is>
+          <t>设置洗手设施。（2分）</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F345" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G345" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>马坑</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D346" s="6" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（6分）</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="F346" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G346" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>马坑</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D347" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F347" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G347" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>马坑</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D348" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F348" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G348" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>马坑</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D349" s="6" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F349" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G349" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>马坑</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D350" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F350" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G350" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>南澳湾花园</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D351" s="6" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F351" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G351" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>南澳湾花园</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D352" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F352" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G352" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>老街</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D353" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F353" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G353" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>老街</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D354" s="6" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F354" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G354" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>老街</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D355" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F355" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G355" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>风球山小区</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D356" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F356" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G356" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>风球山小区</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D357" s="6" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F357" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G357" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>风球山小区</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D358" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F358" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G358" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>上企沙</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D359" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F359" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G359" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>山海名苑</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D360" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F360" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G360" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>下企沙</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D361" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F361" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G361" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>金地朗悦西区</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D362" s="6" t="inlineStr">
+        <is>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F362" s="6" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G362" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>金地朗悦西区</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D363" s="6" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F363" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G363" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>金地朗悦西区</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D364" s="6" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F364" s="6" t="inlineStr">
+        <is>
+          <t>（2）围挡设置不规范（未设置围挡，围挡封闭不全，或使用移动式栅栏、水马等围合）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G364" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>金地朗悦东区</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D365" s="6" t="inlineStr">
+        <is>
+          <t>设置洗手设施。（2分）</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F365" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G365" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>金地朗悦东区</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D366" s="6" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F366" s="6" t="inlineStr">
+        <is>
+          <t>（2）围挡设置不规范（未设置围挡，围挡封闭不全，或使用移动式栅栏、水马等围合）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G366" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
         </is>
@@ -25013,6 +26409,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId341"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId342"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G366" r:id="rId365"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/weeks/2026-09-10/巡查表.xlsx
+++ b/weeks/2026-09-10/巡查表.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Z114"/>
+  <dimension ref="A2:Z157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13187,35 +13187,1597 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>和平大厦</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>龙华区</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>龙华街道</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>景龙社区</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>深圳市龙华区龙华街道景龙社区和平大厦</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O106" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(1项/2张)</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>98</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>2026-09-17 10:27:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>丹枫雅苑</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>龙华区</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>龙华街道</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>景龙社区</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>龙华区龙华街道景龙社区丹枫雅苑</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-2)
+1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+1.12: 桶柜式垃圾投放点柜门应全天保持关闭（作业状态除外）。（4分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O107" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(5项/5张)</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>90</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>2026-09-17 10:27:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>江南华府</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>龙华区</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>龙华街道</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>景龙社区</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>龙华区龙华街道景龙社区江南华府</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>1.16: 禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分） (-4)</t>
+        </is>
+      </c>
+      <c r="O108" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(1项/2张)</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>96</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>2026-09-17 10:27:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>嘉逸花园</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>龙华区</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>龙华街道</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>景龙社区</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>龙华区龙华街道景龙社区嘉逸花园</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+1.16: 禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分） (-2)</t>
+        </is>
+      </c>
+      <c r="O109" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(3项/3张)</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>94</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>2026-09-17 10:27:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>东华明珠园</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>龙华区</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>龙华街道</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>景龙社区</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>龙华区龙华街道景龙社区东华明珠园</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>1.16: 禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分） (-4)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-6)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(3项/9张)</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>88</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>2026-09-17 10:27:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>城中村</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>樟坑村（三区）</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>龙华区</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>民治街道</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>樟坑社区</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>龙华区民治街道樟坑社区樟坑村3区</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>1.4: 至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分） (-2)
+1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-2)
+1.6: 设置洗手设施。（2分） (-2)
+1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-4)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
+4.5: 回收箱及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O111" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(7项/12张)</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>84</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>2026-09-17 10:26:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>樟坑村（一区）</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>龙华区</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>民治街道</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>樟坑社区</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>龙华区民治街道樟坑社区樟坑村1区</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>1.4: 至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分） (-2)
+1.6: 设置洗手设施。（2分） (-2)
+1.9: 各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分） (-4)
+1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（6分） (-3)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-6)
+1.18: 禁止在楼层、地面或车库等设置分散式垃圾收集容器。（4分） (-5)</t>
+        </is>
+      </c>
+      <c r="O112" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(6项/16张)</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>78</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:37:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>南景新村</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>龙华区</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>民治街道</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>樟坑社区</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>深圳市龙华区民治街道樟坑社区南景新村</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>1.2: 至少设置一处有害垃圾收集容器。（2分） (-2)
+1.4: 至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分） (-2)
+1.6: 设置洗手设施。（2分） (-2)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-6)</t>
+        </is>
+      </c>
+      <c r="O113" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(5项/12张)</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>86</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:20:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>樟坑村（二区）</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>龙华区</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>民治街道</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>樟坑社区</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>龙华区民治街道樟坑社区樟坑村2区</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>1.2: 至少设置一处有害垃圾收集容器。（2分） (-2)
+1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-2)
+1.6: 设置洗手设施。（2分） (-1)
+1.12: 桶柜式垃圾投放点柜门应全天保持关闭（作业状态除外）。（4分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
+        </is>
+      </c>
+      <c r="O114" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(5项/6张)</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>91</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:20:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>樟坑老村</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>龙华区</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>民治街道</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>樟坑社区</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>龙华区民治街道樟坑社区樟坑老村</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>1.4: 至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分） (-2)
+1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-4)
+1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+5.1: 公共区域宣传栏张贴垃圾分类投放指引或宣传海报。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O115" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(4项/6张)</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>90</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:20:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>竹园村</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>坪山区</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>马峦街道</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>江岭社区</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>坪山区马峦街道江岭社区竹元村</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+3.1: 各类垃圾及时清运。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O116" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(2项/3张)</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>96</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:21:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>丰华苑</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>深圳市宝安区洪浪北路61号</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O117" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(3项/3张)</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>94</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:37:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TATA公寓</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>深圳市宝安区新安三路h102号附近</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+6.1: 公共区域宣传栏张贴垃圾分类投放指引或宣传海报。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O118" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(2项/3张)</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>96</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:37:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>华联城市全景</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>深圳华联城市全景</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-4)</t>
+        </is>
+      </c>
+      <c r="O119" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(1项/2张)</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>96</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:37:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>嘉洲商务中心</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>深圳市宝安区嘉州商务中心</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-4)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-4)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O120" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(4项/6张)</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>88</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:37:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>云顶嘉园</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>新安街道</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>深圳市宝安区新安街道云顶嘉园</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O121" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(3项/3张)</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>94</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:37:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>鸿景园</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>新安街道</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>深圳市宝安区新安街道鸿景园</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-2)
+1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+2.3: 各类垃圾及时清运。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)
+3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O122" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(6项/11张)</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>88</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:37:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>欣荔苑</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>南山区</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>南山区工业八路兴工路11号</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O123" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(2项/3张)</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>96</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:39:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>餐饮场所</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>庄周过水鱼</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>南山区</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>南山区兴工路8号</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>1.3: 各类收集容器的分类标志完整、正确、清晰。 （18分） (-12)</t>
+        </is>
+      </c>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(1项/4张)</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>88</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:38:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>深圳市南山区雍景湾幼儿园</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>南山区</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>深圳市南山区雍景湾幼儿园</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>1.2: 用餐区摆放厨余垃圾、其他垃圾收集容器。（4分） (-4)
+1.3: 后厨区摆放可回收物、厨余垃圾、其他垃圾收集容器。（4分） (-4)
+1.4: 洗手间摆放其他垃圾收集容器。（6分） (-3)
+1.6: 各类收集容器的分类标志完整、正确、清晰。 （12分） (-9)
+2.2: 收集容器、暂存点及其周围环境干净整洁，无垃圾满溢、暴露垃圾，无杂物堆放。（9分） (-6)
+3.5: 每年至少开展一次全校性生活垃圾分类主题活动。 （3分） (-3)</t>
+        </is>
+      </c>
+      <c r="O125" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(6项/12张)</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>71</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:38:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>机关事业单位办公场所</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>招商街道办</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>南山区</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>招商街道</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>广东省深圳市南山区招商街道近海路半岛花园</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>1.6: 各类收集容器的分类标志完整、正确、清晰。 （12分） (-6)
+3.1: 公共区域张贴或摆放垃圾分类宣传海报或指引等。（4分） (-4)</t>
+        </is>
+      </c>
+      <c r="O126" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(2项/4张)</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>87</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:38:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>源华综合楼</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>南山区</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>南山区荔园路51号</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+2.3: 各类垃圾及时清运。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O127" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(2项/3张)</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>96</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:38:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>翠薇园小区</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>南山区</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>南山区工业八路197号</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>1.1: 设置集中分类投放点，摆放可回收物、厨余垃圾、其他垃圾三类收集容器。（6分） (-2)
+2.3: 各类垃圾及时清运。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O128" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(2项/2张)</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>96</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:38:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>玫瑰园小区</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>南山区</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>招商街道</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>广东省深圳市南山区招商街道玫瑰园(工业八路)</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+2.3: 各类垃圾及时清运。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O129" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(4项/4张)</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>92</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:37:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>枫南</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>龙岗区</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>南澳街道</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>广东省深圳市龙岗区南澳街道关厂小区</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
+2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O130" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(2项/3张)</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>96</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>2026-09-17 09:39:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
         <is>
           <t>马坑</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>龙岗区</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>南澳街道</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>广东省深圳市龙岗区南澳街道南澳派出所辖区工作点大鹏新区</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr">
+      <c r="N131" t="inlineStr">
         <is>
           <t>1.6: 设置洗手设施。（2分） (-1)
 1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（6分） (-3)
@@ -13225,515 +14787,1558 @@
 2.3: 各类垃圾及时清运。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O106" s="4" t="inlineStr">
+      <c r="O131" s="4" t="inlineStr">
         <is>
           <t>查看证据(6项/6张)</t>
         </is>
       </c>
-      <c r="P106" t="n">
+      <c r="P131" t="n">
         <v>88</v>
       </c>
-      <c r="T106" t="inlineStr">
+      <c r="T131" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="U131" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="V106" t="inlineStr">
+      <c r="V131" t="inlineStr">
         <is>
           <t>2026-09-16 14:01:54</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>住宅小区</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
         <is>
           <t>南澳湾花园</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>龙岗区</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>南澳街道</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>广东省深圳市龙岗区南澳街道南澳湾花园</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr">
+      <c r="N132" t="inlineStr">
         <is>
           <t>2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
 2.3: 各类垃圾及时清运。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O107" s="4" t="inlineStr">
+      <c r="O132" s="4" t="inlineStr">
         <is>
           <t>查看证据(2项/2张)</t>
         </is>
       </c>
-      <c r="P107" t="n">
+      <c r="P132" t="n">
         <v>96</v>
       </c>
-      <c r="T107" t="inlineStr">
+      <c r="T132" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="U132" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="V107" t="inlineStr">
+      <c r="V132" t="inlineStr">
         <is>
           <t>2026-09-16 14:02:04</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>城中村</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>老街</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>龙岗区</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>南澳街道</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>广东省深圳市龙岗区南澳街道南澳湾花园大鹏新区</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr">
+      <c r="N133" t="inlineStr">
         <is>
           <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
 2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
 2.3: 各类垃圾及时清运。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O108" s="4" t="inlineStr">
+      <c r="O133" s="4" t="inlineStr">
         <is>
           <t>查看证据(3项/4张)</t>
         </is>
       </c>
-      <c r="P108" t="n">
+      <c r="P133" t="n">
         <v>94</v>
       </c>
-      <c r="T108" t="inlineStr">
+      <c r="T133" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="U133" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="V108" t="inlineStr">
+      <c r="V133" t="inlineStr">
         <is>
           <t>2026-09-16 14:02:12</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>城中村</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>风球山小区</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>龙岗区</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>南澳街道</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>广东省深圳市龙岗区南澳街道风球山小区</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr">
+      <c r="N134" t="inlineStr">
         <is>
           <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
 2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
 2.3: 各类垃圾及时清运。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O109" s="4" t="inlineStr">
+      <c r="O134" s="4" t="inlineStr">
         <is>
           <t>查看证据(3项/3张)</t>
         </is>
       </c>
-      <c r="P109" t="n">
+      <c r="P134" t="n">
         <v>94</v>
       </c>
-      <c r="T109" t="inlineStr">
+      <c r="T134" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="U134" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="V109" t="inlineStr">
+      <c r="V134" t="inlineStr">
         <is>
           <t>2026-09-16 14:02:15</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>城中村</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>上企沙</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>龙岗区</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>南澳街道</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>广东省深圳市龙岗区南澳街道上企沙大鹏新区</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr">
+      <c r="N135" t="inlineStr">
         <is>
           <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O110" s="4" t="inlineStr">
+      <c r="O135" s="4" t="inlineStr">
         <is>
           <t>查看证据(1项/1张)</t>
         </is>
       </c>
-      <c r="P110" t="n">
+      <c r="P135" t="n">
         <v>98</v>
       </c>
-      <c r="T110" t="inlineStr">
+      <c r="T135" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="U135" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="V110" t="inlineStr">
+      <c r="V135" t="inlineStr">
         <is>
           <t>2026-09-16 14:02:18</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>住宅小区</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
         <is>
           <t>山海名苑</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>龙岗区</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>南澳街道</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F136" t="inlineStr">
         <is>
           <t>广东省深圳市龙岗区南澳街道山海名苑</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr">
+      <c r="N136" t="inlineStr">
         <is>
           <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-4)</t>
         </is>
       </c>
-      <c r="O111" s="4" t="inlineStr">
+      <c r="O136" s="4" t="inlineStr">
         <is>
           <t>查看证据(1项/2张)</t>
         </is>
       </c>
-      <c r="P111" t="n">
+      <c r="P136" t="n">
         <v>96</v>
       </c>
-      <c r="T111" t="inlineStr">
+      <c r="T136" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="U136" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="V111" t="inlineStr">
+      <c r="V136" t="inlineStr">
         <is>
           <t>2026-09-16 14:02:22</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>城中村</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>下企沙</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>龙岗区</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>南澳街道</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>广东省深圳市龙岗区南澳街道企沙下路大鹏新区</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr">
+      <c r="N137" t="inlineStr">
         <is>
           <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O112" s="4" t="inlineStr">
+      <c r="O137" s="4" t="inlineStr">
         <is>
           <t>查看证据(1项/2张)</t>
         </is>
       </c>
-      <c r="P112" t="n">
+      <c r="P137" t="n">
         <v>98</v>
       </c>
-      <c r="T112" t="inlineStr">
+      <c r="T137" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="U137" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="V112" t="inlineStr">
+      <c r="V137" t="inlineStr">
         <is>
           <t>2026-09-16 14:02:25</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>住宅小区</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
         <is>
           <t>金地朗悦西区</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>坪山区</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>马峦街道</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>坪山区马峦街道金地朗悦西区3栋集中分类投放点</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr">
+      <c r="N138" t="inlineStr">
         <is>
           <t>1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-4)
 1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O113" s="4" t="inlineStr">
+      <c r="O138" s="4" t="inlineStr">
         <is>
           <t>查看证据(3项/5张)</t>
         </is>
       </c>
-      <c r="P113" t="n">
+      <c r="P138" t="n">
         <v>92</v>
       </c>
-      <c r="T113" t="inlineStr">
+      <c r="T138" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="U138" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="V113" t="inlineStr">
+      <c r="V138" t="inlineStr">
         <is>
           <t>2026-09-16 12:11:41</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>住宅小区</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
         <is>
           <t>金地朗悦东区</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>坪山区</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>马峦街道</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>坪山区马峦街道金地朗悦东区1栋集中分类投放点</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr">
+      <c r="N139" t="inlineStr">
         <is>
           <t>1.6: 设置洗手设施。（2分） (-1)
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O114" s="4" t="inlineStr">
+      <c r="O139" s="4" t="inlineStr">
         <is>
           <t>查看证据(2项/3张)</t>
         </is>
       </c>
-      <c r="P114" t="n">
+      <c r="P139" t="n">
         <v>97</v>
       </c>
-      <c r="T114" t="inlineStr">
+      <c r="T139" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="U139" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="V114" t="inlineStr">
+      <c r="V139" t="inlineStr">
         <is>
           <t>2026-09-16 12:11:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>都市阳光名苑</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>深南大道6017号</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+6.1: 公共区域宣传栏张贴垃圾分类投放指引或宣传海报。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O140" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(3项/4张)</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>94</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:11:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>深圳安华工业区（住宅）</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>福田区</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>沙头街道</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>广东省深圳市福田区沙头街道深圳安华工业区(泰然八路)</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>1.16: 禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-6)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O141" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(4项/9张)</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>88</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>龙园创展大厦</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>宝安南路2010号</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
+2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)
+3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O142" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(5项/5张)</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>90</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:12:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>供电北小区</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>罗湖区</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>深圳市罗湖区河边路1号</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O143" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(3项/3张)</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>94</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:41:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>中医院小区</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>河边路5号</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+1.16: 禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O144" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(6项/8张)</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>88</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:41:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>顺基楼</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>解放路3017号</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O145" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(3项/6张)</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>94</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:42:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>医疗机构</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>泰源社区健康服务中心</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>泰然四路123号</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>1.1: 公共区域成组摆放可回收物、其他垃圾收集容器。（12分） (-3)
+1.5: 至少设置一处有害垃圾收集容器。（5分） (-5)
+3.1: 公共区域张贴或摆放垃圾分类宣传海报或指引等。 （5分） (-5)</t>
+        </is>
+      </c>
+      <c r="O146" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(3项/3张)</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>87</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:42:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>玉律一区</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>光明区</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>玉塘街道</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>广东省深圳市光明区玉塘街道玉泉西路110号</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>1.6: 设置洗手设施。（2分） (-1)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-4)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O147" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(3项/4张)</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>93</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:41:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>天安高尔夫花园</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>福田区</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>沙头街道</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>天安社区</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>深圳市福田区沙头街道天安社区天安高尔夫花园</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>1.4: 至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分） (-2)
+1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+1.12: 桶柜式垃圾投放点柜门应全天保持关闭（作业状态除外）。（4分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O148" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(4项/8张)</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>92</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:42:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>玉律二区</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>光明区</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>玉塘街道</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>深圳市光明区玉塘街道环玉路玉律广场西北侧约70米</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>1.6: 设置洗手设施。（2分） (-2)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-6)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-6)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O149" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(4项/12张)</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>84</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:12:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>天安数码城（智慧园）</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>福田区</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>沙头街道</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>广东省深圳市福田区沙头街道昌泰公寓</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+1.16: 禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分） (-4)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O150" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(4项/14张)</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>90</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:42:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>港岛银座</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>解放路3002号</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O151" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(2项/2张)</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>96</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:42:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>和平广场</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>和平路3009号</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)
+4.3: 设备齐全完好，摆放整齐有序，功能正常，外观没有严重破损，没有用电隐患。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O152" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(5项/6张)</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>90</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:42:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>鸿隆世纪广场</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>深南东路4002号</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>1.16: 禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
+        </is>
+      </c>
+      <c r="O153" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(2项/2张)</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>96</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:42:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>塘下涌一村</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>深圳市宝安区塘下涌一村</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>1.9: 各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分） (-6)
+3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O154" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(2项/6张)</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>92</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:42:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>购物中心</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>盛客隆商场</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>燕罗街道</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>塘下涌社区</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>深圳市宝安区燕罗街道塘下涌社区众福路16号</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>1.2: 生活（果蔬）超市摆放厨余垃圾、其他垃圾收集容器。 (-5)
+1.5: 至少设置一处有害垃圾收集容器。 (0)
+2.2: 收集容器、暂存点及其周围环境干净整洁，无垃圾满溢、暴露垃圾，无杂物堆放。 (-3)
+2.3: 将各类垃圾分类收集、暂存和移交。 (-5)
+3.1: 公共区域张贴或摆放垃圾分类宣传海报或指引等。 (-4)</t>
+        </is>
+      </c>
+      <c r="O155" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(5项/7张)</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>83</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:42:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>集贸市场</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>塘下涌综合市场</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>燕罗街道</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>广东省深圳市宝安区燕罗街道众福路66号塘下涌农贸市场</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>1.1: 公共区域摆放可回收物、厨余垃圾、其他垃圾收集容器；垃圾暂存点摆放可回收物、厨余垃圾、其他垃圾和有害垃圾收集容器。 (-3)
+1.3: 各类收集容器的分类标志完整、正确、清晰。 (-3)
+1.4: 各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题。 (-3)
+2.3: 将各类垃圾分类收集、暂存和移交。 (-5)</t>
+        </is>
+      </c>
+      <c r="O156" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(4项/4张)</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>86</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:42:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>塘下涌二村</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>深圳市宝安区塘下涌二村</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>1.6: 设置洗手设施。（2分） (-2)
+1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+1.9: 各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分） (-6)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)</t>
+        </is>
+      </c>
+      <c r="O157" s="4" t="inlineStr">
+        <is>
+          <t>查看证据(4项/10张)</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>88</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:42:26</t>
         </is>
       </c>
     </row>
@@ -13851,6 +16456,49 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId155"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13862,7 +16510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G366"/>
+  <dimension ref="A1:G514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -25253,32 +27901,32 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>城中村</t>
+          <t>住宅小区</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>马坑</t>
+          <t>和平大厦</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D345" s="6" t="inlineStr">
         <is>
-          <t>设置洗手设施。（2分）</t>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G345" s="4" t="inlineStr">
@@ -25290,32 +27938,32 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>城中村</t>
+          <t>住宅小区</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>马坑</t>
+          <t>丹枫雅苑</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D346" s="6" t="inlineStr">
         <is>
-          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（6分）</t>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G346" s="4" t="inlineStr">
@@ -25327,22 +27975,22 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>城中村</t>
+          <t>住宅小区</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>马坑</t>
+          <t>丹枫雅苑</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D347" s="6" t="inlineStr">
         <is>
-          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -25352,7 +28000,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G347" s="4" t="inlineStr">
@@ -25364,22 +28012,22 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>城中村</t>
+          <t>住宅小区</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>马坑</t>
+          <t>丹枫雅苑</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D348" s="6" t="inlineStr">
         <is>
-          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+          <t>桶柜式垃圾投放点柜门应全天保持关闭（作业状态除外）。（4分）</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -25389,7 +28037,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+          <t>（2）柜门未保持关闭(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G348" s="4" t="inlineStr">
@@ -25401,22 +28049,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>城中村</t>
+          <t>住宅小区</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>马坑</t>
+          <t>丹枫雅苑</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D349" s="6" t="inlineStr">
         <is>
-          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -25426,7 +28074,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G349" s="4" t="inlineStr">
@@ -25438,22 +28086,22 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>城中村</t>
+          <t>住宅小区</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>马坑</t>
+          <t>丹枫雅苑</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="D350" s="6" t="inlineStr">
         <is>
-          <t>各类垃圾及时清运。（2分）</t>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -25463,7 +28111,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G350" s="4" t="inlineStr">
@@ -25480,27 +28128,27 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>南澳湾花园</t>
+          <t>江南华府</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D351" s="6" t="inlineStr">
         <is>
-          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+          <t>禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分）</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+          <t>（2）投放口被封闭或遮挡(-2)（1处问题）； （3）内桶未开盖(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G351" s="4" t="inlineStr">
@@ -25517,17 +28165,17 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>南澳湾花园</t>
+          <t>嘉逸花园</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D352" s="6" t="inlineStr">
         <is>
-          <t>各类垃圾及时清运。（2分）</t>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -25537,7 +28185,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+          <t>（2）责任公示牌缺失(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G352" s="4" t="inlineStr">
@@ -25549,22 +28197,22 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>城中村</t>
+          <t>住宅小区</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>老街</t>
+          <t>嘉逸花园</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="D353" s="6" t="inlineStr">
         <is>
-          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -25574,7 +28222,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G353" s="4" t="inlineStr">
@@ -25586,22 +28234,22 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>城中村</t>
+          <t>住宅小区</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>老街</t>
+          <t>嘉逸花园</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D354" s="6" t="inlineStr">
         <is>
-          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+          <t>禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分）</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -25611,7 +28259,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+          <t>（2）投放口被封闭或遮挡(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G354" s="4" t="inlineStr">
@@ -25623,32 +28271,32 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>城中村</t>
+          <t>住宅小区</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>老街</t>
+          <t>东华明珠园</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D355" s="6" t="inlineStr">
         <is>
-          <t>各类垃圾及时清运。（2分）</t>
+          <t>禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分）</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+          <t>（2）投放口被封闭或遮挡(-2)（2处问题）</t>
         </is>
       </c>
       <c r="G355" s="4" t="inlineStr">
@@ -25660,12 +28308,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>城中村</t>
+          <t>住宅小区</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>风球山小区</t>
+          <t>东华明珠园</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -25680,12 +28328,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（5处问题）</t>
         </is>
       </c>
       <c r="G356" s="4" t="inlineStr">
@@ -25697,22 +28345,22 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>城中村</t>
+          <t>住宅小区</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>风球山小区</t>
+          <t>东华明珠园</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D357" s="6" t="inlineStr">
         <is>
-          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -25722,7 +28370,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G357" s="4" t="inlineStr">
@@ -25739,17 +28387,17 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>风球山小区</t>
+          <t>樟坑村（三区）</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D358" s="6" t="inlineStr">
         <is>
-          <t>各类垃圾及时清运。（2分）</t>
+          <t>至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分）</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -25759,7 +28407,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+          <t>否(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G358" s="4" t="inlineStr">
@@ -25776,17 +28424,17 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>上企沙</t>
+          <t>樟坑村（三区）</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="D359" s="6" t="inlineStr">
         <is>
-          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -25796,7 +28444,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G359" s="4" t="inlineStr">
@@ -25808,32 +28456,32 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>住宅小区</t>
+          <t>城中村</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>山海名苑</t>
+          <t>樟坑村（三区）</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D360" s="6" t="inlineStr">
         <is>
-          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+          <t>设置洗手设施。（2分）</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（2处问题）</t>
         </is>
       </c>
       <c r="G360" s="4" t="inlineStr">
@@ -25850,27 +28498,27 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>下企沙</t>
+          <t>樟坑村（三区）</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D361" s="6" t="inlineStr">
         <is>
-          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（3处问题）</t>
         </is>
       </c>
       <c r="G361" s="4" t="inlineStr">
@@ -25882,32 +28530,32 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>住宅小区</t>
+          <t>城中村</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>金地朗悦西区</t>
+          <t>樟坑村（三区）</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="D362" s="6" t="inlineStr">
         <is>
-          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（2处问题）</t>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G362" s="4" t="inlineStr">
@@ -25919,22 +28567,22 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>住宅小区</t>
+          <t>城中村</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>金地朗悦西区</t>
+          <t>樟坑村（三区）</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="D363" s="6" t="inlineStr">
         <is>
-          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -25944,7 +28592,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G363" s="4" t="inlineStr">
@@ -25956,22 +28604,22 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>住宅小区</t>
+          <t>城中村</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>金地朗悦西区</t>
+          <t>樟坑村（三区）</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="D364" s="6" t="inlineStr">
         <is>
-          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+          <t>回收箱及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分）</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -25981,7 +28629,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>（2）围挡设置不规范（未设置围挡，围挡封闭不全，或使用移动式栅栏、水马等围合）(-2)（1处问题）</t>
+          <t>（3）其他问题(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G364" s="4" t="inlineStr">
@@ -25993,32 +28641,32 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>住宅小区</t>
+          <t>城中村</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>金地朗悦东区</t>
+          <t>樟坑村（一区）</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D365" s="6" t="inlineStr">
         <is>
-          <t>设置洗手设施。（2分）</t>
+          <t>至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分）</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+          <t>否(-2)（1处问题）</t>
         </is>
       </c>
       <c r="G365" s="4" t="inlineStr">
@@ -26030,35 +28678,5511 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>住宅小区</t>
+          <t>城中村</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
+          <t>樟坑村（一区）</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D366" s="6" t="inlineStr">
+        <is>
+          <t>设置洗手设施。（2分）</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F366" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（4处问题）</t>
+        </is>
+      </c>
+      <c r="G366" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>樟坑村（一区）</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="D367" s="6" t="inlineStr">
+        <is>
+          <t>各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分）</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F367" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G367" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>樟坑村（一区）</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D368" s="6" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（6分）</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="F368" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G368" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>樟坑村（一区）</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D369" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="F369" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
+        </is>
+      </c>
+      <c r="G369" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>樟坑村（一区）</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="D370" s="6" t="inlineStr">
+        <is>
+          <t>禁止在楼层、地面或车库等设置分散式垃圾收集容器。（4分）</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="F370" s="6" t="inlineStr">
+        <is>
+          <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-5)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G370" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>南景新村</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D371" s="6" t="inlineStr">
+        <is>
+          <t>至少设置一处有害垃圾收集容器。（2分）</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F371" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类收集容器缺失(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G371" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>南景新村</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D372" s="6" t="inlineStr">
+        <is>
+          <t>至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分）</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F372" s="6" t="inlineStr">
+        <is>
+          <t>否(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G372" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>南景新村</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D373" s="6" t="inlineStr">
+        <is>
+          <t>设置洗手设施。（2分）</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F373" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G373" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>南景新村</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D374" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F374" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G374" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>南景新村</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D375" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="F375" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
+        </is>
+      </c>
+      <c r="G375" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>樟坑村（二区）</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D376" s="6" t="inlineStr">
+        <is>
+          <t>至少设置一处有害垃圾收集容器。（2分）</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F376" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类收集容器缺失(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G376" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>樟坑村（二区）</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D377" s="6" t="inlineStr">
+        <is>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F377" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G377" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>樟坑村（二区）</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D378" s="6" t="inlineStr">
+        <is>
+          <t>设置洗手设施。（2分）</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F378" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G378" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>樟坑村（二区）</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="D379" s="6" t="inlineStr">
+        <is>
+          <t>桶柜式垃圾投放点柜门应全天保持关闭（作业状态除外）。（4分）</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F379" s="6" t="inlineStr">
+        <is>
+          <t>（2）柜门未保持关闭(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G379" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>樟坑村（二区）</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D380" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F380" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G380" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>樟坑老村</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D381" s="6" t="inlineStr">
+        <is>
+          <t>至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分）</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F381" s="6" t="inlineStr">
+        <is>
+          <t>否(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G381" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>樟坑老村</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D382" s="6" t="inlineStr">
+        <is>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F382" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）； （3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G382" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>樟坑老村</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D383" s="6" t="inlineStr">
+        <is>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F383" s="6" t="inlineStr">
+        <is>
+          <t>（2）责任公示牌缺失(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G383" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>樟坑老村</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="D384" s="6" t="inlineStr">
+        <is>
+          <t>公共区域宣传栏张贴垃圾分类投放指引或宣传海报。（2分）</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F384" s="6" t="inlineStr">
+        <is>
+          <t>（2）未规范张贴垃圾分类宣传海报（海报缺失、内容错误/未更新等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G384" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>竹园村</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D385" s="6" t="inlineStr">
+        <is>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F385" s="6" t="inlineStr">
+        <is>
+          <t>（2）责任公示牌缺失(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G385" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>竹园村</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D386" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F386" s="6" t="inlineStr">
+        <is>
+          <t>（1）无问题； （2）暂存点内垃圾清运不及时(-2)（1处问题）； （3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G386" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>丰华苑</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D387" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F387" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G387" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>丰华苑</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D388" s="6" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F388" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G388" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>丰华苑</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D389" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F389" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G389" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>TATA公寓</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D390" s="6" t="inlineStr">
+        <is>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F390" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G390" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>TATA公寓</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="D391" s="6" t="inlineStr">
+        <is>
+          <t>公共区域宣传栏张贴垃圾分类投放指引或宣传海报。（2分）</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F391" s="6" t="inlineStr">
+        <is>
+          <t>（2）未规范张贴垃圾分类宣传海报（海报缺失、内容错误/未更新等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G391" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>华联城市全景</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D392" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F392" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G392" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>嘉洲商务中心</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D393" s="6" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F393" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G393" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>嘉洲商务中心</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D394" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F394" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）； （3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G394" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>嘉洲商务中心</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D395" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F395" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G395" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>嘉洲商务中心</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D396" s="6" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F396" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G396" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>云顶嘉园</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D397" s="6" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F397" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G397" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>云顶嘉园</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D398" s="6" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F398" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G398" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>云顶嘉园</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D399" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F399" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G399" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>鸿景园</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D400" s="6" t="inlineStr">
+        <is>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F400" s="6" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G400" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>鸿景园</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D401" s="6" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F401" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G401" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>鸿景园</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D402" s="6" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F402" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G402" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>鸿景园</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D403" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F403" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G403" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>鸿景园</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D404" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F404" s="6" t="inlineStr">
+        <is>
+          <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G404" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>鸿景园</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="D405" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分）</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F405" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G405" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>欣荔苑</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D406" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F406" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G406" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>欣荔苑</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D407" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F407" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G407" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>餐饮场所</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>庄周过水鱼</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D408" s="6" t="inlineStr">
+        <is>
+          <t>各类收集容器的分类标志完整、正确、清晰。 （18分）</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="F408" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（4处问题）</t>
+        </is>
+      </c>
+      <c r="G408" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>深圳市南山区雍景湾幼儿园</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D409" s="6" t="inlineStr">
+        <is>
+          <t>用餐区摆放厨余垃圾、其他垃圾收集容器。（4分）</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F409" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-4)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G409" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>深圳市南山区雍景湾幼儿园</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D410" s="6" t="inlineStr">
+        <is>
+          <t>后厨区摆放可回收物、厨余垃圾、其他垃圾收集容器。（4分）</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F410" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-4)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G410" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>深圳市南山区雍景湾幼儿园</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D411" s="6" t="inlineStr">
+        <is>
+          <t>洗手间摆放其他垃圾收集容器。（6分）</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="F411" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-3)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G411" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>深圳市南山区雍景湾幼儿园</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D412" s="6" t="inlineStr">
+        <is>
+          <t>各类收集容器的分类标志完整、正确、清晰。 （12分）</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-9</t>
+        </is>
+      </c>
+      <c r="F412" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（3处问题）</t>
+        </is>
+      </c>
+      <c r="G412" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>深圳市南山区雍景湾幼儿园</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D413" s="6" t="inlineStr">
+        <is>
+          <t>收集容器、暂存点及其周围环境干净整洁，无垃圾满溢、暴露垃圾，无杂物堆放。（9分）</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="F413" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-3)（1处问题）； （3）环境卫生不整洁（投放点有散落垃圾、杂物堆放，地面有明显污水污渍等）(-3)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G413" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>深圳市南山区雍景湾幼儿园</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D414" s="6" t="inlineStr">
+        <is>
+          <t>每年至少开展一次全校性生活垃圾分类主题活动。 （3分）</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="F414" s="6" t="inlineStr">
+        <is>
+          <t>（2）未按要求开展活垃圾分类相关主题活动(-3)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G414" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>机关事业单位办公场所</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>招商街道办</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D415" s="6" t="inlineStr">
+        <is>
+          <t>各类收集容器的分类标志完整、正确、清晰。 （12分）</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="F415" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G415" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>机关事业单位办公场所</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>招商街道办</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D416" s="6" t="inlineStr">
+        <is>
+          <t>公共区域张贴或摆放垃圾分类宣传海报或指引等。（4分）</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F416" s="6" t="inlineStr">
+        <is>
+          <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-4)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G416" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>源华综合楼</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D417" s="6" t="inlineStr">
+        <is>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F417" s="6" t="inlineStr">
+        <is>
+          <t>（4）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G417" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>源华综合楼</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D418" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F418" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G418" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>翠薇园小区</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D419" s="6" t="inlineStr">
+        <is>
+          <t>设置集中分类投放点，摆放可回收物、厨余垃圾、其他垃圾三类收集容器。（6分）</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F419" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类收集容器缺失(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G419" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>翠薇园小区</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D420" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F420" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G420" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>玫瑰园小区</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D421" s="6" t="inlineStr">
+        <is>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F421" s="6" t="inlineStr">
+        <is>
+          <t>（4）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G421" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>玫瑰园小区</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D422" s="6" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F422" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G422" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>玫瑰园小区</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D423" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F423" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G423" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>玫瑰园小区</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D424" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F424" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G424" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>枫南</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D425" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F425" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G425" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>枫南</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D426" s="6" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F426" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G426" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>马坑</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D427" s="6" t="inlineStr">
+        <is>
+          <t>设置洗手设施。（2分）</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F427" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G427" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>马坑</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D428" s="6" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（6分）</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="F428" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G428" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>马坑</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D429" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F429" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G429" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>马坑</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D430" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F430" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G430" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>马坑</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D431" s="6" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F431" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G431" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>马坑</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D432" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F432" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G432" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>南澳湾花园</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D433" s="6" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F433" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G433" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>南澳湾花园</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D434" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F434" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G434" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>老街</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D435" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F435" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G435" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>老街</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D436" s="6" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F436" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G436" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>老街</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D437" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F437" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G437" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>风球山小区</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D438" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F438" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G438" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>风球山小区</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D439" s="6" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F439" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G439" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>风球山小区</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D440" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F440" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G440" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>上企沙</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D441" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F441" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G441" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>山海名苑</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D442" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F442" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G442" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>下企沙</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D443" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F443" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G443" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>金地朗悦西区</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D444" s="6" t="inlineStr">
+        <is>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F444" s="6" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G444" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>金地朗悦西区</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D445" s="6" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F445" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G445" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>金地朗悦西区</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D446" s="6" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F446" s="6" t="inlineStr">
+        <is>
+          <t>（2）围挡设置不规范（未设置围挡，围挡封闭不全，或使用移动式栅栏、水马等围合）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G446" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
           <t>金地朗悦东区</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D447" s="6" t="inlineStr">
+        <is>
+          <t>设置洗手设施。（2分）</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F447" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G447" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>金地朗悦东区</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="D366" s="6" t="inlineStr">
+      <c r="D448" s="6" t="inlineStr">
         <is>
           <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr">
+      <c r="E448" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="F366" s="6" t="inlineStr">
+      <c r="F448" s="6" t="inlineStr">
         <is>
           <t>（2）围挡设置不规范（未设置围挡，围挡封闭不全，或使用移动式栅栏、水马等围合）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G366" s="4" t="inlineStr">
+      <c r="G448" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>都市阳光名苑</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D449" s="6" t="inlineStr">
+        <is>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F449" s="6" t="inlineStr">
+        <is>
+          <t>（2）责任公示牌缺失(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G449" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>都市阳光名苑</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D450" s="6" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F450" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G450" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>都市阳光名苑</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="D451" s="6" t="inlineStr">
+        <is>
+          <t>公共区域宣传栏张贴垃圾分类投放指引或宣传海报。（2分）</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F451" s="6" t="inlineStr">
+        <is>
+          <t>（2）未规范张贴垃圾分类宣传海报（海报缺失、内容错误/未更新等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G451" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>深圳安华工业区（住宅）</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="D452" s="6" t="inlineStr">
+        <is>
+          <t>禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分）</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F452" s="6" t="inlineStr">
+        <is>
+          <t>（3）内桶未开盖(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G452" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>深圳安华工业区（住宅）</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D453" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="F453" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
+        </is>
+      </c>
+      <c r="G453" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>深圳安华工业区（住宅）</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D454" s="6" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F454" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G454" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>深圳安华工业区（住宅）</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D455" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F455" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G455" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>龙园创展大厦</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D456" s="6" t="inlineStr">
+        <is>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F456" s="6" t="inlineStr">
+        <is>
+          <t>（2）责任公示牌缺失(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G456" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>龙园创展大厦</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D457" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F457" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G457" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>龙园创展大厦</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D458" s="6" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F458" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G458" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>龙园创展大厦</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D459" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F459" s="6" t="inlineStr">
+        <is>
+          <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G459" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>龙园创展大厦</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="D460" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分）</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F460" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G460" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>供电北小区</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D461" s="6" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F461" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G461" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>供电北小区</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D462" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F462" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G462" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>供电北小区</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D463" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F463" s="6" t="inlineStr">
+        <is>
+          <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G463" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>中医院小区</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D464" s="6" t="inlineStr">
+        <is>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F464" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G464" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>中医院小区</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D465" s="6" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F465" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G465" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>中医院小区</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D466" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F466" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G466" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>中医院小区</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="D467" s="6" t="inlineStr">
+        <is>
+          <t>禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分）</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F467" s="6" t="inlineStr">
+        <is>
+          <t>（4）厨余误时投放点未开放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G467" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>中医院小区</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D468" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F468" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G468" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>中医院小区</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D469" s="6" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F469" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G469" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>顺基楼</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D470" s="6" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F470" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G470" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>顺基楼</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D471" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F471" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G471" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>顺基楼</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D472" s="6" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F472" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G472" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>医疗机构</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>泰源社区健康服务中心</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D473" s="6" t="inlineStr">
+        <is>
+          <t>公共区域成组摆放可回收物、其他垃圾收集容器。（12分）</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="F473" s="6" t="inlineStr">
+        <is>
+          <t>（2）未成组摆放两分类收集容器(-3)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G473" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>医疗机构</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>泰源社区健康服务中心</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D474" s="6" t="inlineStr">
+        <is>
+          <t>至少设置一处有害垃圾收集容器。（5分）</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="F474" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-5)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G474" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>医疗机构</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>泰源社区健康服务中心</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D475" s="6" t="inlineStr">
+        <is>
+          <t>公共区域张贴或摆放垃圾分类宣传海报或指引等。 （5分）</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="F475" s="6" t="inlineStr">
+        <is>
+          <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-5)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G475" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>玉律一区</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D476" s="6" t="inlineStr">
+        <is>
+          <t>设置洗手设施。（2分）</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F476" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G476" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>玉律一区</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D477" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F477" s="6" t="inlineStr">
+        <is>
+          <t>（2）未在黄线划定区域内(-2)（1处问题）； （3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G477" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>玉律一区</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D478" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F478" s="6" t="inlineStr">
+        <is>
+          <t>（7）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G478" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>天安高尔夫花园</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D479" s="6" t="inlineStr">
+        <is>
+          <t>至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分）</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F479" s="6" t="inlineStr">
+        <is>
+          <t>否(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G479" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>天安高尔夫花园</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D480" s="6" t="inlineStr">
+        <is>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F480" s="6" t="inlineStr">
+        <is>
+          <t>（2）责任公示牌缺失(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G480" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>天安高尔夫花园</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="D481" s="6" t="inlineStr">
+        <is>
+          <t>桶柜式垃圾投放点柜门应全天保持关闭（作业状态除外）。（4分）</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F481" s="6" t="inlineStr">
+        <is>
+          <t>（2）柜门未保持关闭(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G481" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>天安高尔夫花园</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D482" s="6" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F482" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G482" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>玉律二区</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D483" s="6" t="inlineStr">
+        <is>
+          <t>设置洗手设施。（2分）</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F483" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G483" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>玉律二区</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D484" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="F484" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）； （3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G484" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>玉律二区</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D485" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="F485" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
+        </is>
+      </c>
+      <c r="G485" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>玉律二区</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D486" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F486" s="6" t="inlineStr">
+        <is>
+          <t>（7）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G486" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>天安数码城（智慧园）</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D487" s="6" t="inlineStr">
+        <is>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F487" s="6" t="inlineStr">
+        <is>
+          <t>（2）责任公示牌缺失(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G487" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>天安数码城（智慧园）</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="D488" s="6" t="inlineStr">
+        <is>
+          <t>禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分）</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F488" s="6" t="inlineStr">
+        <is>
+          <t>（3）内桶未开盖(-2)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G488" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>天安数码城（智慧园）</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D489" s="6" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F489" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G489" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>天安数码城（智慧园）</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D490" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F490" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）； （5）暂存点存在用水用电安全隐患(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G490" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>港岛银座</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D491" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F491" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G491" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>港岛银座</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D492" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F492" s="6" t="inlineStr">
+        <is>
+          <t>（5）暂存点存在用水用电安全隐患(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G492" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>和平广场</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D493" s="6" t="inlineStr">
+        <is>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F493" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G493" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>和平广场</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D494" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F494" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G494" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>和平广场</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D495" s="6" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F495" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G495" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>和平广场</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D496" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F496" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G496" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>和平广场</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="D497" s="6" t="inlineStr">
+        <is>
+          <t>设备齐全完好，摆放整齐有序，功能正常，外观没有严重破损，没有用电隐患。（2分）</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F497" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G497" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>鸿隆世纪广场</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="D498" s="6" t="inlineStr">
+        <is>
+          <t>禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分）</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F498" s="6" t="inlineStr">
+        <is>
+          <t>（4）误时投放点未开放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G498" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>鸿隆世纪广场</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D499" s="6" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F499" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G499" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>塘下涌一村</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="D500" s="6" t="inlineStr">
+        <is>
+          <t>各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分）</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="F500" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（3处问题）</t>
+        </is>
+      </c>
+      <c r="G500" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>塘下涌一村</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="D501" s="6" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分）</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F501" s="6" t="inlineStr">
+        <is>
+          <t>（4）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G501" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>购物中心</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>盛客隆商场</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="D502" s="6" t="inlineStr">
+        <is>
+          <t>生活（果蔬）超市摆放厨余垃圾、其他垃圾收集容器。</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="F502" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-5)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G502" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>购物中心</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>盛客隆商场</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D503" s="6" t="inlineStr">
+        <is>
+          <t>至少设置一处有害垃圾收集容器。</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F503" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失</t>
+        </is>
+      </c>
+      <c r="G503" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>购物中心</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>盛客隆商场</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D504" s="6" t="inlineStr">
+        <is>
+          <t>收集容器、暂存点及其周围环境干净整洁，无垃圾满溢、暴露垃圾，无杂物堆放。</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="F504" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有散落垃圾、杂物堆放，地面有明显污水污渍）(-3)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G504" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>购物中心</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>盛客隆商场</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D505" s="6" t="inlineStr">
+        <is>
+          <t>将各类垃圾分类收集、暂存和移交。</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="F505" s="6" t="inlineStr">
+        <is>
+          <t>（2）未将各类垃圾分类收集、暂存和移交(-5)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G505" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>购物中心</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>盛客隆商场</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="D506" s="6" t="inlineStr">
+        <is>
+          <t>公共区域张贴或摆放垃圾分类宣传海报或指引等。</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F506" s="6" t="inlineStr">
+        <is>
+          <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-4)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G506" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>集贸市场</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>塘下涌综合市场</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D507" s="6" t="inlineStr">
+        <is>
+          <t>公共区域摆放可回收物、厨余垃圾、其他垃圾收集容器；垃圾暂存点摆放可回收物、厨余垃圾、其他垃圾和有害垃圾收集容器。</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="F507" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-3)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G507" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>集贸市场</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>塘下涌综合市场</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D508" s="6" t="inlineStr">
+        <is>
+          <t>各类收集容器的分类标志完整、正确、清晰。</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="F508" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G508" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>集贸市场</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>塘下涌综合市场</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D509" s="6" t="inlineStr">
+        <is>
+          <t>各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题。</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="F509" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐，内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-3)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G509" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>集贸市场</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>塘下涌综合市场</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D510" s="6" t="inlineStr">
+        <is>
+          <t>将各类垃圾分类收集、暂存和移交。</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="F510" s="6" t="inlineStr">
+        <is>
+          <t>（2）未将各类垃圾分类收集、暂存和移交(-5)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G510" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>塘下涌二村</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D511" s="6" t="inlineStr">
+        <is>
+          <t>设置洗手设施。（2分）</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F511" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G511" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>塘下涌二村</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D512" s="6" t="inlineStr">
+        <is>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F512" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G512" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>塘下涌二村</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="D513" s="6" t="inlineStr">
+        <is>
+          <t>各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分）</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="F513" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（3处问题）； （3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G513" s="4" t="inlineStr">
+        <is>
+          <t>查看证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>塘下涌二村</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D514" s="6" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F514" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G514" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
         </is>
@@ -26431,6 +34555,154 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId363"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId364"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G502" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G503" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G504" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G505" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G506" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G507" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G508" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G509" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G510" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G511" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G512" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G513" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G514" r:id="rId513"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/weeks/2026-09-10/巡查表.xlsx
+++ b/weeks/2026-09-10/巡查表.xlsx
@@ -16585,7 +16585,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -16618,7 +16622,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -16651,7 +16659,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>（2）投放口被封闭或遮挡(-2)（1处问题）； （4）厨余误时投放点未开放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -16684,7 +16696,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -16717,7 +16733,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -16750,7 +16770,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -16783,7 +16807,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -16816,7 +16844,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>否(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -16849,7 +16881,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -16882,7 +16918,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>（2）投放口被封闭或遮挡(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -16915,7 +16955,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -16948,7 +16992,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>否(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -16981,7 +17029,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17014,7 +17066,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）； （3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17047,7 +17103,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>（3）内桶未开盖(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17080,7 +17140,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17113,7 +17177,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17146,7 +17214,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17179,7 +17251,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17212,7 +17288,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17245,7 +17325,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>（2）车辆挡住投放点过道、投放口前堆放大件杂物，阻碍居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17278,7 +17362,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17311,7 +17399,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17344,7 +17436,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>（2）未在黄线划定区域内(-2)（2处问题）； （3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17377,7 +17473,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）； （5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17410,7 +17510,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17443,7 +17547,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17476,7 +17584,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）； （4）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17509,7 +17621,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17542,7 +17658,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17575,7 +17695,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17608,7 +17732,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17641,7 +17769,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17674,7 +17806,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>（2）未使用(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17707,7 +17843,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr"/>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（2处问题）</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17740,7 +17880,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐，内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17773,7 +17917,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17806,7 +17954,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17839,7 +17991,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17872,7 +18028,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr"/>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>（2）未成组摆放两分类收集容器(-3)</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17905,7 +18065,11 @@
           <t>-5</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr"/>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-5)（1处问题）</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17938,7 +18102,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -17971,7 +18139,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-6)（1处问题）</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18004,7 +18176,11 @@
           <t>-9</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（3处问题）</t>
+        </is>
+      </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18037,7 +18213,11 @@
           <t>-5</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>（2）未设置光盘行动、节约粮食等宣传海报或温馨提示等(-5)（1处问题）</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18070,7 +18250,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18103,7 +18287,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18136,7 +18324,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18169,7 +18361,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18202,7 +18398,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（2处问题）</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18235,7 +18435,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>（2）未成组摆放两分类收集容器；(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18268,7 +18472,11 @@
           <t>-9</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（3处问题）</t>
+        </is>
+      </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18301,7 +18509,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>（2）其他问题说明（备注描述）(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18334,7 +18546,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>（2）未张贴节约用纸、双面打印宣传标语(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18367,7 +18583,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（2处问题）</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18400,7 +18620,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18433,7 +18657,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr"/>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18466,7 +18694,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18499,7 +18731,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr"/>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18532,7 +18768,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18565,7 +18805,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr"/>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>（3）内桶未开盖(-2)（1处问题）； （4）误时投放点未开放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18598,7 +18842,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr"/>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18631,7 +18879,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr"/>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18664,7 +18916,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr"/>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18697,7 +18953,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F66" s="6" t="inlineStr"/>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>（4）误时投放点未开放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18730,7 +18990,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr"/>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18763,7 +19027,11 @@
           <t>-5</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr"/>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-5)（1处问题）</t>
+        </is>
+      </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18796,7 +19064,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr"/>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18829,7 +19101,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F70" s="6" t="inlineStr"/>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>（7）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18862,7 +19138,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr"/>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>（2）存在超过3家(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18895,7 +19175,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr"/>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18928,7 +19212,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr"/>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18961,7 +19249,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr"/>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -18994,7 +19286,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr"/>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19027,7 +19323,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr"/>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）； （5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19060,7 +19360,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr"/>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19093,7 +19397,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr"/>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）； （4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）； （7）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19126,7 +19434,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr"/>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>（2）未规范张贴垃圾分类宣传海报（海报缺失、内容错误/未更新等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19159,7 +19471,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr"/>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19192,7 +19508,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr"/>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19225,7 +19545,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr"/>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19258,7 +19582,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr"/>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19291,7 +19619,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr"/>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19324,7 +19656,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr"/>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19357,7 +19693,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr"/>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>（4）误时投放点未开放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19390,7 +19730,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr"/>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19423,7 +19767,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr"/>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19456,7 +19804,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr"/>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19489,7 +19841,11 @@
           <t>-10</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr"/>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>（2）主动向消费者提供客房一次性日用品(-10)（1处问题）</t>
+        </is>
+      </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19522,7 +19878,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr"/>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19555,7 +19915,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr"/>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>（2）投放口被封闭或遮挡(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19588,7 +19952,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr"/>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19621,7 +19989,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F94" s="6" t="inlineStr"/>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19654,7 +20026,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr"/>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19687,7 +20063,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr"/>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>（2）存在超过3家(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19720,7 +20100,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr"/>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>周边环境脏乱(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19753,7 +20137,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr"/>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19786,7 +20174,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr"/>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19819,7 +20211,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr"/>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（4处问题）</t>
+        </is>
+      </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19852,7 +20248,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F101" s="6" t="inlineStr"/>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19885,7 +20285,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F102" s="6" t="inlineStr"/>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19918,7 +20322,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F103" s="6" t="inlineStr"/>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19951,7 +20359,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F104" s="6" t="inlineStr"/>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -19984,7 +20396,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F105" s="6" t="inlineStr"/>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20017,7 +20433,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F106" s="6" t="inlineStr"/>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20050,7 +20470,11 @@
           <t>-5</t>
         </is>
       </c>
-      <c r="F107" s="6" t="inlineStr"/>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失；(-5)（1处问题）</t>
+        </is>
+      </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20083,7 +20507,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F108" s="6" t="inlineStr"/>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20116,7 +20544,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F109" s="6" t="inlineStr"/>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>（2）责任公示牌缺失(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20149,7 +20581,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F110" s="6" t="inlineStr"/>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20182,7 +20618,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F111" s="6" t="inlineStr"/>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20215,7 +20655,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F112" s="6" t="inlineStr"/>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20248,7 +20692,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F113" s="6" t="inlineStr"/>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20281,7 +20729,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F114" s="6" t="inlineStr"/>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20314,7 +20766,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F115" s="6" t="inlineStr"/>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20347,7 +20803,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F116" s="6" t="inlineStr"/>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20380,7 +20840,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F117" s="6" t="inlineStr"/>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20413,7 +20877,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F118" s="6" t="inlineStr"/>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20446,7 +20914,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F119" s="6" t="inlineStr"/>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20479,7 +20951,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F120" s="6" t="inlineStr"/>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20512,7 +20988,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F121" s="6" t="inlineStr"/>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类收集容器缺失(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20545,7 +21025,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F122" s="6" t="inlineStr"/>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（4处问题）</t>
+        </is>
+      </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20578,7 +21062,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F123" s="6" t="inlineStr"/>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20611,7 +21099,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F124" s="6" t="inlineStr"/>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20644,7 +21136,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F125" s="6" t="inlineStr"/>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20677,7 +21173,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F126" s="6" t="inlineStr"/>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20710,7 +21210,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr"/>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20743,7 +21247,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F128" s="6" t="inlineStr"/>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20776,7 +21284,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F129" s="6" t="inlineStr"/>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20809,7 +21321,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F130" s="6" t="inlineStr"/>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20842,7 +21358,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F131" s="6" t="inlineStr"/>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（5处问题）</t>
+        </is>
+      </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20875,7 +21395,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F132" s="6" t="inlineStr"/>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20908,7 +21432,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F133" s="6" t="inlineStr"/>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20941,7 +21469,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr"/>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -20974,7 +21506,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F135" s="6" t="inlineStr"/>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21007,7 +21543,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F136" s="6" t="inlineStr"/>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21040,7 +21580,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F137" s="6" t="inlineStr"/>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21073,7 +21617,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F138" s="6" t="inlineStr"/>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21106,7 +21654,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F139" s="6" t="inlineStr"/>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21139,7 +21691,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F140" s="6" t="inlineStr"/>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21172,7 +21728,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F141" s="6" t="inlineStr"/>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21205,7 +21765,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F142" s="6" t="inlineStr"/>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21238,7 +21802,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F143" s="6" t="inlineStr"/>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>（1）存在问题(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21271,7 +21839,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F144" s="6" t="inlineStr"/>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21304,7 +21876,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F145" s="6" t="inlineStr"/>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21337,7 +21913,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F146" s="6" t="inlineStr"/>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（4处问题）</t>
+        </is>
+      </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21370,7 +21950,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F147" s="6" t="inlineStr"/>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（4处问题）</t>
+        </is>
+      </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21403,7 +21987,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F148" s="6" t="inlineStr"/>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G148" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21436,7 +22024,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F149" s="6" t="inlineStr"/>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21469,7 +22061,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F150" s="6" t="inlineStr"/>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-6)（1处问题）</t>
+        </is>
+      </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21502,7 +22098,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F151" s="6" t="inlineStr"/>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G151" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21535,7 +22135,11 @@
           <t>-5</t>
         </is>
       </c>
-      <c r="F152" s="6" t="inlineStr"/>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>（2）未设置光盘行动、节约粮食等宣传海报或温馨提示等(-5)（1处问题）</t>
+        </is>
+      </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21568,7 +22172,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F153" s="6" t="inlineStr"/>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-4)（1处问题）</t>
+        </is>
+      </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21601,7 +22209,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F154" s="6" t="inlineStr"/>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21634,7 +22246,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F155" s="6" t="inlineStr"/>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21667,7 +22283,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F156" s="6" t="inlineStr"/>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21700,7 +22320,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F157" s="6" t="inlineStr"/>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21733,7 +22357,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F158" s="6" t="inlineStr"/>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G158" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21766,7 +22394,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F159" s="6" t="inlineStr"/>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21799,7 +22431,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F160" s="6" t="inlineStr"/>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G160" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21832,7 +22468,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F161" s="6" t="inlineStr"/>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21865,7 +22505,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F162" s="6" t="inlineStr"/>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21898,7 +22542,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F163" s="6" t="inlineStr"/>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21931,7 +22579,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F164" s="6" t="inlineStr"/>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（2处问题）</t>
+        </is>
+      </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21964,7 +22616,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F165" s="6" t="inlineStr"/>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>（2）责任公示牌缺失(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -21997,7 +22653,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F166" s="6" t="inlineStr"/>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22030,7 +22690,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F167" s="6" t="inlineStr"/>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G167" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22063,7 +22727,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F168" s="6" t="inlineStr"/>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22096,7 +22764,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F169" s="6" t="inlineStr"/>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>（2）责任公示牌缺失(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22129,7 +22801,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F170" s="6" t="inlineStr"/>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22162,7 +22838,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F171" s="6" t="inlineStr"/>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>（2）柜门未保持关闭(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22195,7 +22875,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F172" s="6" t="inlineStr"/>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>（3）内桶未开盖(-2)（1处问题）； （4）误时投放点未开放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G172" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22228,7 +22912,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F173" s="6" t="inlineStr"/>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G173" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22261,7 +22949,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F174" s="6" t="inlineStr"/>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G174" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22294,7 +22986,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F175" s="6" t="inlineStr"/>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>（2）未使用(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G175" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22327,7 +23023,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F176" s="6" t="inlineStr"/>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>否(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G176" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22360,7 +23060,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F177" s="6" t="inlineStr"/>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G177" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22393,7 +23097,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F178" s="6" t="inlineStr"/>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G178" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22426,7 +23134,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F179" s="6" t="inlineStr"/>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22459,7 +23171,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F180" s="6" t="inlineStr"/>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G180" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22492,7 +23208,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F181" s="6" t="inlineStr"/>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>（2）未规范张贴垃圾分类宣传海报（海报缺失、内容错误/未更新等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22525,7 +23245,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F182" s="6" t="inlineStr"/>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>否(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G182" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22558,7 +23282,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F183" s="6" t="inlineStr"/>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G183" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22591,7 +23319,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F184" s="6" t="inlineStr"/>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G184" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22624,7 +23356,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr"/>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>（2）责任公示牌缺失(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G185" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22657,7 +23393,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr"/>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G186" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22690,7 +23430,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr"/>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>（3）内桶未开盖(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G187" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22723,7 +23467,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr"/>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G188" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22756,7 +23504,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr"/>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G189" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22789,7 +23541,11 @@
           <t>-5</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr"/>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-5)（1处问题）</t>
+        </is>
+      </c>
       <c r="G190" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22822,7 +23578,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F191" s="6" t="inlineStr"/>
+      <c r="F191" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（2处问题）</t>
+        </is>
+      </c>
       <c r="G191" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22855,7 +23615,11 @@
           <t>-10</t>
         </is>
       </c>
-      <c r="F192" s="6" t="inlineStr"/>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>（2）主动向消费者提供客房一次性日用品(-10)（1处问题）</t>
+        </is>
+      </c>
       <c r="G192" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22888,7 +23652,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F193" s="6" t="inlineStr"/>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-6)（1处问题）</t>
+        </is>
+      </c>
       <c r="G193" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22921,7 +23689,11 @@
           <t>-9</t>
         </is>
       </c>
-      <c r="F194" s="6" t="inlineStr"/>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（3处问题）</t>
+        </is>
+      </c>
       <c r="G194" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22954,7 +23726,11 @@
           <t>-5</t>
         </is>
       </c>
-      <c r="F195" s="6" t="inlineStr"/>
+      <c r="F195" s="6" t="inlineStr">
+        <is>
+          <t>（2）未设置光盘行动、节约粮食等宣传海报或温馨提示等(-5)（1处问题）</t>
+        </is>
+      </c>
       <c r="G195" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -22987,7 +23763,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F196" s="6" t="inlineStr"/>
+      <c r="F196" s="6" t="inlineStr">
+        <is>
+          <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-4)（1处问题）</t>
+        </is>
+      </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23020,7 +23800,11 @@
           <t>-8</t>
         </is>
       </c>
-      <c r="F197" s="6" t="inlineStr"/>
+      <c r="F197" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述） (-8)（1处问题）</t>
+        </is>
+      </c>
       <c r="G197" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23053,7 +23837,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F198" s="6" t="inlineStr"/>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（2处问题）</t>
+        </is>
+      </c>
       <c r="G198" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23086,7 +23874,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F199" s="6" t="inlineStr"/>
+      <c r="F199" s="6" t="inlineStr">
+        <is>
+          <t>（2）未成组摆放两分类收集容器(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G199" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23119,7 +23911,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F200" s="6" t="inlineStr"/>
+      <c r="F200" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(5)（1处问题）</t>
+        </is>
+      </c>
       <c r="G200" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23152,7 +23948,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F201" s="6" t="inlineStr"/>
+      <c r="F201" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有散落垃圾、杂物堆放，地面有明显污水污渍等）(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G201" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23185,7 +23985,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F202" s="6" t="inlineStr"/>
+      <c r="F202" s="6" t="inlineStr">
+        <is>
+          <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-4)（1处问题）</t>
+        </is>
+      </c>
       <c r="G202" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23218,7 +24022,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F203" s="6" t="inlineStr"/>
+      <c r="F203" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G203" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23251,7 +24059,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F204" s="6" t="inlineStr"/>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G204" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23284,7 +24096,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F205" s="6" t="inlineStr"/>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G205" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23317,7 +24133,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F206" s="6" t="inlineStr"/>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G206" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23350,7 +24170,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F207" s="6" t="inlineStr"/>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G207" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23383,7 +24207,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F208" s="6" t="inlineStr"/>
+      <c r="F208" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G208" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23416,7 +24244,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F209" s="6" t="inlineStr"/>
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G209" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23449,7 +24281,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F210" s="6" t="inlineStr"/>
+      <c r="F210" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G210" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23482,7 +24318,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F211" s="6" t="inlineStr"/>
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>（2）洗手设施缺失(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G211" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23515,7 +24355,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F212" s="6" t="inlineStr"/>
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G212" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23548,7 +24392,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F213" s="6" t="inlineStr"/>
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G213" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23581,7 +24429,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F214" s="6" t="inlineStr"/>
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G214" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23614,7 +24466,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F215" s="6" t="inlineStr"/>
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G215" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23647,7 +24503,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F216" s="6" t="inlineStr"/>
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G216" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23680,7 +24540,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F217" s="6" t="inlineStr"/>
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>（4）误时投放点未开放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G217" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23713,7 +24577,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F218" s="6" t="inlineStr"/>
+      <c r="F218" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G218" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23746,7 +24614,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F219" s="6" t="inlineStr"/>
+      <c r="F219" s="6" t="inlineStr">
+        <is>
+          <t>（2）未使用(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G219" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23779,7 +24651,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F220" s="6" t="inlineStr"/>
+      <c r="F220" s="6" t="inlineStr">
+        <is>
+          <t>（2）洗手设施缺失(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G220" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23812,7 +24688,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F221" s="6" t="inlineStr"/>
+      <c r="F221" s="6" t="inlineStr">
+        <is>
+          <t>（2）围挡设置不规范（未设置围挡，围挡封闭不全，或使用移动式栅栏、水马等围合）(-2)（1处问题）； （3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）； （5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G221" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23845,7 +24725,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F222" s="6" t="inlineStr"/>
+      <c r="F222" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G222" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23878,7 +24762,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F223" s="6" t="inlineStr"/>
+      <c r="F223" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23911,7 +24799,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F224" s="6" t="inlineStr"/>
+      <c r="F224" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23944,7 +24836,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F225" s="6" t="inlineStr"/>
+      <c r="F225" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G225" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -23977,7 +24873,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F226" s="6" t="inlineStr"/>
+      <c r="F226" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G226" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24010,7 +24910,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F227" s="6" t="inlineStr"/>
+      <c r="F227" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G227" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24043,7 +24947,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F228" s="6" t="inlineStr"/>
+      <c r="F228" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）； （5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G228" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24076,7 +24984,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F229" s="6" t="inlineStr"/>
+      <c r="F229" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G229" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24109,7 +25021,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F230" s="6" t="inlineStr"/>
+      <c r="F230" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G230" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24142,7 +25058,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F231" s="6" t="inlineStr"/>
+      <c r="F231" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G231" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24175,7 +25095,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F232" s="6" t="inlineStr"/>
+      <c r="F232" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G232" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24208,7 +25132,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F233" s="6" t="inlineStr"/>
+      <c r="F233" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G233" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24241,7 +25169,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F234" s="6" t="inlineStr"/>
+      <c r="F234" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）； （5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G234" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24274,7 +25206,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F235" s="6" t="inlineStr"/>
+      <c r="F235" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G235" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24307,7 +25243,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F236" s="6" t="inlineStr"/>
+      <c r="F236" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G236" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24340,7 +25280,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F237" s="6" t="inlineStr"/>
+      <c r="F237" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G237" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24373,7 +25317,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F238" s="6" t="inlineStr"/>
+      <c r="F238" s="6" t="inlineStr">
+        <is>
+          <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-4)（1处问题）</t>
+        </is>
+      </c>
       <c r="G238" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24406,7 +25354,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F239" s="6" t="inlineStr"/>
+      <c r="F239" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G239" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24439,7 +25391,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F240" s="6" t="inlineStr"/>
+      <c r="F240" s="6" t="inlineStr">
+        <is>
+          <t>周边环境脏乱(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G240" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24472,7 +25428,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F241" s="6" t="inlineStr"/>
+      <c r="F241" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类收集容器缺失(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G241" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24505,7 +25465,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F242" s="6" t="inlineStr"/>
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>（2）洗手设施缺失(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G242" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24538,7 +25502,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F243" s="6" t="inlineStr"/>
+      <c r="F243" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G243" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24571,7 +25539,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F244" s="6" t="inlineStr"/>
+      <c r="F244" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G244" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24604,7 +25576,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F245" s="6" t="inlineStr"/>
+      <c r="F245" s="6" t="inlineStr">
+        <is>
+          <t>（2）未使用(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G245" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24637,7 +25613,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F246" s="6" t="inlineStr"/>
+      <c r="F246" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G246" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24670,7 +25650,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F247" s="6" t="inlineStr"/>
+      <c r="F247" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G247" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24703,7 +25687,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F248" s="6" t="inlineStr"/>
+      <c r="F248" s="6" t="inlineStr">
+        <is>
+          <t>（2）车辆挡住投放点过道、投放口前堆放大件杂物，阻碍居民投放(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G248" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24736,7 +25724,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F249" s="6" t="inlineStr"/>
+      <c r="F249" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G249" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24769,7 +25761,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F250" s="6" t="inlineStr"/>
+      <c r="F250" s="6" t="inlineStr">
+        <is>
+          <t>（4）其他问题（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G250" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24802,7 +25798,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F251" s="6" t="inlineStr"/>
+      <c r="F251" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G251" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24835,7 +25835,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F252" s="6" t="inlineStr"/>
+      <c r="F252" s="6" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G252" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24868,7 +25872,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F253" s="6" t="inlineStr"/>
+      <c r="F253" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G253" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24901,7 +25909,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F254" s="6" t="inlineStr"/>
+      <c r="F254" s="6" t="inlineStr">
+        <is>
+          <t>（4）误时投放点未开放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G254" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24934,7 +25946,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F255" s="6" t="inlineStr"/>
+      <c r="F255" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G255" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -24967,7 +25983,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F256" s="6" t="inlineStr"/>
+      <c r="F256" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G256" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25000,7 +26020,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F257" s="6" t="inlineStr"/>
+      <c r="F257" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G257" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25033,7 +26057,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F258" s="6" t="inlineStr"/>
+      <c r="F258" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G258" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25066,7 +26094,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F259" s="6" t="inlineStr"/>
+      <c r="F259" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G259" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25099,7 +26131,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F260" s="6" t="inlineStr"/>
+      <c r="F260" s="6" t="inlineStr">
+        <is>
+          <t>（3）内桶未开盖(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G260" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25132,7 +26168,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F261" s="6" t="inlineStr"/>
+      <c r="F261" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G261" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25165,7 +26205,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F262" s="6" t="inlineStr"/>
+      <c r="F262" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G262" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25198,7 +26242,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F263" s="6" t="inlineStr"/>
+      <c r="F263" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G263" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25231,7 +26279,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F264" s="6" t="inlineStr"/>
+      <c r="F264" s="6" t="inlineStr">
+        <is>
+          <t>（4）误时投放点未开放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G264" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25264,7 +26316,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F265" s="6" t="inlineStr"/>
+      <c r="F265" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G265" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25297,7 +26353,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F266" s="6" t="inlineStr"/>
+      <c r="F266" s="6" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G266" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25330,7 +26390,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F267" s="6" t="inlineStr"/>
+      <c r="F267" s="6" t="inlineStr">
+        <is>
+          <t>（3）暂存点与专项垃圾暂存点共用的，应保留一部分位置存放专项垃圾(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G267" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25363,7 +26427,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F268" s="6" t="inlineStr"/>
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G268" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25396,7 +26464,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F269" s="6" t="inlineStr"/>
+      <c r="F269" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G269" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25429,7 +26501,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F270" s="6" t="inlineStr"/>
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G270" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25462,7 +26538,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F271" s="6" t="inlineStr"/>
+      <c r="F271" s="6" t="inlineStr">
+        <is>
+          <t>（4）其他问题（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G271" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25495,7 +26575,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F272" s="6" t="inlineStr"/>
+      <c r="F272" s="6" t="inlineStr">
+        <is>
+          <t>否(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G272" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25528,7 +26612,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F273" s="6" t="inlineStr"/>
+      <c r="F273" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（3处问题）</t>
+        </is>
+      </c>
       <c r="G273" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25561,7 +26649,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F274" s="6" t="inlineStr"/>
+      <c r="F274" s="6" t="inlineStr">
+        <is>
+          <t>（2）投放口被封闭或遮挡(-2)（3处问题）； （3）内桶未开盖(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G274" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25594,7 +26686,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F275" s="6" t="inlineStr"/>
+      <c r="F275" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（5处问题）</t>
+        </is>
+      </c>
       <c r="G275" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25627,7 +26723,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F276" s="6" t="inlineStr"/>
+      <c r="F276" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G276" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25660,7 +26760,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F277" s="6" t="inlineStr"/>
+      <c r="F277" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）； （3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G277" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25693,7 +26797,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F278" s="6" t="inlineStr"/>
+      <c r="F278" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G278" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25726,7 +26834,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F279" s="6" t="inlineStr"/>
+      <c r="F279" s="6" t="inlineStr">
+        <is>
+          <t>（4）误时投放点未开放(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G279" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25759,7 +26871,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F280" s="6" t="inlineStr"/>
+      <c r="F280" s="6" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G280" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25792,7 +26908,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F281" s="6" t="inlineStr"/>
+      <c r="F281" s="6" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G281" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25825,7 +26945,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F282" s="6" t="inlineStr"/>
+      <c r="F282" s="6" t="inlineStr">
+        <is>
+          <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G282" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25858,7 +26982,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F283" s="6" t="inlineStr"/>
+      <c r="F283" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类收集容器缺失(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G283" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25891,7 +27019,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F284" s="6" t="inlineStr"/>
+      <c r="F284" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（3处问题）</t>
+        </is>
+      </c>
       <c r="G284" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25924,7 +27056,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F285" s="6" t="inlineStr"/>
+      <c r="F285" s="6" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G285" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25957,7 +27093,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F286" s="6" t="inlineStr"/>
+      <c r="F286" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G286" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -25990,7 +27130,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F287" s="6" t="inlineStr"/>
+      <c r="F287" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G287" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26023,7 +27167,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F288" s="6" t="inlineStr"/>
+      <c r="F288" s="6" t="inlineStr">
+        <is>
+          <t>（2）责任公示牌缺失(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G288" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26056,7 +27204,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F289" s="6" t="inlineStr"/>
+      <c r="F289" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（2处问题）； （3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G289" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26089,7 +27241,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F290" s="6" t="inlineStr"/>
+      <c r="F290" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
+        </is>
+      </c>
       <c r="G290" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26122,7 +27278,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F291" s="6" t="inlineStr"/>
+      <c r="F291" s="6" t="inlineStr">
+        <is>
+          <t>（2）未成组摆放两分类收集容器(-3)</t>
+        </is>
+      </c>
       <c r="G291" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26155,7 +27315,11 @@
           <t>-5</t>
         </is>
       </c>
-      <c r="F292" s="6" t="inlineStr"/>
+      <c r="F292" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-5)（1处问题）</t>
+        </is>
+      </c>
       <c r="G292" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26188,7 +27352,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F293" s="6" t="inlineStr"/>
+      <c r="F293" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G293" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26221,7 +27389,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F294" s="6" t="inlineStr"/>
+      <c r="F294" s="6" t="inlineStr">
+        <is>
+          <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-4)（1处问题）</t>
+        </is>
+      </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26254,7 +27426,11 @@
           <t>-3</t>
         </is>
       </c>
-      <c r="F295" s="6" t="inlineStr"/>
+      <c r="F295" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
+        </is>
+      </c>
       <c r="G295" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26287,7 +27463,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F296" s="6" t="inlineStr"/>
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类收集容器缺失(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G296" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26320,7 +27500,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F297" s="6" t="inlineStr"/>
+      <c r="F297" s="6" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G297" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26353,7 +27537,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F298" s="6" t="inlineStr"/>
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>（3）内桶未开盖(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G298" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26386,7 +27574,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F299" s="6" t="inlineStr"/>
+      <c r="F299" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
+        </is>
+      </c>
       <c r="G299" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26419,7 +27611,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F300" s="6" t="inlineStr"/>
+      <c r="F300" s="6" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G300" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26452,7 +27648,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F301" s="6" t="inlineStr"/>
+      <c r="F301" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G301" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26485,7 +27685,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F302" s="6" t="inlineStr"/>
+      <c r="F302" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G302" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26518,7 +27722,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F303" s="6" t="inlineStr"/>
+      <c r="F303" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G303" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26551,7 +27759,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F304" s="6" t="inlineStr"/>
+      <c r="F304" s="6" t="inlineStr">
+        <is>
+          <t>（2）投放口被封闭或遮挡(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G304" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26584,7 +27796,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F305" s="6" t="inlineStr"/>
+      <c r="F305" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）； （4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）； （5）暂存点存在用水用电安全隐患(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G305" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26617,7 +27833,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F306" s="6" t="inlineStr"/>
+      <c r="F306" s="6" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G306" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26650,7 +27870,11 @@
           <t>-9</t>
         </is>
       </c>
-      <c r="F307" s="6" t="inlineStr"/>
+      <c r="F307" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（3处问题）</t>
+        </is>
+      </c>
       <c r="G307" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26683,7 +27907,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F308" s="6" t="inlineStr"/>
+      <c r="F308" s="6" t="inlineStr">
+        <is>
+          <t>否(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G308" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26716,7 +27944,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F309" s="6" t="inlineStr"/>
+      <c r="F309" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
+        </is>
+      </c>
       <c r="G309" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26749,7 +27981,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F310" s="6" t="inlineStr"/>
+      <c r="F310" s="6" t="inlineStr">
+        <is>
+          <t>否(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G310" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26782,7 +28018,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F311" s="6" t="inlineStr"/>
+      <c r="F311" s="6" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（5处问题）</t>
+        </is>
+      </c>
       <c r="G311" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26815,7 +28055,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F312" s="6" t="inlineStr"/>
+      <c r="F312" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（5处问题）</t>
+        </is>
+      </c>
       <c r="G312" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26848,7 +28092,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F313" s="6" t="inlineStr"/>
+      <c r="F313" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G313" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -26881,7 +28129,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F314" s="6" t="inlineStr"/>
+      <c r="F314" s="6" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（5处问题）</t>
+        </is>
+      </c>
       <c r="G314" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27099,7 +28351,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F320" s="6" t="inlineStr"/>
+      <c r="F320" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G320" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27132,7 +28388,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F321" s="6" t="inlineStr"/>
+      <c r="F321" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G321" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27165,7 +28425,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F322" s="6" t="inlineStr"/>
+      <c r="F322" s="6" t="inlineStr">
+        <is>
+          <t>（4）其他问题说明（备注描述）(-1)（2处问题）</t>
+        </is>
+      </c>
       <c r="G322" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27198,7 +28462,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F323" s="6" t="inlineStr"/>
+      <c r="F323" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G323" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27231,7 +28499,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F324" s="6" t="inlineStr"/>
+      <c r="F324" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（2处问题）； （3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G324" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27264,7 +28536,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F325" s="6" t="inlineStr"/>
+      <c r="F325" s="6" t="inlineStr">
+        <is>
+          <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G325" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27297,7 +28573,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F326" s="6" t="inlineStr"/>
+      <c r="F326" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G326" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27330,7 +28610,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F327" s="6" t="inlineStr"/>
+      <c r="F327" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）； （4）分类设施存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G327" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27363,7 +28647,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F328" s="6" t="inlineStr"/>
+      <c r="F328" s="6" t="inlineStr">
+        <is>
+          <t>（4）其他问题说明（备注描述）(-1)（2处问题）</t>
+        </is>
+      </c>
       <c r="G328" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27396,7 +28684,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F329" s="6" t="inlineStr"/>
+      <c r="F329" s="6" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G329" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27429,7 +28721,11 @@
           <t>-6</t>
         </is>
       </c>
-      <c r="F330" s="6" t="inlineStr"/>
+      <c r="F330" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）； （3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G330" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27462,7 +28758,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F331" s="6" t="inlineStr"/>
+      <c r="F331" s="6" t="inlineStr">
+        <is>
+          <t>（4）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G331" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27495,7 +28795,11 @@
           <t>-5</t>
         </is>
       </c>
-      <c r="F332" s="6" t="inlineStr"/>
+      <c r="F332" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-5)（1处问题）</t>
+        </is>
+      </c>
       <c r="G332" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27528,7 +28832,11 @@
           <t>-12</t>
         </is>
       </c>
-      <c r="F333" s="6" t="inlineStr"/>
+      <c r="F333" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（4处问题）</t>
+        </is>
+      </c>
       <c r="G333" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27561,7 +28869,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F334" s="6" t="inlineStr"/>
+      <c r="F334" s="6" t="inlineStr">
+        <is>
+          <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-4)（1处问题）</t>
+        </is>
+      </c>
       <c r="G334" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27594,7 +28906,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F335" s="6" t="inlineStr"/>
+      <c r="F335" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）； （3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G335" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27627,7 +28943,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F336" s="6" t="inlineStr"/>
+      <c r="F336" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G336" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27660,7 +28980,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F337" s="6" t="inlineStr"/>
+      <c r="F337" s="6" t="inlineStr">
+        <is>
+          <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G337" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27693,7 +29017,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F338" s="6" t="inlineStr"/>
+      <c r="F338" s="6" t="inlineStr">
+        <is>
+          <t>（2）未使用(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G338" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27726,7 +29054,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F339" s="6" t="inlineStr"/>
+      <c r="F339" s="6" t="inlineStr">
+        <is>
+          <t>周边环境脏乱(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G339" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27759,7 +29091,11 @@
           <t>-1</t>
         </is>
       </c>
-      <c r="F340" s="6" t="inlineStr"/>
+      <c r="F340" s="6" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
       <c r="G340" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27792,7 +29128,11 @@
           <t>-4</t>
         </is>
       </c>
-      <c r="F341" s="6" t="inlineStr"/>
+      <c r="F341" s="6" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（2处问题）</t>
+        </is>
+      </c>
       <c r="G341" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27825,7 +29165,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F342" s="6" t="inlineStr"/>
+      <c r="F342" s="6" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G342" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27858,7 +29202,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F343" s="6" t="inlineStr"/>
+      <c r="F343" s="6" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G343" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
@@ -27891,7 +29239,11 @@
           <t>-2</t>
         </is>
       </c>
-      <c r="F344" s="6" t="inlineStr"/>
+      <c r="F344" s="6" t="inlineStr">
+        <is>
+          <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
+        </is>
+      </c>
       <c r="G344" s="4" t="inlineStr">
         <is>
           <t>查看证据</t>
